--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 12-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 13-03-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -459,7 +459,7 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>C. VANIGLIA</v>
@@ -471,7 +471,7 @@
         <v>C. LATTE</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
@@ -511,7 +511,7 @@
         <v>C. ZENZERO</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>C. MADAGASCAR</v>
@@ -531,7 +531,7 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>C. CANNELLA</v>
@@ -543,7 +543,7 @@
         <v>C. VENEZUELA</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="str">
         <v>ANGURIA</v>
@@ -575,7 +575,7 @@
         <v>AVOCADO E LIME</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -744,7 +744,7 @@
         <v>FRUTTI BOSCO</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -758,7 +758,7 @@
         <v>C. ESTASY</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
         <v>LAMPONE</v>
@@ -812,7 +812,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="str">
         <v>NOCCIOLATA</v>
@@ -821,7 +821,7 @@
         <v>P. VEGAN</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
         <v>MANGO</v>
@@ -847,7 +847,7 @@
         <v>MELA N. E C.</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -881,7 +881,7 @@
         <v>LAVANDA</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="str">
         <v>SUSHI GELATO</v>
@@ -969,7 +969,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="str">
         <v>PANETTONE</v>
@@ -1021,7 +1021,7 @@
         <v>PISTACCHI</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="str">
         <v>PICCHIE</v>
@@ -1047,7 +1047,7 @@
         <v>PESCA AL VINO</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1072,7 +1072,7 @@
         <v>STRIA</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="str">
         <v>COPP. GRANDI</v>
@@ -1113,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1160,7 +1160,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -1169,10 +1169,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2.898</v>
+        <v>8.688</v>
       </c>
     </row>
     <row r="4">
@@ -1180,7 +1180,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -1189,10 +1189,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>8.688</v>
+        <v>6.087</v>
       </c>
     </row>
     <row r="5">
@@ -1200,7 +1200,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -1209,10 +1209,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>12.109</v>
+        <v>2.466</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>CACHI</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -1232,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>2.466</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1240,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>CACHI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -1249,10 +1249,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="str">
-        <v>2.022</v>
+        <v>11.858</v>
       </c>
     </row>
     <row r="8">
@@ -1260,7 +1260,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -1269,10 +1269,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>11.858</v>
+        <v>2.947</v>
       </c>
     </row>
     <row r="9">
@@ -1280,7 +1280,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -1292,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>2.947</v>
+        <v>2.876</v>
       </c>
     </row>
     <row r="10">
@@ -1300,7 +1300,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.876</v>
+        <v>3.057</v>
       </c>
     </row>
     <row r="11">
@@ -1320,7 +1320,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -1332,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>3.057</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -1352,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.000</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="13">
@@ -1360,7 +1360,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -1372,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.775</v>
+        <v>3.001</v>
       </c>
     </row>
     <row r="14">
@@ -1380,7 +1380,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -1392,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.001</v>
+        <v>2.881</v>
       </c>
     </row>
     <row r="15">
@@ -1400,7 +1400,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1409,10 +1409,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>5.762</v>
+        <v>2.970</v>
       </c>
     </row>
     <row r="16">
@@ -1420,7 +1420,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1429,10 +1429,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.970</v>
+        <v>5.432</v>
       </c>
     </row>
     <row r="17">
@@ -1440,7 +1440,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1449,10 +1449,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>5.432</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="18">
@@ -1460,7 +1460,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1472,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.616</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="19">
@@ -1480,7 +1480,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -1492,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.819</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="20">
@@ -1500,7 +1500,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -1512,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.708</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="21">
@@ -1520,7 +1520,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1529,10 +1529,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.764</v>
+        <v>5.909</v>
       </c>
     </row>
     <row r="22">
@@ -1540,7 +1540,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -1549,10 +1549,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="str">
-        <v>8.614</v>
+        <v>9.486</v>
       </c>
     </row>
     <row r="23">
@@ -1560,7 +1560,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FRAGOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -1569,10 +1569,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>11.591</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="24">
@@ -1580,7 +1580,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LEMON CURD</v>
+        <v>LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -1589,10 +1589,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>2.609</v>
+        <v>10.105</v>
       </c>
     </row>
     <row r="25">
@@ -1600,7 +1600,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -1609,10 +1609,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>12.603</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="26">
@@ -1620,7 +1620,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.722</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="27">
@@ -1640,7 +1640,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -1649,10 +1649,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>3.050</v>
+        <v>5.229</v>
       </c>
     </row>
     <row r="28">
@@ -1660,7 +1660,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -1669,10 +1669,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>5.229</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="29">
@@ -1680,7 +1680,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MORA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -1689,10 +1689,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.325</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="30">
@@ -1700,7 +1700,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MORA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -1709,10 +1709,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="str">
-        <v>2.411</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="31">
@@ -1720,7 +1720,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1732,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="F31" t="str">
-        <v>9.065</v>
+        <v>8.812</v>
       </c>
     </row>
     <row r="32">
@@ -1740,7 +1740,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>NOCCIOLA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1749,10 +1749,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>8.812</v>
+        <v>2.652</v>
       </c>
     </row>
     <row r="33">
@@ -1760,7 +1760,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1769,10 +1769,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.652</v>
+        <v>4.986</v>
       </c>
     </row>
     <row r="34">
@@ -1780,7 +1780,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PERA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1789,10 +1789,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>7.465</v>
+        <v>2.160</v>
       </c>
     </row>
     <row r="35">
@@ -1800,7 +1800,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PERA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1812,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.160</v>
+        <v>2.917</v>
       </c>
     </row>
     <row r="36">
@@ -1820,7 +1820,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.917</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="37">
@@ -1840,7 +1840,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1852,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.292</v>
+        <v>2.806</v>
       </c>
     </row>
     <row r="38">
@@ -1860,7 +1860,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1869,10 +1869,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.702</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="39">
@@ -1880,7 +1880,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1889,10 +1889,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>2.806</v>
+        <v>8.617</v>
       </c>
     </row>
     <row r="40">
@@ -1900,7 +1900,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1909,10 +1909,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>3.101</v>
+        <v>5.277</v>
       </c>
     </row>
     <row r="41">
@@ -1920,7 +1920,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>STRACCIATELLA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1929,10 +1929,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>11.498</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="42">
@@ -1940,7 +1940,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>TIRAMISU'</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1949,10 +1949,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>5.277</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="43">
@@ -1960,7 +1960,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>3.055</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="44">
@@ -1980,7 +1980,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1989,10 +1989,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>3.029</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="45">
@@ -2000,7 +2000,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PENSIERO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.916</v>
+        <v>2.732</v>
       </c>
     </row>
     <row r="46">
@@ -2020,7 +2020,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -2029,10 +2029,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>5.346</v>
+        <v>3.300</v>
       </c>
     </row>
     <row r="47">
@@ -2040,7 +2040,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>5.882</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="48">
@@ -2060,7 +2060,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>MONT BLANC</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -2072,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>3.300</v>
+        <v>2.807</v>
       </c>
     </row>
     <row r="49">
@@ -2080,7 +2080,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>3.287</v>
+        <v>2.827</v>
       </c>
     </row>
     <row r="50">
@@ -2100,7 +2100,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.807</v>
+        <v>2.746</v>
       </c>
     </row>
     <row r="51">
@@ -2120,7 +2120,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -2132,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.827</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="52">
@@ -2140,7 +2140,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -2152,59 +2152,19 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.746</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B53" t="str">
-        <v>CASTAGNA AL WHISKY</v>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E53" t="str">
-        <v>1</v>
-      </c>
-      <c r="F53" t="str">
-        <v>3.169</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B54" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E54" t="str">
-        <v>1</v>
-      </c>
-      <c r="F54" t="str">
         <v>2.586</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F52"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2291,7 +2251,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2300,10 +2260,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="str">
-        <v>2.707</v>
+        <v>20.534</v>
       </c>
     </row>
     <row r="6">
@@ -2311,7 +2271,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2320,10 +2280,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>14.448</v>
+        <v>2.353</v>
       </c>
     </row>
     <row r="7">
@@ -2331,7 +2291,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2340,10 +2300,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.353</v>
+        <v>5.470</v>
       </c>
     </row>
     <row r="8">
@@ -2351,7 +2311,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2360,10 +2320,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.470</v>
+        <v>2.822</v>
       </c>
     </row>
     <row r="9">
@@ -2371,7 +2331,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2380,10 +2340,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>5.588</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="10">
@@ -2391,7 +2351,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -2400,10 +2360,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>2.565</v>
+        <v>5.110</v>
       </c>
     </row>
     <row r="11">
@@ -2411,7 +2371,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -2420,10 +2380,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>5.110</v>
+        <v>3.092</v>
       </c>
     </row>
     <row r="12">
@@ -2431,7 +2391,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -2440,10 +2400,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>6.350</v>
+        <v>3.185</v>
       </c>
     </row>
     <row r="13">
@@ -2451,7 +2411,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -2460,10 +2420,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>6.237</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="14">
@@ -2471,7 +2431,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -2480,10 +2440,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>6.210</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2451,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -2503,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>2.752</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="16">
@@ -2511,7 +2471,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -2520,10 +2480,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.222</v>
+        <v>5.999</v>
       </c>
     </row>
     <row r="17">
@@ -2531,7 +2491,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -2543,7 +2503,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>5.999</v>
+        <v>5.880</v>
       </c>
     </row>
     <row r="18">
@@ -2551,7 +2511,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -2560,10 +2520,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>2.912</v>
+        <v>5.879</v>
       </c>
     </row>
     <row r="19">
@@ -2571,7 +2531,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -2583,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>5.879</v>
+        <v>5.330</v>
       </c>
     </row>
     <row r="20">
@@ -2591,7 +2551,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -2600,10 +2560,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="str">
-        <v>5.330</v>
+        <v>7.833</v>
       </c>
     </row>
     <row r="21">
@@ -2611,7 +2571,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -2620,10 +2580,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>7.833</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="22">
@@ -2631,7 +2591,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -2643,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.403</v>
+        <v>2.705</v>
       </c>
     </row>
     <row r="23">
@@ -2651,7 +2611,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -2660,10 +2620,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>2.705</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="24">
@@ -2671,7 +2631,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -2680,10 +2640,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>2.711</v>
+        <v>7.213</v>
       </c>
     </row>
     <row r="25">
@@ -2691,7 +2651,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -2703,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>5.551</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="26">
@@ -2711,7 +2671,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -2720,10 +2680,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>4.856</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="27">
@@ -2731,7 +2691,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -2743,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.247</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="28">
@@ -2751,7 +2711,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -2760,10 +2720,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.276</v>
+        <v>4.937</v>
       </c>
     </row>
     <row r="29">
@@ -2771,7 +2731,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -2780,10 +2740,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.659</v>
+        <v>5.557</v>
       </c>
     </row>
     <row r="30">
@@ -2791,7 +2751,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -2800,10 +2760,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>5.087</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="31">
@@ -2811,7 +2771,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -2820,10 +2780,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.557</v>
+        <v>2.378</v>
       </c>
     </row>
     <row r="32">
@@ -2831,7 +2791,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -2840,10 +2800,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.935</v>
+        <v>4.634</v>
       </c>
     </row>
     <row r="33">
@@ -2851,7 +2811,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -2863,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>2.378</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="34">
@@ -2871,7 +2831,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -2880,10 +2840,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.396</v>
+        <v>5.610</v>
       </c>
     </row>
     <row r="35">
@@ -2891,7 +2851,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -2900,10 +2860,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>8.327</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="36">
@@ -2911,7 +2871,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -2923,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.977</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="37">
@@ -2931,7 +2891,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -2943,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.392</v>
+        <v>2.493</v>
       </c>
     </row>
     <row r="38">
@@ -2960,10 +2920,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="str">
-        <v>25.038</v>
+        <v>21.856</v>
       </c>
     </row>
     <row r="39">
@@ -3063,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="F43" t="str">
-        <v>16.653</v>
+        <v>16.658</v>
       </c>
     </row>
     <row r="44">
@@ -3120,10 +3080,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>5.656</v>
+        <v>2.837</v>
       </c>
     </row>
     <row r="47">
@@ -3160,10 +3120,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="str">
-        <v>5.301</v>
+        <v>8.065</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3151,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3203,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.873</v>
+        <v>750</v>
       </c>
     </row>
     <row r="51">
@@ -3211,7 +3171,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3223,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>750</v>
+        <v>3.053</v>
       </c>
     </row>
     <row r="52">
@@ -3231,7 +3191,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>MONT BLANC</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3243,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>3.053</v>
+        <v>3.275</v>
       </c>
     </row>
     <row r="53">
@@ -3251,7 +3211,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3260,10 +3220,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>6.718</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="54">
@@ -3271,7 +3231,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3280,10 +3240,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" t="str">
-        <v>2.675</v>
+        <v>2.670</v>
       </c>
     </row>
     <row r="55">
@@ -3291,7 +3251,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3303,39 +3263,19 @@
         <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>1.076</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B56" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E56" t="str">
-        <v>2</v>
-      </c>
-      <c r="F56" t="str">
         <v>5.842</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F55"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C77"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3361,7 +3301,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
@@ -3372,40 +3312,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BANANA E LIME</v>
+        <v>CACHI</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CACHI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
@@ -3416,40 +3356,40 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
@@ -3460,29 +3400,29 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -3493,62 +3433,62 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -3559,7 +3499,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -3570,7 +3510,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -3581,7 +3521,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FRAGOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
@@ -3592,7 +3532,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LEMON CURD</v>
+        <v>LIMONE</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
@@ -3603,29 +3543,29 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -3636,18 +3576,18 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MORA</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
@@ -3658,7 +3598,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MORA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
@@ -3669,7 +3609,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -3680,7 +3620,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>NOCCIOLA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
@@ -3691,18 +3631,18 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PERA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
@@ -3713,7 +3653,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PERA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
@@ -3724,84 +3664,84 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>STRACCIATELLA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C41" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>TIRAMISU'</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -3812,73 +3752,73 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PENSIERO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MONT BLANC</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -3889,62 +3829,62 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ALBICOCCA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
@@ -3955,18 +3895,18 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>BIANCANEVE</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
@@ -3977,7 +3917,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CAFFE'</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
@@ -3988,40 +3928,40 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -4032,7 +3972,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -4043,18 +3983,18 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -4065,18 +4005,18 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
@@ -4126,7 +4066,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4153,7 +4093,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -4164,18 +4104,18 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
@@ -4184,20 +4124,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C78" t="str">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C77"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -889,6 +889,9 @@
       <c r="G22" t="str">
         <v>MIRTILLO</v>
       </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1020,9 +1023,6 @@
       <c r="C29" t="str">
         <v>PISTACCHI</v>
       </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
       <c r="E29" t="str">
         <v>PICCHIE</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>PERA GORGONZOLA</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1071,9 +1071,6 @@
       <c r="A32" t="str">
         <v>STRIA</v>
       </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
       <c r="E32" t="str">
         <v>COPP. GRANDI</v>
       </c>
@@ -1100,7 +1097,7 @@
         <v>ZUCCA E SEMI</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 13-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 15-03-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -400,46 +400,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Flavor 1</v>
+        <v>Gelato</v>
       </c>
       <c r="B1" t="str">
-        <v>Qty 1</v>
+        <v>ORDINE</v>
       </c>
       <c r="C1" t="str">
-        <v>Flavor 2</v>
+        <v>Creme</v>
       </c>
       <c r="D1" t="str">
-        <v>Qty 2</v>
+        <v>ORDINE</v>
       </c>
       <c r="E1" t="str">
-        <v>Flavor 3</v>
+        <v>Cioccolati</v>
       </c>
       <c r="F1" t="str">
-        <v>Qty 3</v>
+        <v>ORDINE</v>
       </c>
       <c r="G1" t="str">
-        <v>Flavor 4</v>
+        <v>Sorbetti</v>
       </c>
       <c r="H1" t="str">
-        <v>Qty 4</v>
+        <v>ORDINE</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ARACHIDI</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="str">
-        <v>CREMA</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
@@ -459,16 +456,16 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="str">
-        <v>C. VANIGLIA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>C. LATTE</v>
+        <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -482,71 +479,68 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BAKLAVA</v>
+        <v>BASILICO NOCI E MIELE</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
       <c r="C4" t="str">
-        <v>C. FRAGOLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="str">
-        <v>C. KENTUCKY</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>AMARENA E BIRRA</v>
+        <v>ANANAS E ZENZERO</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BASILICO NOCI E MELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>C. ZENZERO</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
-        <v>C. MADAGASCAR</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="G5" t="str">
-        <v>ANANAS E ZENZ.</v>
+        <v>ANGURIA</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BIANCANEVE</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C6" t="str">
-        <v>C. CANNELLA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>C. VENEZUELA</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="G6" t="str">
-        <v>ANGURIA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -554,25 +548,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CAFFÈ</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="str">
-        <v>C. AGNESE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>C. PIMENTO</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="str">
-        <v>AVOCADO E LIME</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -580,85 +574,82 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CIOCC. BIANCO</v>
+        <v>COCCO CREMA</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>C. LEMON CURD</v>
+        <v>CREMA PASTICCIERA PARISI</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>C. LAPSANG</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>BANANA E LIME</v>
+        <v>CACHI</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>COCCO CREMA</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
+        <v>CREMA BANANA E CROCCANTE AL SESAMO</v>
       </c>
       <c r="C9" t="str">
-        <v>CHEESE MIRT</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="str">
-        <v>C. WASABY</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>CIOCCOLATO EQUADOR</v>
       </c>
       <c r="G9" t="str">
-        <v>CACHI</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>CILIEGIA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>C. BANANA</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
+        <v>FICHI ALLA GRECA</v>
       </c>
       <c r="C10" t="str">
-        <v>CARROT LAKE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10" t="str">
-        <v>C. ROSEMARY</v>
+        <v>CIOCCOLATO KENTUCKY</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>CASTAGNA</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>COCCO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FINOCCHIO</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="C11" t="str">
-        <v>TIRAMISU</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="str">
-        <v>C. PORCELLANA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
       <c r="G11" t="str">
         <v>COCCO AL RUM</v>
@@ -678,110 +669,101 @@
         <v>2</v>
       </c>
       <c r="E12" t="str">
-        <v>C. AMBOA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v>FICHI</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>ZABAIONE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="str">
-        <v>GIANDUIA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="G13" t="str">
-        <v>FRAGOLA</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MENTA CIOCC.</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
+        <v>LATTE &amp; CEREALI</v>
       </c>
       <c r="C14" t="str">
-        <v>Z. MOSCATO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="str">
-        <v>C. ARANCIA</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
+        <v>CIOCCOLATO UGANDA</v>
       </c>
       <c r="G14" t="str">
-        <v>FRAG. CALVADOS</v>
+        <v>FEIJOA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>M. BIANCA</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Z. RATAFIA</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="E15" t="str">
-        <v>C. FRUTTOSIO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
       </c>
       <c r="G15" t="str">
-        <v>FRUTTI BOSCO</v>
-      </c>
-      <c r="H15">
-        <v>3</v>
+        <v>FICHI</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>M. TOSTATA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
       </c>
       <c r="C16" t="str">
-        <v>Z. FATA</v>
+        <v>speciali</v>
       </c>
       <c r="E16" t="str">
-        <v>C. ESTASY</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>LAMPONE</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
+        <v>FICHI D INDIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>M. ARANCIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17" t="str">
-        <v>Z. ZIBIBBO</v>
+        <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
       </c>
       <c r="E17" t="str">
-        <v>N. FRUTTOSIO</v>
+        <v>ESTASI</v>
       </c>
       <c r="G17" t="str">
-        <v>LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -789,125 +771,110 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>M. CARDAMOMO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>SACHER</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>CASTAGNACCIO</v>
       </c>
       <c r="E18" t="str">
-        <v>V. GIANDUIA</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="G18" t="str">
-        <v>MANDARINO</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
-        <v>NOCCIOLATA</v>
+        <v>COTOGNATA</v>
       </c>
       <c r="E19" t="str">
-        <v>P. VEGAN</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="G19" t="str">
-        <v>MANGO</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>NOCI E UVETTA</v>
+        <v>MANDORLA E ARANCIA</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>LA-LA-</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
+        <v>CREMA COGNAC E NOCE MOSCATA</v>
       </c>
       <c r="E20" t="str">
-        <v>COPPA</v>
+        <v>GIANDUIA VARIEGATA</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>MELA N. E C.</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
+        <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PERE BH</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C21" t="str">
-        <v>STRACCHINO</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
+        <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
       </c>
       <c r="E21" t="str">
-        <v>CIALDINE</v>
+        <v>MOU LATTE SALATO</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>MELONE</v>
+        <v>HIBISCUS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>POLLICINA</v>
+        <v>MONTBLANC</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>LAVANDA</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
+        <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
       </c>
       <c r="E22" t="str">
-        <v>SUSHI GELATO</v>
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>MIRTILLO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BRONTE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C23" t="str">
-        <v>NOCE BURRO</v>
-      </c>
-      <c r="E23" t="str">
-        <v>SUSHI TIRAMISU</v>
+        <v>FIORI DI MAGNOLIA &amp; LIME</v>
       </c>
       <c r="G23" t="str">
-        <v>MORA</v>
+        <v>LIMONE</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -915,36 +882,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>RICOTTA AGRUMI</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C24" t="str">
-        <v>FIORDIFIOR</v>
+        <v>GELATO DI PANETTONE</v>
       </c>
       <c r="E24" t="str">
-        <v>SUSHI MISTI</v>
+        <v>Varie</v>
       </c>
       <c r="G24" t="str">
-        <v>PANACEA</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
+        <v>MANDARINO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>RICOTTA COCCO</v>
+        <v>NOCI E UVETTA DI CORINTO</v>
       </c>
       <c r="C25" t="str">
-        <v>PAMPANELLA</v>
+        <v>GELSI BIANCHI, SAKE' E ANACARDI SALATI</v>
       </c>
       <c r="E25" t="str">
-        <v>T.S. 6P</v>
+        <v>CAPRESE</v>
       </c>
       <c r="G25" t="str">
-        <v>PASSION</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -952,165 +913,358 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>RISO E VANIGLIA</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
+        <v>NOCI PECAN</v>
       </c>
       <c r="C26" t="str">
-        <v>TORRONE</v>
+        <v>GORGONZOLA</v>
       </c>
       <c r="E26" t="str">
-        <v>T.S. 8P</v>
+        <v>CHICCHIAINI</v>
       </c>
       <c r="G26" t="str">
-        <v>PAPAYA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C27" t="str">
-        <v>PANETTONE</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
+        <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
       </c>
       <c r="E27" t="str">
-        <v>T.G. 6P</v>
+        <v>CIALDINE</v>
       </c>
       <c r="G27" t="str">
-        <v>PENSIERO</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SEADAS</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C28" t="str">
-        <v>MONTBLANC</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
+        <v>MATE-LATE</v>
       </c>
       <c r="E28" t="str">
-        <v>T.G. 8P</v>
+        <v>CIOCCOLATA CALDA</v>
       </c>
       <c r="G28" t="str">
-        <v>PERA</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
+        <v>MELONE</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" t="str">
-        <v>PISTACCHI</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="E29" t="str">
-        <v>PICCHIE</v>
+        <v>COPPA IN CIALDA</v>
       </c>
       <c r="G29" t="str">
-        <v>PERA GORGONZOLA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>VENERE</v>
+        <v>POLLICINA</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
       </c>
       <c r="C30" t="str">
-        <v>RICE COCCO</v>
+        <v>NON TI SCORDAR DI ME</v>
       </c>
       <c r="E30" t="str">
-        <v>HUMA</v>
+        <v>COPPETTA GRANDE</v>
       </c>
       <c r="G30" t="str">
-        <v>PESCA AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>THE VERDE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="str">
-        <v>LIM/MAS</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="E31" t="str">
-        <v>COPP. PICCOLE</v>
+        <v>COPPETTA PICCOLA</v>
       </c>
       <c r="G31" t="str">
-        <v>PUNCH</v>
+        <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>STRIA</v>
+        <v>RICOTTA E FICHI ALLA GRECA</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PECORINO</v>
       </c>
       <c r="E32" t="str">
-        <v>COPP. GRANDI</v>
+        <v>MOUSSE</v>
       </c>
       <c r="G32" t="str">
-        <v>UVA NOCI</v>
+        <v>PAPAYA</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PERA AL GORGONZOLA</v>
+      </c>
       <c r="E33" t="str">
-        <v>CAPRESE</v>
+        <v>SUSHI GELATO</v>
       </c>
       <c r="G33" t="str">
-        <v>UVA FRAGOLA</v>
+        <v>PASSION FRUIT</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="str">
+        <v>RICOTTA, AMARENE &amp; NOCCIOLE PRALINATE</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PERA E PECORINO DOP</v>
+      </c>
       <c r="E34" t="str">
-        <v>C. CALDA</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
+        <v>SUSHI MISTI</v>
       </c>
       <c r="G34" t="str">
-        <v>ZUCCA E SEMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>RICOTTA, MIELE E COCCO</v>
+      </c>
+      <c r="C35" t="str">
+        <v>PESCA BIANCA AL BASILICO</v>
+      </c>
+      <c r="E35" t="str">
+        <v>SUSHI TIRAMISU</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PERA</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>RISO E VANIGLIA</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PESCA TABACCHIERA</v>
+      </c>
+      <c r="E36" t="str">
+        <v>TORTA AGNESE 6P</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PESCHE AL VINO</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SEADAS</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="str">
+        <v>POMODORO DATTERINO</v>
+      </c>
+      <c r="E37" t="str">
+        <v>TORTA AGNESE 8P</v>
+      </c>
+      <c r="G37" t="str">
+        <v>PRUGNA ROSSA, FIORI D'IBISCO</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="C38" t="str">
+        <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
+      </c>
+      <c r="E38" t="str">
+        <v>TORTA CHEESCAKE 6P</v>
+      </c>
+      <c r="G38" t="str">
+        <v>PRUGNE AL SAKE'</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ROSA KAEKADE E ARANCIA</v>
+      </c>
+      <c r="E39" t="str">
+        <v>TORTA CHEESCAKE 8P</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PUNCH PARADISE</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>STRACCIATELLA</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="str">
+        <v>STRACCIATELLA AL FIOR DI RISO</v>
+      </c>
+      <c r="E40" t="str">
+        <v>TORTA LAURA 6P</v>
+      </c>
+      <c r="G40" t="str">
+        <v>RIBES NERO</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41" t="str">
+        <v>TORRONE SALATO</v>
+      </c>
+      <c r="E41" t="str">
+        <v>TORTA LAURA 8P</v>
+      </c>
+      <c r="G41" t="str">
+        <v>UVA E NOCI</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>VENERE ROSA</v>
+      </c>
+      <c r="C42" t="str">
+        <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>TORTA TIRAMISU 6P</v>
+      </c>
+      <c r="G42" t="str">
+        <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>YOGURT</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
+      </c>
+      <c r="E43" t="str">
+        <v>TORTA TIRAMISU 8P</v>
+      </c>
+      <c r="G43" t="str">
+        <v>V. BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" t="str">
+        <v>V. CASTAGNA AL WHISKY</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" t="str">
+        <v>V. CASTAGNA E MIRTO</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" t="str">
+        <v>V. EVERGREEN BRONTE VEGAN</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" t="str">
+        <v>V. NOCCIOLA AL FRUTTOSIO</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="str">
+        <v>ZUCCA COI SUOI SEMI CARAMELLATI</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1177,7 +1331,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -1186,10 +1340,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>6.087</v>
+        <v>3.277</v>
       </c>
     </row>
     <row r="5">
@@ -1197,7 +1351,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -1206,10 +1360,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>2.466</v>
+        <v>9.098</v>
       </c>
     </row>
     <row r="6">
@@ -1217,7 +1371,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>CACHI</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -1229,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>2.022</v>
+        <v>2.466</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1391,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>CIOCCOLATO</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -1246,10 +1400,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>11.858</v>
+        <v>5.509</v>
       </c>
     </row>
     <row r="8">
@@ -1257,7 +1411,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -1266,10 +1420,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.947</v>
+        <v>5.462</v>
       </c>
     </row>
     <row r="9">
@@ -1277,7 +1431,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -1286,10 +1440,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>2.876</v>
+        <v>5.537</v>
       </c>
     </row>
     <row r="10">
@@ -1297,7 +1451,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CACHI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1309,7 +1463,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>3.057</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="11">
@@ -1317,7 +1471,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -1326,10 +1480,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="str">
-        <v>3.000</v>
+        <v>8.885</v>
       </c>
     </row>
     <row r="12">
@@ -1337,7 +1491,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -1349,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>2.775</v>
+        <v>2.947</v>
       </c>
     </row>
     <row r="13">
@@ -1357,7 +1511,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -1369,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>3.001</v>
+        <v>2.876</v>
       </c>
     </row>
     <row r="14">
@@ -1377,7 +1531,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -1389,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>2.881</v>
+        <v>3.057</v>
       </c>
     </row>
     <row r="15">
@@ -1397,7 +1551,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1409,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>2.970</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="16">
@@ -1417,7 +1571,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1426,10 +1580,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.432</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="17">
@@ -1437,7 +1591,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1449,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.616</v>
+        <v>3.001</v>
       </c>
     </row>
     <row r="18">
@@ -1457,7 +1611,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1469,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.819</v>
+        <v>2.881</v>
       </c>
     </row>
     <row r="19">
@@ -1477,7 +1631,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -1489,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.708</v>
+        <v>2.970</v>
       </c>
     </row>
     <row r="20">
@@ -1497,7 +1651,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -1506,10 +1660,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="str">
-        <v>2.764</v>
+        <v>7.933</v>
       </c>
     </row>
     <row r="21">
@@ -1517,7 +1671,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1526,10 +1680,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>5.909</v>
+        <v>2.527</v>
       </c>
     </row>
     <row r="22">
@@ -1537,7 +1691,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -1546,10 +1700,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>9.486</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="23">
@@ -1557,7 +1711,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>LEMON CURD</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -1569,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.609</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="24">
@@ -1577,7 +1731,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -1586,10 +1740,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>10.105</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="25">
@@ -1597,7 +1751,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -1609,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>2.722</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="26">
@@ -1617,7 +1771,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -1626,10 +1780,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>3.050</v>
+        <v>5.909</v>
       </c>
     </row>
     <row r="27">
@@ -1637,7 +1791,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -1646,10 +1800,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>5.229</v>
+        <v>9.486</v>
       </c>
     </row>
     <row r="28">
@@ -1657,7 +1811,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -1669,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>2.639</v>
+        <v>2.252</v>
       </c>
     </row>
     <row r="29">
@@ -1677,7 +1831,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MORA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -1689,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>2.411</v>
+        <v>2.291</v>
       </c>
     </row>
     <row r="30">
@@ -1697,7 +1851,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -1706,10 +1860,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>9.065</v>
+        <v>5.239</v>
       </c>
     </row>
     <row r="31">
@@ -1717,7 +1871,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>NOCCIOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1726,10 +1880,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>8.812</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="32">
@@ -1737,7 +1891,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1746,10 +1900,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32" t="str">
-        <v>2.652</v>
+        <v>10.105</v>
       </c>
     </row>
     <row r="33">
@@ -1757,7 +1911,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PASSION FRUIT</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1766,10 +1920,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>4.986</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="34">
@@ -1777,7 +1931,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>PERA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1789,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.160</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="35">
@@ -1797,7 +1951,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1809,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.917</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="36">
@@ -1817,7 +1971,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1829,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.841</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="37">
@@ -1837,7 +1991,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1846,10 +2000,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>2.806</v>
+        <v>5.229</v>
       </c>
     </row>
     <row r="38">
@@ -1857,7 +2011,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1869,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>3.101</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="39">
@@ -1877,7 +2031,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MORA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1886,10 +2040,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>8.617</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="40">
@@ -1897,7 +2051,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>TIRAMISU'</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1906,10 +2060,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="str">
-        <v>5.277</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="41">
@@ -1917,7 +2071,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1926,10 +2080,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" t="str">
-        <v>3.055</v>
+        <v>11.651</v>
       </c>
     </row>
     <row r="42">
@@ -1937,7 +2091,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1949,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>3.029</v>
+        <v>2.652</v>
       </c>
     </row>
     <row r="43">
@@ -1957,7 +2111,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PENSIERO</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1969,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.916</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="44">
@@ -1977,7 +2131,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1989,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>5.346</v>
+        <v>4.986</v>
       </c>
     </row>
     <row r="45">
@@ -1997,7 +2151,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -2009,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.732</v>
+        <v>2.917</v>
       </c>
     </row>
     <row r="46">
@@ -2017,7 +2171,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>MONT BLANC</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -2026,10 +2180,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>3.300</v>
+        <v>5.406</v>
       </c>
     </row>
     <row r="47">
@@ -2037,7 +2191,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -2049,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>3.287</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="48">
@@ -2057,7 +2211,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -2069,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.807</v>
+        <v>2.806</v>
       </c>
     </row>
     <row r="49">
@@ -2077,7 +2231,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -2089,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.827</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="50">
@@ -2097,7 +2251,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -2106,10 +2260,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.746</v>
+        <v>5.744</v>
       </c>
     </row>
     <row r="51">
@@ -2117,7 +2271,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -2126,10 +2280,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>3.169</v>
+        <v>5.277</v>
       </c>
     </row>
     <row r="52">
@@ -2137,7 +2291,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -2149,19 +2303,239 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.586</v>
+        <v>2.090</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B53" t="str">
+        <v>CIOCCOLATO WASABI</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E53" t="str">
+        <v>1</v>
+      </c>
+      <c r="F53" t="str">
+        <v>3.055</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B54" t="str">
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E54" t="str">
+        <v>1</v>
+      </c>
+      <c r="F54" t="str">
+        <v>3.029</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B55" t="str">
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2</v>
+      </c>
+      <c r="F55" t="str">
+        <v>5.502</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2</v>
+      </c>
+      <c r="F56" t="str">
+        <v>5.346</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B57" t="str">
+        <v>PISTACCHIO SIRIANO</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E57" t="str">
+        <v>3</v>
+      </c>
+      <c r="F57" t="str">
+        <v>8.566</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B58" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E58" t="str">
+        <v>1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>3.108</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ZABAIONE AL SAKE'</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E59" t="str">
+        <v>1</v>
+      </c>
+      <c r="F59" t="str">
+        <v>3.287</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B60" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2.807</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E61" t="str">
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2.746</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
+        <v>CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E62" t="str">
+        <v>1</v>
+      </c>
+      <c r="F62" t="str">
+        <v>3.169</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E63" t="str">
+        <v>1</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2.965</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F63"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2257,10 +2631,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="str">
-        <v>20.534</v>
+        <v>17.642</v>
       </c>
     </row>
     <row r="6">
@@ -2268,7 +2642,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2280,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>2.353</v>
+        <v>2.820</v>
       </c>
     </row>
     <row r="7">
@@ -2288,7 +2662,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2300,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>5.470</v>
+        <v>5.905</v>
       </c>
     </row>
     <row r="8">
@@ -2308,7 +2682,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2320,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.822</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="9">
@@ -2328,7 +2702,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2337,10 +2711,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>2.565</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="10">
@@ -2348,7 +2722,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -2357,10 +2731,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>5.110</v>
+        <v>3.185</v>
       </c>
     </row>
     <row r="11">
@@ -2368,7 +2742,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -2380,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>3.092</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="12">
@@ -2388,7 +2762,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -2400,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.185</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="13">
@@ -2408,7 +2782,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -2420,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.989</v>
+        <v>2.940</v>
       </c>
     </row>
     <row r="14">
@@ -2428,7 +2802,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -2437,10 +2811,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>2.752</v>
+        <v>5.880</v>
       </c>
     </row>
     <row r="15">
@@ -2448,7 +2822,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -2460,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.222</v>
+        <v>3.113</v>
       </c>
     </row>
     <row r="16">
@@ -2468,7 +2842,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -2480,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>5.999</v>
+        <v>5.172</v>
       </c>
     </row>
     <row r="17">
@@ -2488,7 +2862,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -2497,10 +2871,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>5.880</v>
+        <v>7.689</v>
       </c>
     </row>
     <row r="18">
@@ -2508,7 +2882,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -2520,7 +2894,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.879</v>
+        <v>5.020</v>
       </c>
     </row>
     <row r="19">
@@ -2528,7 +2902,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -2537,10 +2911,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>5.330</v>
+        <v>2.705</v>
       </c>
     </row>
     <row r="20">
@@ -2548,7 +2922,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -2557,10 +2931,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>7.833</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="21">
@@ -2568,7 +2942,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -2577,10 +2951,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.403</v>
+        <v>4.747</v>
       </c>
     </row>
     <row r="22">
@@ -2588,7 +2962,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -2597,10 +2971,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>2.705</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="23">
@@ -2608,7 +2982,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -2617,10 +2991,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.607</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="24">
@@ -2628,7 +3002,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -2637,10 +3011,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>7.213</v>
+        <v>4.937</v>
       </c>
     </row>
     <row r="25">
@@ -2648,7 +3022,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -2657,10 +3031,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>4.756</v>
+        <v>2.838</v>
       </c>
     </row>
     <row r="26">
@@ -2668,7 +3042,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -2680,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.276</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="27">
@@ -2688,7 +3062,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -2700,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.659</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="28">
@@ -2708,7 +3082,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMONE</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -2717,10 +3091,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>4.937</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="29">
@@ -2728,7 +3102,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -2740,7 +3114,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>5.557</v>
+        <v>5.760</v>
       </c>
     </row>
     <row r="30">
@@ -2748,7 +3122,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -2760,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.935</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="31">
@@ -2768,7 +3142,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PERA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -2780,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.378</v>
+        <v>2.377</v>
       </c>
     </row>
     <row r="32">
@@ -2788,7 +3162,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -2797,10 +3171,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>4.634</v>
+        <v>2.493</v>
       </c>
     </row>
     <row r="33">
@@ -2808,7 +3182,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MIRTILLO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -2817,10 +3191,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F33" t="str">
-        <v>2.427</v>
+        <v>19.767</v>
       </c>
     </row>
     <row r="34">
@@ -2828,7 +3202,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>NOCCIOLA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -2837,10 +3211,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.610</v>
+        <v>3.139</v>
       </c>
     </row>
     <row r="35">
@@ -2848,7 +3222,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -2860,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.977</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="36">
@@ -2868,7 +3242,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -2877,10 +3251,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F36" t="str">
-        <v>2.392</v>
+        <v>13.858</v>
       </c>
     </row>
     <row r="37">
@@ -2888,7 +3262,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -2897,10 +3271,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>2.493</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="38">
@@ -2908,7 +3282,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -2917,10 +3291,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>21.856</v>
+        <v>2.837</v>
       </c>
     </row>
     <row r="39">
@@ -2928,7 +3302,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>POLLICINA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -2940,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>3.137</v>
+        <v>3.107</v>
       </c>
     </row>
     <row r="40">
@@ -2948,7 +3322,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -2957,10 +3331,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>3.139</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="41">
@@ -2968,7 +3342,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -2980,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>2.809</v>
+        <v>2.521</v>
       </c>
     </row>
     <row r="42">
@@ -2988,7 +3362,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>SEADAS</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3000,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.879</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43">
@@ -3008,7 +3382,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3017,10 +3391,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>16.658</v>
+        <v>3.327</v>
       </c>
     </row>
     <row r="44">
@@ -3028,7 +3402,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>YOGURT</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3040,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.927</v>
+        <v>1.001</v>
       </c>
     </row>
     <row r="45">
@@ -3048,7 +3422,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3057,10 +3431,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>3.052</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="46">
@@ -3068,7 +3442,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3080,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.837</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="47">
@@ -3088,7 +3462,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SACRIPANTE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3097,10 +3471,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F47" t="str">
-        <v>3.107</v>
+        <v>3.717</v>
       </c>
     </row>
     <row r="48">
@@ -3108,7 +3482,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3117,162 +3491,22 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>8.065</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B49" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E49" t="str">
-        <v>1</v>
-      </c>
-      <c r="F49" t="str">
-        <v>1.017</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B50" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E50" t="str">
-        <v>1</v>
-      </c>
-      <c r="F50" t="str">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B51" t="str">
-        <v>MONT BLANC</v>
-      </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="D51" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E51" t="str">
-        <v>1</v>
-      </c>
-      <c r="F51" t="str">
-        <v>3.053</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B52" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E52" t="str">
-        <v>1</v>
-      </c>
-      <c r="F52" t="str">
-        <v>3.275</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B53" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E53" t="str">
-        <v>1</v>
-      </c>
-      <c r="F53" t="str">
-        <v>2.675</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B54" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E54" t="str">
-        <v>5</v>
-      </c>
-      <c r="F54" t="str">
-        <v>2.670</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B55" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E55" t="str">
-        <v>2</v>
-      </c>
-      <c r="F55" t="str">
         <v>5.842</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3309,29 +3543,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CACHI</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
@@ -3342,7 +3576,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CIOCCOLATO</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
@@ -3353,7 +3587,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
@@ -3364,7 +3598,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
@@ -3375,117 +3609,117 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CACHI</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -3496,18 +3730,18 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -3518,18 +3752,18 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>LEMON CURD</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
@@ -3540,29 +3774,29 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -3573,7 +3807,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
@@ -3584,18 +3818,18 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MORA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
@@ -3606,7 +3840,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>NOCCIOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -3617,18 +3851,18 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>LIMONE</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>PASSION FRUIT</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -3639,51 +3873,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>PERA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -3694,18 +3928,18 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MORA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TIRAMISU'</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
@@ -3716,7 +3950,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -3727,18 +3961,18 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PENSIERO</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -3749,7 +3983,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -3760,29 +3994,29 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MONT BLANC</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -3793,40 +4027,40 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
@@ -3837,128 +4071,128 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ALBICOCCA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>BIANCANEVE</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>CAFFE'</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>CREMA AGNESE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -3969,7 +4203,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -3980,18 +4214,18 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>MIRTILLO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -4002,7 +4236,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
@@ -4013,18 +4247,18 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>POLLICINA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
@@ -4035,7 +4269,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SEADAS</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
@@ -4046,7 +4280,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YOGURT</v>
+        <v>PERA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
@@ -4057,7 +4291,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
@@ -4068,7 +4302,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SACRIPANTE</v>
+        <v>SEADAS</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
@@ -4079,18 +4313,18 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -4101,29 +4335,84 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TORTA CAPRESE</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C80" t="str">
         <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C82" t="str">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C82"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -400,31 +400,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:P48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Gelato</v>
       </c>
       <c r="B1" t="str">
-        <v>ORDINE</v>
+        <v>ESAURITO</v>
       </c>
       <c r="C1" t="str">
-        <v>Creme</v>
+        <v>MANTENIMENTO</v>
       </c>
       <c r="D1" t="str">
         <v>ORDINE</v>
       </c>
       <c r="E1" t="str">
+        <v>Creme</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="G1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="H1" t="str">
+        <v>ORDINE</v>
+      </c>
+      <c r="I1" t="str">
         <v>Cioccolati</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="L1" t="str">
         <v>ORDINE</v>
       </c>
-      <c r="G1" t="str">
+      <c r="M1" t="str">
         <v>Sorbetti</v>
       </c>
-      <c r="H1" t="str">
+      <c r="N1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="O1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="P1" t="str">
         <v>ORDINE</v>
       </c>
     </row>
@@ -432,74 +456,149 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="str">
         <v>CIOCCOLATO</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3">
-        <v>4</v>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="E3" t="str">
+      <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4">
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4">
         <v>2</v>
       </c>
     </row>
@@ -507,359 +606,899 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
       </c>
-      <c r="G5" t="str">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
       <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
       </c>
-      <c r="G6" t="str">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6">
-        <v>0</v>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>0</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7">
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="G7" t="str">
+      <c r="M7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>0</v>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="str">
         <v>CACHI</v>
       </c>
-      <c r="H8">
-        <v>0</v>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>CREMA BANANA E CROCCANTE AL SESAMO</v>
       </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
       <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
       </c>
-      <c r="G9" t="str">
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>CILIEGIA</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>FICHI ALLA GRECA</v>
       </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
       <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="str">
         <v>COCCO</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
       <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>COCCO AL RUM</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" t="str">
+        <v/>
       </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12">
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="E12" t="str">
+      <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13">
-        <v>0</v>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
       </c>
-      <c r="G13" t="str">
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>LATTE &amp; CEREALI</v>
       </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
       <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
         <v>ZABAIONE GELATO</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
       </c>
-      <c r="G14" t="str">
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>FEIJOA</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15" t="str">
         <v>FICHI</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="str">
+        <v/>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
         <v>speciali</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>FICHI D INDIA</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="str">
+        <v/>
       </c>
       <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="G17" t="str">
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17" t="str">
         <v>FRAGOLA</v>
       </c>
-      <c r="H17">
-        <v>0</v>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="str">
+        <v/>
       </c>
       <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="G18" t="str">
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19">
-        <v>1</v>
+      <c r="B19" t="str">
+        <v/>
       </c>
       <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
         <v>COTOGNATA</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="G19" t="str">
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20">
-        <v>0</v>
+      <c r="B20" t="str">
+        <v/>
       </c>
       <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
       <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>HIBISCUS</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>MONTBLANC</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22">
         <v>2</v>
       </c>
-      <c r="C22" t="str">
+      <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
       </c>
-      <c r="E22" t="str">
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>SACHER TORTE</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22">
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22">
         <v>1</v>
       </c>
     </row>
@@ -867,64 +1506,199 @@
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23">
-        <v>0</v>
+      <c r="B23" t="str">
+        <v/>
       </c>
       <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
       </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
       <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H23">
-        <v>0</v>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
       <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
       </c>
-      <c r="E24" t="str">
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>Varie</v>
       </c>
-      <c r="G24" t="str">
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
         <v>MANDARINO</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>NOCI E UVETTA DI CORINTO</v>
       </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
       <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
         <v>GELSI BIANCHI, SAKE' E ANACARDI SALATI</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>CAPRESE</v>
       </c>
-      <c r="G25" t="str">
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>0</v>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v>NOCI PECAN</v>
       </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
       <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
         <v>GORGONZOLA</v>
       </c>
-      <c r="E26" t="str">
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
         <v>CHICCHIAINI</v>
       </c>
-      <c r="G26" t="str">
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26">
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26">
         <v>1</v>
       </c>
     </row>
@@ -932,53 +1706,149 @@
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27">
-        <v>0</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
       <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
       </c>
-      <c r="E27" t="str">
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
         <v>CIALDINE</v>
       </c>
-      <c r="G27" t="str">
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
         <v>MELOGRANO WONDERFUL</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28">
-        <v>7</v>
+      <c r="B28" t="str">
+        <v/>
       </c>
       <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="str">
         <v>MATE-LATE</v>
       </c>
-      <c r="E28" t="str">
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>CIOCCOLATA CALDA</v>
       </c>
-      <c r="G28" t="str">
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
         <v>MELONE</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29">
-        <v>0</v>
+      <c r="B29" t="str">
+        <v/>
       </c>
       <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
       </c>
-      <c r="E29" t="str">
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <v>COPPA IN CIALDA</v>
       </c>
-      <c r="G29" t="str">
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29">
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29">
         <v>2</v>
       </c>
     </row>
@@ -986,110 +1856,299 @@
       <c r="A30" t="str">
         <v>POLLICINA</v>
       </c>
-      <c r="B30">
-        <v>0</v>
+      <c r="B30" t="str">
+        <v/>
       </c>
       <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
       </c>
-      <c r="E30" t="str">
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
         <v>COPPETTA GRANDE</v>
       </c>
-      <c r="G30" t="str">
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30">
-        <v>0</v>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31">
-        <v>1</v>
+      <c r="B31" t="str">
+        <v/>
       </c>
       <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
       </c>
-      <c r="E31" t="str">
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
         <v>COPPETTA PICCOLA</v>
       </c>
-      <c r="G31" t="str">
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>0</v>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v>RICOTTA E FICHI ALLA GRECA</v>
       </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
       <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
         <v>PECORINO</v>
       </c>
-      <c r="E32" t="str">
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
         <v>MOUSSE</v>
       </c>
-      <c r="G32" t="str">
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32">
-        <v>0</v>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33">
-        <v>0</v>
+      <c r="B33" t="str">
+        <v/>
       </c>
       <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
         <v>SUSHI GELATO</v>
       </c>
-      <c r="G33" t="str">
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33">
-        <v>0</v>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v>RICOTTA, AMARENE &amp; NOCCIOLE PRALINATE</v>
       </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
       <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
         <v>PERA E PECORINO DOP</v>
       </c>
-      <c r="E34" t="str">
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
         <v>SUSHI MISTI</v>
       </c>
-      <c r="G34" t="str">
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34">
-        <v>0</v>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
       <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
       </c>
-      <c r="E35" t="str">
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
         <v>SUSHI TIRAMISU</v>
       </c>
-      <c r="G35" t="str">
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
         <v>PERA</v>
       </c>
-      <c r="H35">
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35">
         <v>2</v>
       </c>
     </row>
@@ -1097,19 +2156,49 @@
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36">
-        <v>0</v>
+      <c r="B36" t="str">
+        <v/>
       </c>
       <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
         <v>TORTA AGNESE 6P</v>
       </c>
-      <c r="G36" t="str">
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36">
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36">
         <v>2</v>
       </c>
     </row>
@@ -1117,147 +2206,605 @@
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37">
         <v>2</v>
       </c>
-      <c r="C37" t="str">
+      <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
       </c>
-      <c r="E37" t="str">
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
         <v>TORTA AGNESE 8P</v>
       </c>
-      <c r="G37" t="str">
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
         <v>PRUGNA ROSSA, FIORI D'IBISCO</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
       <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
       </c>
-      <c r="E38" t="str">
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
         <v>TORTA CHEESCAKE 6P</v>
       </c>
-      <c r="G38" t="str">
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
         <v>PRUGNE AL SAKE'</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
-      <c r="B39">
-        <v>2</v>
+      <c r="B39" t="str">
+        <v/>
       </c>
       <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
       </c>
-      <c r="E39" t="str">
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
         <v>TORTA CHEESCAKE 8P</v>
       </c>
-      <c r="G39" t="str">
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
         <v>PUNCH PARADISE</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>STRACCIATELLA</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40">
         <v>4</v>
       </c>
-      <c r="C40" t="str">
+      <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
       </c>
-      <c r="E40" t="str">
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
         <v>TORTA LAURA 6P</v>
       </c>
-      <c r="G40" t="str">
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
         <v>RIBES NERO</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41">
-        <v>0</v>
+      <c r="B41" t="str">
+        <v/>
       </c>
       <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
         <v>TORRONE SALATO</v>
       </c>
-      <c r="E41" t="str">
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
         <v>TORTA LAURA 8P</v>
       </c>
-      <c r="G41" t="str">
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
         <v>UVA E NOCI</v>
       </c>
-      <c r="H41">
-        <v>0</v>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v>VENERE ROSA</v>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
       <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
       </c>
-      <c r="E42" t="str">
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
         <v>TORTA TIRAMISU 6P</v>
       </c>
-      <c r="G42" t="str">
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
         <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43">
-        <v>3</v>
+      <c r="B43" t="str">
+        <v/>
       </c>
       <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
       </c>
-      <c r="E43" t="str">
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
         <v>TORTA TIRAMISU 8P</v>
       </c>
-      <c r="G43" t="str">
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
         <v>V. BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
       <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
         <v>V. CASTAGNA AL WHISKY</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
       <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
         <v>V. CASTAGNA E MIRTO</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
       <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
         <v>V. EVERGREEN BRONTE VEGAN</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
       <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
         <v>V. NOCCIOLA AL FRUTTOSIO</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
       <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
         <v>ZUCCA COI SUOI SEMI CARAMELLATI</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3506,7 +5053,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3527,7 +5074,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3560,7 +5107,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3626,7 +5173,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3659,7 +5206,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3703,7 +5250,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3736,7 +5283,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3791,7 +5338,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3890,7 +5437,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4000,7 +5547,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4011,7 +5558,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -4033,7 +5580,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4044,7 +5591,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4099,7 +5646,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4132,7 +5679,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -4198,7 +5745,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4209,7 +5756,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4253,7 +5800,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4319,7 +5866,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4341,7 +5888,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4352,7 +5899,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4385,7 +5932,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -4396,7 +5943,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4407,12 +5954,210 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>9</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>PENSIERO</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C83" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>CIOCCOLATA CALDA FONDENTE</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C84" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>BAKLAVA</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C85" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>CASTAGNA E MIRTO</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C86" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>ESTASI</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C87" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>FICHI</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C88" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>RICOTTA, MIELE E COCCO</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C89" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C90" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>CARROT CAKE</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C91" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C92" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>GIANDUIA</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C93" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>BUONGIORNO AMORE</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C94" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C95" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C96" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>CASTAGNACCIO</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C97" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TORRONE SALATO</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C98" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>MANDARINO</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C99" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>GELATO DI PANETTONE</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C100" t="str">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 15-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 22-03-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -498,8 +498,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2">
-        <v>1</v>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -548,8 +548,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -562,8 +562,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>3</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -662,8 +662,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -698,8 +698,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
-        <v/>
+      <c r="P6">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -737,7 +737,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>1</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -774,8 +774,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -786,8 +786,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>1</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -798,8 +798,8 @@
       <c r="O8" t="str">
         <v/>
       </c>
-      <c r="P8" t="str">
-        <v/>
+      <c r="P8">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -824,8 +824,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -874,8 +874,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>2</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -912,8 +912,8 @@
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="str">
         <v>LEMON CURD</v>
@@ -962,8 +962,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>2</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>2</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -1212,8 +1212,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="D17">
+        <v>2</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>1</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1248,8 +1248,8 @@
       <c r="O17" t="str">
         <v/>
       </c>
-      <c r="P17" t="str">
-        <v/>
+      <c r="P17">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1312,8 +1312,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="D19">
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1362,8 +1362,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1436,8 +1436,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21" t="str">
-        <v/>
+      <c r="L21">
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1462,8 +1462,8 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22">
-        <v>2</v>
+      <c r="D22" t="str">
+        <v/>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1498,8 +1498,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>1</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1512,8 +1512,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1548,8 +1548,8 @@
       <c r="O23" t="str">
         <v/>
       </c>
-      <c r="P23" t="str">
-        <v/>
+      <c r="P23">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1598,8 +1598,8 @@
       <c r="O24" t="str">
         <v/>
       </c>
-      <c r="P24">
-        <v>1</v>
+      <c r="P24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1712,8 +1712,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>1</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1848,8 +1848,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>2</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1898,8 +1898,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2012,8 +2012,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2098,8 +2098,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34">
-        <v>1</v>
+      <c r="P34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2162,8 +2162,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36">
-        <v>1</v>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2198,8 +2198,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>2</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2212,8 +2212,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>2</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2312,8 +2312,8 @@
       <c r="C39" t="str">
         <v/>
       </c>
-      <c r="D39">
-        <v>1</v>
+      <c r="D39" t="str">
+        <v/>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2412,8 +2412,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="D41">
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2513,7 +2513,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>1.817</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>8.688</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2890,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>3.277</v>
+        <v>2.635</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>9.098</v>
+        <v>3.277</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="str">
-        <v>2.466</v>
+        <v>11.857</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +2938,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.509</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.462</v>
+        <v>2.872</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>5.537</v>
+        <v>2.663</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CACHI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.022</v>
+        <v>2.761</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3030,7 +3030,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="str">
-        <v>8.885</v>
+        <v>7.296</v>
       </c>
     </row>
     <row r="12">
@@ -3050,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>2.947</v>
+        <v>2.936</v>
       </c>
     </row>
     <row r="13">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.057</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>3.000</v>
+        <v>5.791</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3130,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>2.775</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3150,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>3.001</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.881</v>
+        <v>3.042</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.970</v>
+        <v>2.957</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>7.933</v>
+        <v>5.762</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3230,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.527</v>
+        <v>2.605</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>2.616</v>
+        <v>7.784</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3270,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.819</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3290,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.708</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>2.764</v>
+        <v>5.531</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FIORDILATTE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>5.909</v>
+        <v>6.202</v>
       </c>
     </row>
     <row r="27">
@@ -3347,10 +3347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>9.486</v>
+        <v>2.745</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.252</v>
+        <v>4.300</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.291</v>
+        <v>5.239</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>5.239</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.609</v>
+        <v>2.691</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LIMONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>10.105</v>
+        <v>2.620</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.752</v>
+        <v>4.995</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>PERA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.846</v>
+        <v>2.789</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.722</v>
+        <v>2.728</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3527,10 +3527,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>3.050</v>
+        <v>4.712</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>5.229</v>
+        <v>8.485</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.639</v>
+        <v>5.606</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MORA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.411</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>9.065</v>
+        <v>5.610</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>11.651</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>SEADAS</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>2.652</v>
+        <v>5.821</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PAPAYA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3670,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.624</v>
+        <v>2.833</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3690,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>4.986</v>
+        <v>4.387</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3710,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.917</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>5.406</v>
+        <v>2.760</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>POLLICINA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>2.736</v>
+        <v>5.502</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.806</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>3.101</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>STRACCIATELLA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.744</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>5.277</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.090</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3870,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>3.055</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>3.029</v>
+        <v>6.192</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>5.502</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.346</v>
+        <v>2.779</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>8.566</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>3.108</v>
+        <v>8.578</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>3.287</v>
+        <v>5.708</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4010,79 +4010,19 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.807</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B61" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E61" t="str">
-        <v>1</v>
-      </c>
-      <c r="F61" t="str">
-        <v>2.746</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B62" t="str">
-        <v>CASTAGNA AL WHISKY</v>
-      </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E62" t="str">
-        <v>1</v>
-      </c>
-      <c r="F62" t="str">
-        <v>3.169</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B63" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="D63" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E63" t="str">
-        <v>1</v>
-      </c>
-      <c r="F63" t="str">
-        <v>2.965</v>
+        <v>2.851</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4109,7 +4049,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -4121,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>1.608</v>
+        <v>1.817</v>
       </c>
     </row>
     <row r="3">
@@ -4129,7 +4069,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -4141,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.208</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="4">
@@ -4149,7 +4089,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4161,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>2.160</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="5">
@@ -4169,7 +4109,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4178,10 +4118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>17.642</v>
+        <v>5.731</v>
       </c>
     </row>
     <row r="6">
@@ -4189,7 +4129,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4198,10 +4138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="str">
-        <v>2.820</v>
+        <v>15.057</v>
       </c>
     </row>
     <row r="7">
@@ -4209,7 +4149,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4218,10 +4158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.905</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="8">
@@ -4229,7 +4169,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4238,10 +4178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.542</v>
+        <v>4.584</v>
       </c>
     </row>
     <row r="9">
@@ -4249,7 +4189,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4261,7 +4201,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>6.333</v>
+        <v>5.455</v>
       </c>
     </row>
     <row r="10">
@@ -4269,7 +4209,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CACHI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4281,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>3.185</v>
+        <v>2.110</v>
       </c>
     </row>
     <row r="11">
@@ -4289,7 +4229,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4301,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.989</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="12">
@@ -4309,7 +4249,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4318,10 +4258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>3.222</v>
+        <v>9.002</v>
       </c>
     </row>
     <row r="13">
@@ -4329,7 +4269,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4338,10 +4278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>2.940</v>
+        <v>6.040</v>
       </c>
     </row>
     <row r="14">
@@ -4349,7 +4289,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4358,10 +4298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>5.880</v>
+        <v>3.037</v>
       </c>
     </row>
     <row r="15">
@@ -4369,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4381,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.113</v>
+        <v>3.057</v>
       </c>
     </row>
     <row r="16">
@@ -4389,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4398,10 +4338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.172</v>
+        <v>3.054</v>
       </c>
     </row>
     <row r="17">
@@ -4409,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4418,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>7.689</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="18">
@@ -4429,7 +4369,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4441,7 +4381,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.020</v>
+        <v>5.762</v>
       </c>
     </row>
     <row r="19">
@@ -4449,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4458,10 +4398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.705</v>
+        <v>6.135</v>
       </c>
     </row>
     <row r="20">
@@ -4469,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4478,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>5.607</v>
+        <v>2.741</v>
       </c>
     </row>
     <row r="21">
@@ -4489,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4498,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>4.747</v>
+        <v>2.613</v>
       </c>
     </row>
     <row r="22">
@@ -4509,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4518,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>4.756</v>
+        <v>2.629</v>
       </c>
     </row>
     <row r="23">
@@ -4529,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4541,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.276</v>
+        <v>3.230</v>
       </c>
     </row>
     <row r="24">
@@ -4549,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LIMONE</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4558,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>4.937</v>
+        <v>3.041</v>
       </c>
     </row>
     <row r="25">
@@ -4569,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4578,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>2.838</v>
+        <v>8.614</v>
       </c>
     </row>
     <row r="26">
@@ -4589,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4598,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="str">
-        <v>2.935</v>
+        <v>8.846</v>
       </c>
     </row>
     <row r="27">
@@ -4609,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4621,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.238</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="28">
@@ -4629,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MIRTILLO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4638,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>2.427</v>
+        <v>7.292</v>
       </c>
     </row>
     <row r="29">
@@ -4649,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>NOCCIOLA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4658,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.760</v>
+        <v>2.687</v>
       </c>
     </row>
     <row r="30">
@@ -4669,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4681,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.977</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="31">
@@ -4689,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>PERA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4701,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.377</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="32">
@@ -4709,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4721,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.493</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="33">
@@ -4729,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4738,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>19.767</v>
+        <v>5.229</v>
       </c>
     </row>
     <row r="34">
@@ -4749,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4761,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>3.139</v>
+        <v>2.686</v>
       </c>
     </row>
     <row r="35">
@@ -4769,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>SEADAS</v>
+        <v>MORA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4781,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.879</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="36">
@@ -4789,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4798,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>13.858</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="37">
@@ -4809,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4818,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="str">
-        <v>5.688</v>
+        <v>11.708</v>
       </c>
     </row>
     <row r="38">
@@ -4829,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4838,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>2.837</v>
+        <v>9.763</v>
       </c>
     </row>
     <row r="39">
@@ -4849,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>SACRIPANTE</v>
+        <v>PERA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -4861,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>3.107</v>
+        <v>2.160</v>
       </c>
     </row>
     <row r="40">
@@ -4869,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -4878,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.376</v>
+        <v>2.292</v>
       </c>
     </row>
     <row r="41">
@@ -4889,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -4898,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
-        <v>2.521</v>
+        <v>13.814</v>
       </c>
     </row>
     <row r="42">
@@ -4909,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -4921,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>750</v>
+        <v>2.700</v>
       </c>
     </row>
     <row r="43">
@@ -4929,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>MONT BLANC</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -4938,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>3.327</v>
+        <v>5.710</v>
       </c>
     </row>
     <row r="44">
@@ -4949,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -4961,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>1.001</v>
+        <v>3.080</v>
       </c>
     </row>
     <row r="45">
@@ -4969,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -4978,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F45" t="str">
-        <v>6.708</v>
+        <v>19.859</v>
       </c>
     </row>
     <row r="46">
@@ -4989,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5001,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.675</v>
+        <v>2.585</v>
       </c>
     </row>
     <row r="47">
@@ -5009,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5018,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>3.717</v>
+        <v>2.629</v>
       </c>
     </row>
     <row r="48">
@@ -5029,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5038,22 +4978,302 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
+        <v>1</v>
+      </c>
+      <c r="F48" t="str">
+        <v>3.315</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B49" t="str">
+        <v>SACRIPANTE</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E49" t="str">
+        <v>1</v>
+      </c>
+      <c r="F49" t="str">
+        <v>3.151</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B50" t="str">
+        <v>BUONGIORNO AMORE</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E50" t="str">
+        <v>1</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2.591</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E51" t="str">
         <v>2</v>
       </c>
-      <c r="F48" t="str">
-        <v>5.842</v>
+      <c r="F51" t="str">
+        <v>5.346</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B52" t="str">
+        <v>CARROT CAKE</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E52" t="str">
+        <v>1</v>
+      </c>
+      <c r="F52" t="str">
+        <v>2.680</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B53" t="str">
+        <v>PISTACCHIO SIRIANO</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E53" t="str">
+        <v>4</v>
+      </c>
+      <c r="F53" t="str">
+        <v>11.924</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B54" t="str">
+        <v>FIOR DI CIOCCOLATO</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E54" t="str">
+        <v>1</v>
+      </c>
+      <c r="F54" t="str">
+        <v>2.771</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B55" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E55" t="str">
+        <v>1</v>
+      </c>
+      <c r="F55" t="str">
+        <v>3.038</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B56" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E56" t="str">
+        <v>1</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3.300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B57" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E57" t="str">
+        <v>1</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2.807</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B58" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E58" t="str">
+        <v>1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2.827</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B59" t="str">
+        <v>CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E59" t="str">
+        <v>1</v>
+      </c>
+      <c r="F59" t="str">
+        <v>2.047</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B60" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2.586</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E61" t="str">
+        <v>3</v>
+      </c>
+      <c r="F61" t="str">
+        <v>1.556</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E62" t="str">
+        <v>1</v>
+      </c>
+      <c r="F62" t="str">
+        <v>3.083</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F62"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5068,7 +5288,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AMARENA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
@@ -5079,62 +5299,62 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>AMARENA</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
@@ -5145,18 +5365,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CACHI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
@@ -5167,13 +5387,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5200,7 +5420,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5211,40 +5431,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5255,7 +5475,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
@@ -5266,7 +5486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -5277,7 +5497,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -5288,7 +5508,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -5299,7 +5519,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
@@ -5310,7 +5530,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
@@ -5321,7 +5541,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
@@ -5332,7 +5552,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FIORDILATTE</v>
+        <v>ESTASI</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
@@ -5349,34 +5569,34 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C27" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
@@ -5387,29 +5607,29 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LIMONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -5420,7 +5640,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>PERA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
@@ -5431,7 +5651,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
@@ -5442,7 +5662,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
@@ -5453,29 +5673,29 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MORA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
@@ -5486,7 +5706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
@@ -5497,7 +5717,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NOCCIOLA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -5508,7 +5728,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>SEADAS</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -5519,18 +5739,18 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PAPAYA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -5541,29 +5761,29 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>POLLICINA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -5574,7 +5794,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -5585,40 +5805,40 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>STRACCIATELLA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
@@ -5629,29 +5849,29 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
@@ -5662,7 +5882,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
@@ -5673,18 +5893,18 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
@@ -5695,7 +5915,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
@@ -5706,7 +5926,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
@@ -5717,29 +5937,29 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SACHER TORTE</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -5750,7 +5970,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ALBICOCCA</v>
+        <v>CACHI</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -5761,18 +5981,18 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -5783,18 +6003,18 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
@@ -5805,29 +6025,29 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>MIRTILLO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>LIMONE</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PERA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
@@ -5838,7 +6058,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
@@ -5849,40 +6069,40 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SEADAS</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>YOGURT</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SACRIPANTE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>MORA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
@@ -5893,40 +6113,40 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>MONT BLANC</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
@@ -5937,40 +6157,40 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PENSIERO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
@@ -5981,18 +6201,18 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>BAKLAVA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6003,40 +6223,40 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ESTASI</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>FICHI</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C88" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6047,7 +6267,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>CARROT CAKE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
@@ -6058,18 +6278,18 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>GIANDUIA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
@@ -6080,7 +6300,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6091,7 +6311,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
@@ -6102,7 +6322,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6113,29 +6333,29 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>CASTAGNACCIO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TORRONE SALATO</v>
+        <v>FICHI</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C98" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>MANDARINO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6146,18 +6366,73 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>GELATO DI PANETTONE</v>
+        <v>UVA FRAGOLA E ZENZERO</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C100" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C101" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C102" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C103" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>CASTAGNACCIO</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C104" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TORRONE SALATO</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C105" t="str">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 22-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 29-03-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -463,7 +463,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -498,8 +498,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2" t="str">
-        <v/>
+      <c r="P2">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -537,7 +537,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -548,8 +548,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3">
-        <v>1</v>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -598,8 +598,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4">
-        <v>1</v>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>1</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -674,8 +674,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -698,8 +698,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6">
-        <v>2</v>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -736,8 +736,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="L7" t="str">
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>1</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -824,8 +824,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9">
-        <v>1</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -874,8 +874,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10">
-        <v>2</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -962,8 +962,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12">
-        <v>3</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -986,8 +986,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12">
-        <v>1</v>
+      <c r="L12" t="str">
+        <v/>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>2</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1162,8 +1162,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="D16">
+        <v>2</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1212,8 +1212,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>2</v>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>2</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1362,8 +1362,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20">
-        <v>1</v>
+      <c r="D20" t="str">
+        <v/>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>1</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1498,8 +1498,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22" t="str">
-        <v/>
+      <c r="P22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1512,8 +1512,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23">
-        <v>4</v>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>3</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1698,8 +1698,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26">
-        <v>1</v>
+      <c r="P26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1712,8 +1712,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="D27">
+        <v>2</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1848,8 +1848,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29" t="str">
-        <v/>
+      <c r="P29">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1862,8 +1862,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="D30">
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1912,8 +1912,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="D31">
+        <v>1</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1998,8 +1998,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32" t="str">
-        <v/>
+      <c r="P32">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2012,8 +2012,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33">
-        <v>1</v>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2198,8 +2198,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36" t="str">
-        <v/>
+      <c r="P36">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.505</v>
+        <v>4.734</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2.403</v>
+        <v>7.418</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2890,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>2.635</v>
+        <v>2.710</v>
       </c>
     </row>
     <row r="5">
@@ -2910,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>3.277</v>
+        <v>3.514</v>
       </c>
     </row>
     <row r="6">
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>11.857</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="7">
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.254</v>
+        <v>4.545</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.872</v>
+        <v>3.058</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2990,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>2.663</v>
+        <v>2.796</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.761</v>
+        <v>2.406</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>7.296</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>2.936</v>
+        <v>5.791</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>2.876</v>
+        <v>5.992</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>2.929</v>
+        <v>5.939</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3110,7 +3110,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>5.791</v>
+        <v>5.831</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.000</v>
+        <v>5.165</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>2.775</v>
+        <v>5.340</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>3.042</v>
+        <v>2.700</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.957</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>5.762</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.605</v>
+        <v>5.462</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3250,7 +3250,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>7.784</v>
+        <v>8.703</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3270,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.626</v>
+        <v>2.324</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3290,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.616</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>5.531</v>
+        <v>2.291</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>6.202</v>
+        <v>2.825</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.745</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>4.300</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDARINO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.239</v>
+        <v>2.524</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.609</v>
+        <v>2.796</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.691</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.620</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MIRTILLO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>4.995</v>
+        <v>5.424</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>PERA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" t="str">
-        <v>2.789</v>
+        <v>7.354</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.728</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3527,10 +3527,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>4.712</v>
+        <v>3.100</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="str">
-        <v>8.485</v>
+        <v>12.033</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>POLLICINA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.606</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PERA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.258</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.610</v>
+        <v>2.963</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3630,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>2.659</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>SEADAS</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>5.821</v>
+        <v>2.809</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3670,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.833</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>UVA E NOCI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3690,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>4.387</v>
+        <v>5.642</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>SEADAS</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>3.055</v>
+        <v>5.952</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>2.760</v>
+        <v>5.589</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3750,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>5.502</v>
+        <v>5.601</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PENSIERO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.461</v>
+        <v>2.090</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>SACRIPANTE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>6.207</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.548</v>
+        <v>2.972</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.982</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3847,10 +3847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.765</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.821</v>
+        <v>5.385</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>MONT BLANC</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>6.192</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="str">
-        <v>3.287</v>
+        <v>8.781</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>SACHER TORTE</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>2.779</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3950,7 +3950,7 @@
         <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>5.616</v>
+        <v>6.064</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58" t="str">
-        <v>8.578</v>
+        <v>15.337</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>5.708</v>
+        <v>3.128</v>
       </c>
     </row>
     <row r="60">
@@ -3998,24 +3998,184 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
+        <v>ZABAIONE AL SAKE'</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>3.287</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E61" t="str">
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <v>3.163</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2</v>
+      </c>
+      <c r="F62" t="str">
+        <v>6.619</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E63" t="str">
+        <v>1</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2.744</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B64" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E64" t="str">
+        <v>3</v>
+      </c>
+      <c r="F64" t="str">
+        <v>8.412</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B65" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2</v>
+      </c>
+      <c r="F65" t="str">
+        <v>6.327</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B66" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5.792</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B67" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E67" t="str">
+        <v>6</v>
+      </c>
+      <c r="F67" t="str">
+        <v>17.007</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B68" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E60" t="str">
-        <v>1</v>
-      </c>
-      <c r="F60" t="str">
-        <v>2.851</v>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5.614</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F68"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4049,7 +4209,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -4061,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>1.817</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="3">
@@ -4081,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.398</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="4">
@@ -4089,7 +4249,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4098,10 +4258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2.898</v>
+        <v>5.702</v>
       </c>
     </row>
     <row r="5">
@@ -4109,7 +4269,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4118,10 +4278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>5.731</v>
+        <v>26.847</v>
       </c>
     </row>
     <row r="6">
@@ -4129,7 +4289,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4138,10 +4298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>15.057</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="7">
@@ -4149,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BAKLAVA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4158,10 +4318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>3.018</v>
+        <v>5.509</v>
       </c>
     </row>
     <row r="8">
@@ -4169,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4181,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>4.584</v>
+        <v>5.443</v>
       </c>
     </row>
     <row r="9">
@@ -4189,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4201,7 +4361,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>5.455</v>
+        <v>5.537</v>
       </c>
     </row>
     <row r="10">
@@ -4221,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.110</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="11">
@@ -4229,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4241,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.444</v>
+        <v>2.856</v>
       </c>
     </row>
     <row r="12">
@@ -4249,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4258,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>9.002</v>
+        <v>5.986</v>
       </c>
     </row>
     <row r="13">
@@ -4269,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4278,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>6.040</v>
+        <v>3.001</v>
       </c>
     </row>
     <row r="14">
@@ -4289,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4298,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="str">
-        <v>3.037</v>
+        <v>9.090</v>
       </c>
     </row>
     <row r="15">
@@ -4309,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4321,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.057</v>
+        <v>2.767</v>
       </c>
     </row>
     <row r="16">
@@ -4329,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4338,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.054</v>
+        <v>5.242</v>
       </c>
     </row>
     <row r="17">
@@ -4349,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4361,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.988</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="18">
@@ -4369,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4378,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>5.762</v>
+        <v>2.527</v>
       </c>
     </row>
     <row r="19">
@@ -4389,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4398,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>6.135</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="20">
@@ -4409,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4421,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.741</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="21">
@@ -4429,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4441,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.613</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="22">
@@ -4449,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4461,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.629</v>
+        <v>3.106</v>
       </c>
     </row>
     <row r="23">
@@ -4469,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4481,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>3.230</v>
+        <v>2.961</v>
       </c>
     </row>
     <row r="24">
@@ -4489,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4498,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>3.041</v>
+        <v>9.853</v>
       </c>
     </row>
     <row r="25">
@@ -4509,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4518,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>8.614</v>
+        <v>4.526</v>
       </c>
     </row>
     <row r="26">
@@ -4529,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4538,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>8.846</v>
+        <v>2.896</v>
       </c>
     </row>
     <row r="27">
@@ -4549,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4561,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.003</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="28">
@@ -4569,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMONE</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4581,7 +4741,7 @@
         <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>7.292</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="29">
@@ -4589,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4598,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.687</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="30">
@@ -4609,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4618,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>2.694</v>
+        <v>5.537</v>
       </c>
     </row>
     <row r="31">
@@ -4629,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4641,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>3.050</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="32">
@@ -4649,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4661,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.883</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="33">
@@ -4669,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4678,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.229</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="34">
@@ -4689,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4701,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.686</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="35">
@@ -4709,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MORA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4718,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.411</v>
+        <v>5.634</v>
       </c>
     </row>
     <row r="36">
@@ -4729,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4738,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>9.065</v>
+        <v>3.130</v>
       </c>
     </row>
     <row r="37">
@@ -4749,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4758,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>11.708</v>
+        <v>2.652</v>
       </c>
     </row>
     <row r="38">
@@ -4769,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4778,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>9.763</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="39">
@@ -4801,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.160</v>
+        <v>2.481</v>
       </c>
     </row>
     <row r="40">
@@ -4809,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -4818,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.292</v>
+        <v>5.645</v>
       </c>
     </row>
     <row r="41">
@@ -4829,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -4838,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>13.814</v>
+        <v>2.363</v>
       </c>
     </row>
     <row r="42">
@@ -4849,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -4858,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F42" t="str">
-        <v>2.700</v>
+        <v>23.038</v>
       </c>
     </row>
     <row r="43">
@@ -4869,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -4881,7 +5041,7 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>5.710</v>
+        <v>5.482</v>
       </c>
     </row>
     <row r="44">
@@ -4889,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>SEADAS</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -4901,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>3.080</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="45">
@@ -4909,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -4918,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>19.859</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="46">
@@ -4929,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>TIRAMISU'</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -4941,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.585</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="47">
@@ -4949,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -4958,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47" t="str">
-        <v>2.629</v>
+        <v>16.691</v>
       </c>
     </row>
     <row r="48">
@@ -4969,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -4981,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>3.315</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="49">
@@ -4989,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>SACRIPANTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -4998,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>3.151</v>
+        <v>5.546</v>
       </c>
     </row>
     <row r="50">
@@ -5009,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5021,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.591</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="51">
@@ -5029,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5041,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>5.346</v>
+        <v>5.502</v>
       </c>
     </row>
     <row r="52">
@@ -5049,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>CARROT CAKE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5061,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.680</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="53">
@@ -5069,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5078,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>11.924</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="54">
@@ -5089,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5101,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.771</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="55">
@@ -5109,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5121,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>3.038</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="56">
@@ -5129,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>MONT BLANC</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5141,7 +5301,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>3.300</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="57">
@@ -5149,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5161,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.807</v>
+        <v>2.746</v>
       </c>
     </row>
     <row r="58">
@@ -5169,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5181,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>2.827</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="59">
@@ -5189,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5198,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F59" t="str">
-        <v>2.047</v>
+        <v>3.076</v>
       </c>
     </row>
     <row r="60">
@@ -5209,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5221,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.586</v>
+        <v>2.965</v>
       </c>
     </row>
     <row r="61">
@@ -5229,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5238,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>1.556</v>
+        <v>2.959</v>
       </c>
     </row>
     <row r="62">
@@ -5249,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5258,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>3.083</v>
+        <v>5.658</v>
       </c>
     </row>
   </sheetData>
@@ -5273,7 +5433,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5288,7 +5448,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
@@ -5299,24 +5459,24 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5338,7 +5498,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -5349,45 +5509,45 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
@@ -5398,18 +5558,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
@@ -5420,18 +5580,18 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
@@ -5442,7 +5602,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
@@ -5453,18 +5613,18 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5475,7 +5635,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
@@ -5486,7 +5646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -5497,18 +5657,18 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -5519,62 +5679,62 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C27" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
@@ -5585,7 +5745,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
@@ -5596,40 +5756,40 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MIRTILLO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -5640,51 +5800,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>PERA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>POLLICINA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -5695,29 +5855,29 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PERA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -5728,29 +5888,29 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SEADAS</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>UVA E NOCI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -5761,7 +5921,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>SEADAS</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
@@ -5772,18 +5932,18 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -5794,7 +5954,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PENSIERO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -5805,7 +5965,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SACRIPANTE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -5816,29 +5976,29 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>YOGURT</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
@@ -5849,51 +6009,51 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>MONT BLANC</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SACHER TORTE</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -5904,7 +6064,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
@@ -5915,7 +6075,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
@@ -5926,7 +6086,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
@@ -5937,106 +6097,106 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ANGURIA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>BAKLAVA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CACHI</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CIOCCOLATO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FIORDILATTE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>GIANDUIA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>LIMONE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
@@ -6047,7 +6207,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
@@ -6058,7 +6218,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>CACHI</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
@@ -6069,29 +6229,29 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -6102,62 +6262,62 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>MORA</v>
+        <v>ESTASI</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>TIRAMISU'</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
@@ -6168,18 +6328,18 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
@@ -6190,18 +6350,18 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
@@ -6212,29 +6372,29 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6245,18 +6405,18 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6267,7 +6427,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>MORA</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
@@ -6278,18 +6438,18 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
@@ -6300,7 +6460,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6311,7 +6471,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
@@ -6322,7 +6482,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6333,7 +6493,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
@@ -6344,7 +6504,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>FICHI</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6355,7 +6515,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>FICHI</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6388,7 +6548,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
@@ -6399,7 +6559,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
@@ -6419,20 +6579,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>TORRONE SALATO</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C105" t="str">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 29-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 05-04-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -463,7 +463,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -525,7 +525,7 @@
         <v/>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>3</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -548,8 +548,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -575,7 +575,7 @@
         <v/>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>2</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -662,8 +662,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -674,8 +674,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6">
-        <v>1</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -698,8 +698,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
-        <v/>
+      <c r="P6">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>2</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -775,7 +775,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -786,8 +786,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8" t="str">
-        <v/>
+      <c r="L8">
+        <v>1</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -924,8 +924,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -962,8 +962,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -986,8 +986,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12" t="str">
-        <v/>
+      <c r="L12">
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>2</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1262,8 +1262,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18">
-        <v>1</v>
+      <c r="D18" t="str">
+        <v/>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>1</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1313,7 +1313,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1386,8 +1386,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v/>
+      <c r="L20">
+        <v>1</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1436,8 +1436,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21">
-        <v>2</v>
+      <c r="L21" t="str">
+        <v/>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1486,8 +1486,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22" t="str">
-        <v/>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1713,7 +1713,7 @@
         <v/>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>1</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2049,7 +2049,7 @@
         <v/>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2162,8 +2162,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36" t="str">
-        <v/>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2212,8 +2212,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37" t="str">
-        <v/>
+      <c r="D37">
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2412,8 +2412,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41">
-        <v>2</v>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2448,8 +2448,8 @@
       <c r="O41" t="str">
         <v/>
       </c>
-      <c r="P41" t="str">
-        <v/>
+      <c r="P41">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2512,8 +2512,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>4.734</v>
+        <v>12.137</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>7.418</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2.710</v>
+        <v>5.308</v>
       </c>
     </row>
     <row r="5">
@@ -2910,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>3.514</v>
+        <v>3.461</v>
       </c>
     </row>
     <row r="6">
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="str">
-        <v>2.848</v>
+        <v>8.931</v>
       </c>
     </row>
     <row r="7">
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
-        <v>4.545</v>
+        <v>6.959</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>3.058</v>
+        <v>2.799</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>2.796</v>
+        <v>8.814</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.406</v>
+        <v>3.341</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="str">
-        <v>2.929</v>
+        <v>9.151</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>5.791</v>
+        <v>8.966</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>5.992</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>5.939</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3110,7 +3110,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>5.831</v>
+        <v>6.019</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.165</v>
+        <v>2.890</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>5.340</v>
+        <v>2.780</v>
       </c>
     </row>
     <row r="18">
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.700</v>
+        <v>2.636</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.712</v>
+        <v>2.740</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3210,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.517</v>
+        <v>2.836</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>5.462</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3250,7 +3250,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>8.703</v>
+        <v>8.088</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FRAGOLA</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>2.324</v>
+        <v>6.330</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>GIANDUIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3290,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>3.008</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3310,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>2.291</v>
+        <v>2.474</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>2.825</v>
+        <v>6.849</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.602</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.821</v>
+        <v>5.372</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDARINO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.524</v>
+        <v>5.022</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.796</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>3.014</v>
+        <v>5.743</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.757</v>
+        <v>2.831</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>5.424</v>
+        <v>6.090</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>7.354</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MIRTILLO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="str">
-        <v>2.433</v>
+        <v>8.287</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>3.100</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>12.033</v>
+        <v>9.394</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>3.065</v>
+        <v>11.673</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.801</v>
+        <v>6.136</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3610,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>2.963</v>
+        <v>3.084</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>2.258</v>
+        <v>4.673</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PERA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.809</v>
+        <v>2.525</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3670,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.942</v>
+        <v>2.856</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>5.642</v>
+        <v>2.467</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>SEADAS</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.952</v>
+        <v>2.919</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>5.589</v>
+        <v>3.225</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>TIRAMISU'</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>5.601</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>UVA E NOCI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.090</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>SEADAS</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>3.055</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="str">
-        <v>2.972</v>
+        <v>8.795</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PENSIERO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.491</v>
+        <v>2.784</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SACRIPANTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>6.207</v>
+        <v>5.977</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3870,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>5.385</v>
+        <v>4.435</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3890,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.765</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>8.781</v>
+        <v>5.707</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>2.848</v>
+        <v>5.644</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>6.064</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>MONT BLANC</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>15.337</v>
+        <v>4.916</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>3.128</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +4007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F60" t="str">
-        <v>3.287</v>
+        <v>15.337</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>3.163</v>
+        <v>2.356</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>6.619</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>SACHER TORTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.744</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4087,10 +4087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E64" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>8.412</v>
+        <v>2.711</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="str">
-        <v>6.327</v>
+        <v>8.555</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" t="str">
-        <v>5.792</v>
+        <v>12.777</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +4147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>17.007</v>
+        <v>3.618</v>
       </c>
     </row>
     <row r="68">
@@ -4158,31 +4158,71 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E68" t="str">
+        <v>9</v>
+      </c>
+      <c r="F68" t="str">
+        <v>27.005</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B69" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E69" t="str">
+        <v>1</v>
+      </c>
+      <c r="F69" t="str">
+        <v>3.042</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E68" t="str">
-        <v>2</v>
-      </c>
-      <c r="F68" t="str">
-        <v>5.614</v>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E70" t="str">
+        <v>3</v>
+      </c>
+      <c r="F70" t="str">
+        <v>8.640</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4221,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.505</v>
+        <v>2.435</v>
       </c>
     </row>
     <row r="3">
@@ -4229,7 +4269,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -4241,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.442</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="4">
@@ -4261,7 +4301,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>5.702</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="5">
@@ -4269,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4278,10 +4318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>26.847</v>
+        <v>6.791</v>
       </c>
     </row>
     <row r="6">
@@ -4289,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4298,10 +4338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6" t="str">
-        <v>2.396</v>
+        <v>24.088</v>
       </c>
     </row>
     <row r="7">
@@ -4309,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4318,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.509</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="8">
@@ -4338,10 +4378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.443</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="9">
@@ -4361,7 +4401,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>5.537</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="10">
@@ -4369,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CACHI</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4378,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>2.022</v>
+        <v>7.408</v>
       </c>
     </row>
     <row r="11">
@@ -4389,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4401,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.856</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="12">
@@ -4409,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4418,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>5.986</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="13">
@@ -4429,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4441,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>3.001</v>
+        <v>2.869</v>
       </c>
     </row>
     <row r="14">
@@ -4449,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4458,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>9.090</v>
+        <v>3.049</v>
       </c>
     </row>
     <row r="15">
@@ -4469,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4478,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>2.767</v>
+        <v>12.002</v>
       </c>
     </row>
     <row r="16">
@@ -4489,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4501,7 +4541,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>5.242</v>
+        <v>5.756</v>
       </c>
     </row>
     <row r="17">
@@ -4509,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4518,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>2.444</v>
+        <v>8.701</v>
       </c>
     </row>
     <row r="18">
@@ -4529,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4538,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>2.527</v>
+        <v>5.240</v>
       </c>
     </row>
     <row r="19">
@@ -4549,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4558,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.681</v>
+        <v>5.340</v>
       </c>
     </row>
     <row r="20">
@@ -4569,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4578,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>2.708</v>
+        <v>5.326</v>
       </c>
     </row>
     <row r="21">
@@ -4589,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4601,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.764</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="22">
@@ -4609,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>ESTASI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4621,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>3.106</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="23">
@@ -4629,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FIORDILATTE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4641,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.961</v>
+        <v>3.096</v>
       </c>
     </row>
     <row r="24">
@@ -4649,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FRAGOLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4658,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="str">
-        <v>9.853</v>
+        <v>14.372</v>
       </c>
     </row>
     <row r="25">
@@ -4669,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4678,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>4.526</v>
+        <v>14.049</v>
       </c>
     </row>
     <row r="26">
@@ -4689,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>GIANDUIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4701,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.896</v>
+        <v>2.078</v>
       </c>
     </row>
     <row r="27">
@@ -4718,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>2.009</v>
+        <v>4.519</v>
       </c>
     </row>
     <row r="28">
@@ -4738,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>7.884</v>
+        <v>5.668</v>
       </c>
     </row>
     <row r="29">
@@ -4749,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4758,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.044</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="30">
@@ -4769,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4778,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>5.537</v>
+        <v>10.405</v>
       </c>
     </row>
     <row r="31">
@@ -4789,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4801,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.722</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="32">
@@ -4809,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4821,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.639</v>
+        <v>2.950</v>
       </c>
     </row>
     <row r="33">
@@ -4829,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MIRTILLO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4838,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v>2.562</v>
+        <v>10.636</v>
       </c>
     </row>
     <row r="34">
@@ -4849,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4858,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.977</v>
+        <v>4.830</v>
       </c>
     </row>
     <row r="35">
@@ -4869,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4881,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>5.634</v>
+        <v>4.723</v>
       </c>
     </row>
     <row r="36">
@@ -4889,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4898,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>3.130</v>
+        <v>6.125</v>
       </c>
     </row>
     <row r="37">
@@ -4909,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4918,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" t="str">
-        <v>2.652</v>
+        <v>15.046</v>
       </c>
     </row>
     <row r="38">
@@ -4938,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.624</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="39">
@@ -4949,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -4958,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.481</v>
+        <v>4.769</v>
       </c>
     </row>
     <row r="40">
@@ -4969,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PERA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -4978,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.645</v>
+        <v>2.789</v>
       </c>
     </row>
     <row r="41">
@@ -4989,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5001,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>2.363</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="42">
@@ -5009,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5018,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>23.038</v>
+        <v>4.680</v>
       </c>
     </row>
     <row r="43">
@@ -5029,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5038,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="str">
-        <v>5.482</v>
+        <v>20.542</v>
       </c>
     </row>
     <row r="44">
@@ -5049,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5061,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.737</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="45">
@@ -5069,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5081,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.742</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="46">
@@ -5098,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>3.101</v>
+        <v>5.308</v>
       </c>
     </row>
     <row r="47">
@@ -5109,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5118,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>16.691</v>
+        <v>2.858</v>
       </c>
     </row>
     <row r="48">
@@ -5129,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5138,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F48" t="str">
-        <v>2.692</v>
+        <v>22.695</v>
       </c>
     </row>
     <row r="49">
@@ -5149,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>YOGURT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5158,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>5.546</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="50">
@@ -5169,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5181,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>3.029</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="51">
@@ -5189,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5198,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>5.502</v>
+        <v>3.187</v>
       </c>
     </row>
     <row r="52">
@@ -5209,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PENSIERO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5218,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.916</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="53">
@@ -5241,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>2.982</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="54">
@@ -5249,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>CARROT CAKE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5258,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="str">
-        <v>2.592</v>
+        <v>8.781</v>
       </c>
     </row>
     <row r="55">
@@ -5269,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5281,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.887</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="56">
@@ -5289,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5298,10 +5338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>2.646</v>
+        <v>6.010</v>
       </c>
     </row>
     <row r="57">
@@ -5309,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>SACHER TORTE</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5321,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.746</v>
+        <v>2.753</v>
       </c>
     </row>
     <row r="58">
@@ -5329,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5341,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.169</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="59">
@@ -5349,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5358,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>3.076</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="60">
@@ -5369,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5381,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.965</v>
+        <v>3.123</v>
       </c>
     </row>
     <row r="61">
@@ -5389,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5398,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>2.959</v>
+        <v>5.523</v>
       </c>
     </row>
     <row r="62">
@@ -5409,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5421,19 +5461,119 @@
         <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>5.658</v>
+        <v>5.616</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E63" t="str">
+        <v>4</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B64" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E64" t="str">
+        <v>1</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2.793</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B65" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5.792</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B66" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E66" t="str">
+        <v>4</v>
+      </c>
+      <c r="F66" t="str">
+        <v>11.341</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
+        <v>2.851</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F67"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5448,7 +5588,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
@@ -5459,7 +5599,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
@@ -5470,13 +5610,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5487,7 +5627,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5498,7 +5638,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -5514,40 +5654,40 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
@@ -5558,7 +5698,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
@@ -5569,57 +5709,57 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5635,29 +5775,29 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C20" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -5668,7 +5808,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -5679,95 +5819,95 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FRAGOLA</v>
+        <v>ESTASI</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GIANDUIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C27" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MANDARINO</v>
+        <v>LIMONE</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -5778,18 +5918,18 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -5800,7 +5940,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
@@ -5811,29 +5951,29 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MIRTILLO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
@@ -5844,7 +5984,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -5855,40 +5995,40 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C41" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PERA</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -5899,51 +6039,51 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SEADAS</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>TIRAMISU'</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -5954,51 +6094,51 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>UVA E NOCI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>SEADAS</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PENSIERO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SACRIPANTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
@@ -6009,7 +6149,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
@@ -6020,40 +6160,40 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -6064,7 +6204,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MONT BLANC</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
@@ -6075,18 +6215,18 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
@@ -6097,7 +6237,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6108,7 +6248,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6119,7 +6259,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SACHER TORTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -6130,18 +6270,18 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
@@ -6152,7 +6292,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -6163,18 +6303,18 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
@@ -6185,7 +6325,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ALBICOCCA</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
@@ -6196,18 +6336,18 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
@@ -6218,7 +6358,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CACHI</v>
+        <v>AMARENA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
@@ -6229,62 +6369,62 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ESTASI</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
@@ -6295,7 +6435,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
@@ -6306,18 +6446,18 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PAPAYA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
@@ -6328,29 +6468,29 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
@@ -6361,117 +6501,117 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C88" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C90" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MORA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>PASSION FRUIT</v>
+        <v>CACHI</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>BAKLAVA</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C94" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
@@ -6482,7 +6622,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>MORA</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6493,18 +6633,18 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6515,7 +6655,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>FICHI</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6526,7 +6666,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6537,7 +6677,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>FICHI</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6548,7 +6688,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>UVA FRAGOLA E ZENZERO</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
@@ -6559,29 +6699,18 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C103" t="str">
         <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>CASTAGNACCIO</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C104" t="str">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 05-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 12-04-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -463,7 +463,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -499,7 +499,7 @@
         <v/>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>4</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v/>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -586,8 +586,8 @@
       <c r="K4" t="str">
         <v/>
       </c>
-      <c r="L4" t="str">
-        <v/>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -662,8 +662,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -736,8 +736,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -763,7 +763,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -775,7 +775,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -936,8 +936,8 @@
       <c r="K11" t="str">
         <v/>
       </c>
-      <c r="L11" t="str">
-        <v/>
+      <c r="L11">
+        <v>1</v>
       </c>
       <c r="M11" t="str">
         <v>COCCO AL RUM</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>1</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1186,8 +1186,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16" t="str">
-        <v/>
+      <c r="L16">
+        <v>1</v>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1212,8 +1212,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="D17">
+        <v>1</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1262,8 +1262,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="D18">
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>2</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1312,8 +1312,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19">
-        <v>1</v>
+      <c r="D19" t="str">
+        <v/>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1436,8 +1436,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21" t="str">
-        <v/>
+      <c r="L21">
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1498,8 +1498,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>2</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1512,8 +1512,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1562,8 +1562,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1598,8 +1598,8 @@
       <c r="O24" t="str">
         <v/>
       </c>
-      <c r="P24" t="str">
-        <v/>
+      <c r="P24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1649,7 +1649,7 @@
         <v/>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1698,8 +1698,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26" t="str">
-        <v/>
+      <c r="P26">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1812,8 +1812,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29">
-        <v>4</v>
+      <c r="D29" t="str">
+        <v/>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1898,8 +1898,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30">
-        <v>1</v>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1912,8 +1912,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>1</v>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2012,8 +2012,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2049,7 +2049,7 @@
         <v/>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2098,8 +2098,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34" t="str">
-        <v/>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>2</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2312,8 +2312,8 @@
       <c r="C39" t="str">
         <v/>
       </c>
-      <c r="D39" t="str">
-        <v/>
+      <c r="D39">
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2512,8 +2512,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43" t="str">
-        <v/>
+      <c r="D43">
+        <v>3</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>12.137</v>
+        <v>2.012</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANGURIA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>5.105</v>
+        <v>4.960</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>5.308</v>
+        <v>3.461</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>3.461</v>
+        <v>9.232</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>8.931</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="7">
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>6.959</v>
+        <v>2.325</v>
       </c>
     </row>
     <row r="8">
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.799</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="9">
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>8.814</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>3.341</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="11">
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>9.151</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="12">
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>8.966</v>
+        <v>3.042</v>
       </c>
     </row>
     <row r="13">
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.915</v>
+        <v>2.714</v>
       </c>
     </row>
     <row r="14">
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>6.019</v>
+        <v>3.080</v>
       </c>
     </row>
     <row r="16">
@@ -3150,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.780</v>
+        <v>2.619</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3167,10 +3167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>2.636</v>
+        <v>5.331</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.740</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3210,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.836</v>
+        <v>2.748</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.517</v>
+        <v>5.232</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>8.088</v>
+        <v>5.254</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3270,7 +3270,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>6.330</v>
+        <v>5.360</v>
       </c>
     </row>
     <row r="24">
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>2.650</v>
+        <v>5.681</v>
       </c>
     </row>
     <row r="25">
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>2.474</v>
+        <v>6.511</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>6.849</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3347,10 +3347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>3.008</v>
+        <v>4.457</v>
       </c>
     </row>
     <row r="28">
@@ -3370,7 +3370,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>5.372</v>
+        <v>5.594</v>
       </c>
     </row>
     <row r="29">
@@ -3390,7 +3390,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>5.022</v>
+        <v>5.723</v>
       </c>
     </row>
     <row r="30">
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.735</v>
+        <v>2.686</v>
       </c>
     </row>
     <row r="31">
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.743</v>
+        <v>3.036</v>
       </c>
     </row>
     <row r="32">
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.831</v>
+        <v>6.226</v>
       </c>
     </row>
     <row r="33">
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="str">
-        <v>6.090</v>
+        <v>9.125</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.757</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MELONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>8.287</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="36">
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.538</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>9.394</v>
+        <v>2.359</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA</v>
+        <v>MORA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>11.673</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>6.136</v>
+        <v>3.119</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="str">
-        <v>3.084</v>
+        <v>8.943</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>4.673</v>
+        <v>2.906</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PERA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.525</v>
+        <v>2.874</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PERA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3670,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.856</v>
+        <v>2.561</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3690,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.467</v>
+        <v>3.022</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>POLLICINA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3710,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.919</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F46" t="str">
-        <v>3.225</v>
+        <v>14.504</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3750,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>2.942</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>2.871</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>SEADAS</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.989</v>
+        <v>2.922</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>8.795</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="str">
-        <v>2.784</v>
+        <v>11.351</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>YOGURT</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>5.977</v>
+        <v>5.669</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PENSIERO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>4.435</v>
+        <v>2.240</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>SACRIPANTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>2.946</v>
+        <v>6.000</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>5.707</v>
+        <v>2.205</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.644</v>
+        <v>3.103</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>2.848</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" t="str">
-        <v>4.916</v>
+        <v>11.387</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F59" t="str">
-        <v>3.114</v>
+        <v>26.376</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>MONT BLANC</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +4007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>15.337</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4027,10 +4027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>2.356</v>
+        <v>6.070</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>COCCO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>2.853</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>3.008</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>SACHER TORTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.711</v>
+        <v>3.085</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>8.555</v>
+        <v>3.006</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F66" t="str">
-        <v>12.777</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>3.618</v>
+        <v>2.905</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4167,10 +4167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E68" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>27.005</v>
+        <v>2.826</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4187,10 +4187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E69" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>3.042</v>
+        <v>6.639</v>
       </c>
     </row>
     <row r="70">
@@ -4210,7 +4210,7 @@
         <v>3</v>
       </c>
       <c r="F70" t="str">
-        <v>8.640</v>
+        <v>8.916</v>
       </c>
     </row>
   </sheetData>
@@ -4222,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4249,7 +4249,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.435</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="3">
@@ -4269,7 +4269,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -4278,10 +4278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>2.403</v>
+        <v>4.916</v>
       </c>
     </row>
     <row r="4">
@@ -4289,7 +4289,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4298,10 +4298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>5.616</v>
+        <v>7.790</v>
       </c>
     </row>
     <row r="5">
@@ -4309,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4318,10 +4318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>6.791</v>
+        <v>7.905</v>
       </c>
     </row>
     <row r="6">
@@ -4341,7 +4341,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="str">
-        <v>24.088</v>
+        <v>23.555</v>
       </c>
     </row>
     <row r="7">
@@ -4358,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.266</v>
+        <v>4.545</v>
       </c>
     </row>
     <row r="8">
@@ -4369,7 +4369,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.884</v>
+        <v>3.030</v>
       </c>
     </row>
     <row r="9">
@@ -4389,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4398,10 +4398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>5.508</v>
+        <v>12.197</v>
       </c>
     </row>
     <row r="10">
@@ -4409,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4418,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>7.408</v>
+        <v>5.548</v>
       </c>
     </row>
     <row r="11">
@@ -4429,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.946</v>
+        <v>3.400</v>
       </c>
     </row>
     <row r="12">
@@ -4449,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4458,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>2.750</v>
+        <v>15.521</v>
       </c>
     </row>
     <row r="13">
@@ -4469,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4481,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.869</v>
+        <v>2.876</v>
       </c>
     </row>
     <row r="14">
@@ -4489,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4501,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.049</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="15">
@@ -4509,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4518,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>12.002</v>
+        <v>5.837</v>
       </c>
     </row>
     <row r="16">
@@ -4529,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4538,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.756</v>
+        <v>2.992</v>
       </c>
     </row>
     <row r="17">
@@ -4549,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4558,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>8.701</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="18">
@@ -4569,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4578,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>5.240</v>
+        <v>3.127</v>
       </c>
     </row>
     <row r="19">
@@ -4589,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4598,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" t="str">
-        <v>5.340</v>
+        <v>14.789</v>
       </c>
     </row>
     <row r="20">
@@ -4609,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4618,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>5.326</v>
+        <v>2.780</v>
       </c>
     </row>
     <row r="21">
@@ -4629,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4638,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.616</v>
+        <v>5.400</v>
       </c>
     </row>
     <row r="22">
@@ -4649,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4658,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>2.819</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="23">
@@ -4669,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4678,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>3.096</v>
+        <v>5.431</v>
       </c>
     </row>
     <row r="24">
@@ -4689,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4698,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>14.372</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="25">
@@ -4709,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4718,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>14.049</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="26">
@@ -4729,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>ESTASI</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4738,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>2.078</v>
+        <v>6.330</v>
       </c>
     </row>
     <row r="27">
@@ -4749,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4758,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>4.519</v>
+        <v>11.329</v>
       </c>
     </row>
     <row r="28">
@@ -4769,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4778,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="str">
-        <v>5.668</v>
+        <v>10.506</v>
       </c>
     </row>
     <row r="29">
@@ -4789,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LEMON CURD</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4798,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>2.609</v>
+        <v>9.094</v>
       </c>
     </row>
     <row r="30">
@@ -4809,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4818,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>10.405</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="31">
@@ -4829,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4838,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>2.752</v>
+        <v>5.372</v>
       </c>
     </row>
     <row r="32">
@@ -4849,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4858,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
-        <v>2.950</v>
+        <v>15.196</v>
       </c>
     </row>
     <row r="33">
@@ -4869,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4878,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>10.636</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="34">
@@ -4889,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDARINO</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4898,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>4.830</v>
+        <v>2.524</v>
       </c>
     </row>
     <row r="35">
@@ -4909,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MIRTILLO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4921,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>4.723</v>
+        <v>5.749</v>
       </c>
     </row>
     <row r="36">
@@ -4929,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4938,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>6.125</v>
+        <v>2.827</v>
       </c>
     </row>
     <row r="37">
@@ -4949,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4958,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>15.046</v>
+        <v>4.786</v>
       </c>
     </row>
     <row r="38">
@@ -4969,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PAPAYA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4981,7 +4981,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>5.337</v>
+        <v>5.681</v>
       </c>
     </row>
     <row r="39">
@@ -4989,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -4998,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>4.769</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="40">
@@ -5009,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5018,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.789</v>
+        <v>6.275</v>
       </c>
     </row>
     <row r="41">
@@ -5029,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5038,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F41" t="str">
-        <v>2.607</v>
+        <v>23.832</v>
       </c>
     </row>
     <row r="42">
@@ -5049,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5058,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>4.680</v>
+        <v>3.071</v>
       </c>
     </row>
     <row r="43">
@@ -5069,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5078,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>20.542</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="44">
@@ -5089,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>POLLICINA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5098,10 +5098,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>2.860</v>
+        <v>4.673</v>
       </c>
     </row>
     <row r="45">
@@ -5109,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PERA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5118,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.801</v>
+        <v>5.326</v>
       </c>
     </row>
     <row r="46">
@@ -5129,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5141,7 +5141,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.308</v>
+        <v>5.772</v>
       </c>
     </row>
     <row r="47">
@@ -5149,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>2.858</v>
+        <v>2.467</v>
       </c>
     </row>
     <row r="48">
@@ -5169,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5178,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>22.695</v>
+        <v>3.038</v>
       </c>
     </row>
     <row r="49">
@@ -5189,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>UVA E NOCI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5198,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>2.297</v>
+        <v>5.993</v>
       </c>
     </row>
     <row r="50">
@@ -5209,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PENSIERO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.461</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="51">
@@ -5229,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SACRIPANTE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5241,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>3.187</v>
+        <v>2.809</v>
       </c>
     </row>
     <row r="52">
@@ -5249,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5258,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>5.334</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="53">
@@ -5269,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5278,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.603</v>
+        <v>5.864</v>
       </c>
     </row>
     <row r="54">
@@ -5289,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5298,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>8.781</v>
+        <v>2.963</v>
       </c>
     </row>
     <row r="55">
@@ -5309,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5318,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F55" t="str">
-        <v>1.031</v>
+        <v>34.709</v>
       </c>
     </row>
     <row r="56">
@@ -5329,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>6.010</v>
+        <v>5.601</v>
       </c>
     </row>
     <row r="57">
@@ -5349,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5361,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.753</v>
+        <v>2.090</v>
       </c>
     </row>
     <row r="58">
@@ -5369,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5381,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.287</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="59">
@@ -5389,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5398,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>1.075</v>
+        <v>8.680</v>
       </c>
     </row>
     <row r="60">
@@ -5409,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5421,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.123</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="61">
@@ -5429,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>SACHER TORTE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5441,7 +5441,7 @@
         <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>5.523</v>
+        <v>5.966</v>
       </c>
     </row>
     <row r="62">
@@ -5449,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5458,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>5.616</v>
+        <v>2.617</v>
       </c>
     </row>
     <row r="63">
@@ -5469,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5478,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.056</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="64">
@@ -5489,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5501,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.793</v>
+        <v>3.128</v>
       </c>
     </row>
     <row r="65">
@@ -5509,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5518,10 +5518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>5.792</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="66">
@@ -5529,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5538,10 +5538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>11.341</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="67">
@@ -5549,31 +5549,271 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
+        <v>3.162</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B68" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E68" t="str">
+        <v>1</v>
+      </c>
+      <c r="F68" t="str">
+        <v>3.075</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B69" t="str">
+        <v>PASTIERA NAPOLETANA</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>1</v>
+      </c>
+      <c r="F69" t="str">
+        <v>3.128</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>1</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2.853</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>6.171</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>6.641</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5.712</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E74" t="str">
+        <v>3</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8.318</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E75" t="str">
+        <v>7</v>
+      </c>
+      <c r="F75" t="str">
+        <v>3.366</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B76" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E76" t="str">
+        <v>1</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2.950</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B77" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E77" t="str">
+        <v>1</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3.618</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B78" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E78" t="str">
+        <v>11</v>
+      </c>
+      <c r="F78" t="str">
+        <v>32.879</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B79" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E67" t="str">
-        <v>1</v>
-      </c>
-      <c r="F67" t="str">
-        <v>2.851</v>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5.650</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F79"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5588,18 +5828,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANGURIA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
@@ -5610,7 +5850,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
@@ -5621,24 +5861,24 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5649,7 +5889,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5671,12 +5911,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
@@ -5693,7 +5933,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -5704,7 +5944,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5737,7 +5977,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -5759,12 +5999,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5775,29 +6015,29 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C20" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -5808,7 +6048,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -5819,7 +6059,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
@@ -5847,29 +6087,29 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C27" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -5891,7 +6131,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -5902,7 +6142,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5913,7 +6153,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -5924,7 +6164,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5940,18 +6180,18 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MELONE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
@@ -5973,7 +6213,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
@@ -5984,7 +6224,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NOCCIOLA</v>
+        <v>MORA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -5995,40 +6235,40 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C41" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PERA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -6039,7 +6279,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PERA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -6050,7 +6290,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -6061,7 +6301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>POLLICINA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
@@ -6072,18 +6312,18 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -6094,18 +6334,18 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SEADAS</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6116,29 +6356,29 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>YOGURT</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
@@ -6149,18 +6389,18 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PENSIERO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SACRIPANTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
@@ -6171,29 +6411,29 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -6204,7 +6444,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
@@ -6215,29 +6455,29 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MONT BLANC</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6248,7 +6488,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>COCCO</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6259,7 +6499,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -6270,7 +6510,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SACHER TORTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -6281,57 +6521,57 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6347,24 +6587,24 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ALBICOCCA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>AMARENA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -6375,45 +6615,45 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
@@ -6424,73 +6664,73 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>LEMON CURD</v>
+        <v>ESTASI</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>PAPAYA</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>UVA E NOCI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
@@ -6501,18 +6741,18 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6523,40 +6763,40 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>YOGURT</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C88" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6567,18 +6807,18 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CACHI</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
@@ -6589,18 +6829,18 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6611,18 +6851,18 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>MORA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6633,29 +6873,29 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>BAKLAVA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C98" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6666,7 +6906,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6677,7 +6917,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FICHI</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6688,29 +6928,117 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>CACHI</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C103" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>CIOCCOLATO</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>MANDORLA TOSTATA</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C105" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C107" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>SEMIFREDDO  TIRAMISU</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C108" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FICHI</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C110" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
         <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
-      <c r="B103" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C103" t="str">
+      <c r="B111" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C111" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 12-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 19-04-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -463,7 +463,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -512,8 +512,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>4</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -548,8 +548,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3">
-        <v>1</v>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -562,8 +562,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>4</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -587,7 +587,7 @@
         <v/>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -598,8 +598,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4" t="str">
-        <v/>
+      <c r="P4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -624,8 +624,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5">
-        <v>1</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>3</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -674,8 +674,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>3</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -736,8 +736,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="L7" t="str">
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -763,7 +763,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -774,8 +774,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -924,8 +924,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11">
-        <v>1</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -936,8 +936,8 @@
       <c r="K11" t="str">
         <v/>
       </c>
-      <c r="L11">
-        <v>1</v>
+      <c r="L11" t="str">
+        <v/>
       </c>
       <c r="M11" t="str">
         <v>COCCO AL RUM</v>
@@ -962,8 +962,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12">
-        <v>3</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -975,7 +975,7 @@
         <v/>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>3</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1186,8 +1186,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16">
-        <v>1</v>
+      <c r="L16" t="str">
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>3</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>2</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1336,8 +1336,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19">
-        <v>1</v>
+      <c r="L19" t="str">
+        <v/>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>1</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1486,8 +1486,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22">
-        <v>1</v>
+      <c r="L22" t="str">
+        <v/>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1512,8 +1512,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23">
-        <v>4</v>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1563,7 +1563,7 @@
         <v/>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>2</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1699,7 +1699,7 @@
         <v/>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1712,8 +1712,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>1</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1849,7 +1849,7 @@
         <v/>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>1</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2012,8 +2012,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33">
-        <v>1</v>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>3</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2113,7 +2113,7 @@
         <v/>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.012</v>
+        <v>4.239</v>
       </c>
     </row>
     <row r="3">
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>4.960</v>
+        <v>2.635</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>3.461</v>
+        <v>5.207</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>9.232</v>
+        <v>2.741</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BAKLAVA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F6" t="str">
-        <v>2.862</v>
+        <v>36.063</v>
       </c>
     </row>
     <row r="7">
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.325</v>
+        <v>4.344</v>
       </c>
     </row>
     <row r="8">
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>3.050</v>
+        <v>6.041</v>
       </c>
     </row>
     <row r="9">
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>3.033</v>
+        <v>8.632</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>5.208</v>
+        <v>7.854</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>2.879</v>
+        <v>6.968</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3050,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.042</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F13" t="str">
-        <v>2.714</v>
+        <v>20.032</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="str">
-        <v>3.000</v>
+        <v>8.950</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>3.080</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3130,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>2.890</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3150,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.619</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +3170,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.331</v>
+        <v>5.840</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>5.556</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>2.748</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>5.232</v>
+        <v>8.202</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>5.254</v>
+        <v>8.213</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.360</v>
+        <v>2.569</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3290,7 +3290,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>5.681</v>
+        <v>5.459</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>6.511</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>3.158</v>
+        <v>5.259</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>ESTASI</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3350,7 +3350,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>4.457</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F28" t="str">
-        <v>5.594</v>
+        <v>16.645</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>5.723</v>
+        <v>9.303</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>2.686</v>
+        <v>9.346</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>3.036</v>
+        <v>6.248</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="str">
-        <v>6.226</v>
+        <v>8.827</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>9.125</v>
+        <v>5.302</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.433</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MELONE</v>
+        <v>LIMONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F35" t="str">
-        <v>2.572</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MIRTILLO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.835</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.359</v>
+        <v>2.980</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MORA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="str">
-        <v>2.319</v>
+        <v>8.858</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>3.119</v>
+        <v>9.125</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>8.943</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" t="str">
-        <v>2.906</v>
+        <v>9.645</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.874</v>
+        <v>2.719</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PERA</v>
+        <v>MELONE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>2.561</v>
+        <v>5.196</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3690,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>3.022</v>
+        <v>2.359</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.439</v>
+        <v>4.707</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>14.504</v>
+        <v>3.060</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F47" t="str">
-        <v>2.137</v>
+        <v>23.127</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3770,7 +3770,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>5.748</v>
+        <v>6.043</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>2.922</v>
+        <v>5.538</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>SEADAS</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.993</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>11.351</v>
+        <v>4.896</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>TIRAMISU'</v>
+        <v>PERA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3847,10 +3847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>5.669</v>
+        <v>2.482</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>UVA E NOCI</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" t="str">
-        <v>2.240</v>
+        <v>8.440</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54" t="str">
-        <v>6.000</v>
+        <v>11.930</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PENSIERO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.205</v>
+        <v>2.574</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>SACRIPANTE</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>3.103</v>
+        <v>4.555</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="str">
-        <v>5.805</v>
+        <v>8.944</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>11.387</v>
+        <v>6.017</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3990,7 +3990,7 @@
         <v>9</v>
       </c>
       <c r="F59" t="str">
-        <v>26.376</v>
+        <v>25.068</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4010,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.158</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>MONT BLANC</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4027,10 +4027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E61" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>6.070</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>COCCO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="str">
-        <v>3.195</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.142</v>
+        <v>3.103</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4087,10 +4087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E64" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" t="str">
-        <v>3.085</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
-        <v>3.006</v>
+        <v>5.999</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>SACHER TORTE</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>2</v>
       </c>
       <c r="F66" t="str">
-        <v>5.421</v>
+        <v>5.564</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +4147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F67" t="str">
-        <v>2.905</v>
+        <v>60.402</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.826</v>
+        <v>2.225</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>6.639</v>
+        <v>5.226</v>
       </c>
     </row>
     <row r="70">
@@ -4198,31 +4198,251 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E70" t="str">
+        <v>1</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2.681</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>6.178</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>6.080</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E73" t="str">
+        <v>1</v>
+      </c>
+      <c r="F73" t="str">
+        <v>3.291</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E74" t="str">
+        <v>4</v>
+      </c>
+      <c r="F74" t="str">
+        <v>10.847</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2</v>
+      </c>
+      <c r="F75" t="str">
+        <v>5.181</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B76" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E76" t="str">
+        <v>6</v>
+      </c>
+      <c r="F76" t="str">
+        <v>3.203</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B77" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E77" t="str">
+        <v>1</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3.110</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B78" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E78" t="str">
+        <v>1</v>
+      </c>
+      <c r="F78" t="str">
+        <v>3.251</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B79" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E79" t="str">
+        <v>6</v>
+      </c>
+      <c r="F79" t="str">
+        <v>17.072</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B80" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E80" t="str">
+        <v>3</v>
+      </c>
+      <c r="F80" t="str">
+        <v>8.578</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B81" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E70" t="str">
-        <v>3</v>
-      </c>
-      <c r="F70" t="str">
-        <v>8.916</v>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E81" t="str">
+        <v>4</v>
+      </c>
+      <c r="F81" t="str">
+        <v>12.106</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F81"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4258,10 +4478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.331</v>
+        <v>4.016</v>
       </c>
     </row>
     <row r="3">
@@ -4278,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>4.916</v>
+        <v>7.087</v>
       </c>
     </row>
     <row r="4">
@@ -4289,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4301,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>7.790</v>
+        <v>8.483</v>
       </c>
     </row>
     <row r="5">
@@ -4309,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4318,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" t="str">
-        <v>7.905</v>
+        <v>18.354</v>
       </c>
     </row>
     <row r="6">
@@ -4329,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4338,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>23.555</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="7">
@@ -4361,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>4.545</v>
+        <v>4.705</v>
       </c>
     </row>
     <row r="8">
@@ -4369,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4378,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>3.030</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="9">
@@ -4389,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4398,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>12.197</v>
+        <v>3.341</v>
       </c>
     </row>
     <row r="10">
@@ -4409,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4421,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.548</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="11">
@@ -4429,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4441,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>3.400</v>
+        <v>3.120</v>
       </c>
     </row>
     <row r="12">
@@ -4449,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4458,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>15.521</v>
+        <v>6.037</v>
       </c>
     </row>
     <row r="13">
@@ -4469,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4478,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>2.876</v>
+        <v>8.189</v>
       </c>
     </row>
     <row r="14">
@@ -4489,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4501,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>2.929</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="15">
@@ -4509,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4518,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>5.837</v>
+        <v>9.654</v>
       </c>
     </row>
     <row r="16">
@@ -4529,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4538,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.992</v>
+        <v>6.212</v>
       </c>
     </row>
     <row r="17">
@@ -4549,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4561,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.775</v>
+        <v>2.890</v>
       </c>
     </row>
     <row r="18">
@@ -4569,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4578,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>3.127</v>
+        <v>8.217</v>
       </c>
     </row>
     <row r="19">
@@ -4589,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4598,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" t="str">
-        <v>14.789</v>
+        <v>10.363</v>
       </c>
     </row>
     <row r="20">
@@ -4609,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4621,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.780</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="21">
@@ -4629,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4641,7 +4861,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>5.400</v>
+        <v>5.488</v>
       </c>
     </row>
     <row r="22">
@@ -4649,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4658,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>7.554</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="23">
@@ -4669,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4678,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.431</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="24">
@@ -4689,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4701,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.712</v>
+        <v>2.728</v>
       </c>
     </row>
     <row r="25">
@@ -4709,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4718,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>2.517</v>
+        <v>11.432</v>
       </c>
     </row>
     <row r="26">
@@ -4729,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>ESTASI</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4738,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F26" t="str">
-        <v>6.330</v>
+        <v>15.660</v>
       </c>
     </row>
     <row r="27">
@@ -4749,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4758,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>11.329</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="28">
@@ -4769,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FRAGOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4781,7 +5001,7 @@
         <v>5</v>
       </c>
       <c r="F28" t="str">
-        <v>10.506</v>
+        <v>13.964</v>
       </c>
     </row>
     <row r="29">
@@ -4789,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4798,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="str">
-        <v>9.094</v>
+        <v>13.366</v>
       </c>
     </row>
     <row r="30">
@@ -4809,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>GIANDUIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4821,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>3.008</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="31">
@@ -4829,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4838,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.372</v>
+        <v>2.947</v>
       </c>
     </row>
     <row r="32">
@@ -4849,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4858,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>15.196</v>
+        <v>2.831</v>
       </c>
     </row>
     <row r="33">
@@ -4869,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4881,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>2.821</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="34">
@@ -4889,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDARINO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4898,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.524</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="35">
@@ -4909,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4918,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>5.749</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="36">
@@ -4929,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4938,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>2.827</v>
+        <v>9.252</v>
       </c>
     </row>
     <row r="37">
@@ -4949,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4958,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F37" t="str">
-        <v>4.786</v>
+        <v>14.936</v>
       </c>
     </row>
     <row r="38">
@@ -4969,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4978,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.681</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="39">
@@ -4989,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MIRTILLO</v>
+        <v>PERA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -4998,10 +5218,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.538</v>
+        <v>4.989</v>
       </c>
     </row>
     <row r="40">
@@ -5009,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5021,7 +5241,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>6.275</v>
+        <v>5.883</v>
       </c>
     </row>
     <row r="41">
@@ -5029,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5038,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F41" t="str">
-        <v>23.832</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="42">
@@ -5049,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5058,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F42" t="str">
-        <v>3.071</v>
+        <v>19.953</v>
       </c>
     </row>
     <row r="43">
@@ -5069,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5078,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>5.796</v>
+        <v>2.900</v>
       </c>
     </row>
     <row r="44">
@@ -5089,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5101,7 +5321,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>4.673</v>
+        <v>5.991</v>
       </c>
     </row>
     <row r="45">
@@ -5109,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5121,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>5.326</v>
+        <v>5.951</v>
       </c>
     </row>
     <row r="46">
@@ -5129,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5141,7 +5361,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.772</v>
+        <v>5.982</v>
       </c>
     </row>
     <row r="47">
@@ -5149,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5158,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F47" t="str">
-        <v>2.467</v>
+        <v>28.271</v>
       </c>
     </row>
     <row r="48">
@@ -5169,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5178,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>3.038</v>
+        <v>5.911</v>
       </c>
     </row>
     <row r="49">
@@ -5189,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5198,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>5.993</v>
+        <v>2.240</v>
       </c>
     </row>
     <row r="50">
@@ -5209,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5218,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.258</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="51">
@@ -5229,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5238,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.809</v>
+        <v>4.435</v>
       </c>
     </row>
     <row r="52">
@@ -5249,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5261,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.942</v>
+        <v>3.046</v>
       </c>
     </row>
     <row r="53">
@@ -5269,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5278,10 +5498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>5.864</v>
+        <v>2.682</v>
       </c>
     </row>
     <row r="54">
@@ -5289,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>SEADAS</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5301,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.963</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="55">
@@ -5309,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>STRACCIATELLA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5318,10 +5538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>34.709</v>
+        <v>2.594</v>
       </c>
     </row>
     <row r="56">
@@ -5329,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>TIRAMISU'</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5338,10 +5558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.601</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="57">
@@ -5349,7 +5569,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>UVA E NOCI</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5361,7 +5581,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.090</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="58">
@@ -5369,7 +5589,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5381,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.055</v>
+        <v>2.356</v>
       </c>
     </row>
     <row r="59">
@@ -5389,7 +5609,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5398,10 +5618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>8.680</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="60">
@@ -5409,7 +5629,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5421,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.491</v>
+        <v>3.085</v>
       </c>
     </row>
     <row r="61">
@@ -5429,7 +5649,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>SACRIPANTE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5438,10 +5658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>5.966</v>
+        <v>993</v>
       </c>
     </row>
     <row r="62">
@@ -5449,7 +5669,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5461,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>2.617</v>
+        <v>3.006</v>
       </c>
     </row>
     <row r="63">
@@ -5469,7 +5689,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CARROT CAKE</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5478,10 +5698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>2.879</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="64">
@@ -5489,7 +5709,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5498,10 +5718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="str">
-        <v>3.128</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="65">
@@ -5509,7 +5729,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5518,10 +5738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="str">
-        <v>2.848</v>
+        <v>9.827</v>
       </c>
     </row>
     <row r="66">
@@ -5529,7 +5749,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5541,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.322</v>
+        <v>3.109</v>
       </c>
     </row>
     <row r="67">
@@ -5549,7 +5769,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -5558,10 +5778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67" t="str">
-        <v>3.162</v>
+        <v>14.521</v>
       </c>
     </row>
     <row r="68">
@@ -5569,7 +5789,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>MONT BLANC</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -5578,10 +5798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>3.075</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="69">
@@ -5589,7 +5809,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -5601,219 +5821,19 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>3.128</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B70" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E70" t="str">
-        <v>1</v>
-      </c>
-      <c r="F70" t="str">
-        <v>2.853</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E71" t="str">
-        <v>2</v>
-      </c>
-      <c r="F71" t="str">
-        <v>6.171</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E72" t="str">
-        <v>2</v>
-      </c>
-      <c r="F72" t="str">
-        <v>6.641</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B73" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="D73" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E73" t="str">
-        <v>2</v>
-      </c>
-      <c r="F73" t="str">
-        <v>5.712</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B74" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="D74" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E74" t="str">
-        <v>3</v>
-      </c>
-      <c r="F74" t="str">
-        <v>8.318</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B75" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E75" t="str">
-        <v>7</v>
-      </c>
-      <c r="F75" t="str">
-        <v>3.366</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B76" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="D76" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E76" t="str">
-        <v>1</v>
-      </c>
-      <c r="F76" t="str">
-        <v>2.950</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B77" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E77" t="str">
-        <v>1</v>
-      </c>
-      <c r="F77" t="str">
-        <v>3.618</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B78" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E78" t="str">
-        <v>11</v>
-      </c>
-      <c r="F78" t="str">
-        <v>32.879</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="D79" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E79" t="str">
-        <v>2</v>
-      </c>
-      <c r="F79" t="str">
-        <v>5.650</v>
+        <v>2.758</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5834,7 +5854,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5845,34 +5865,34 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BAKLAVA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
@@ -5900,7 +5920,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5911,12 +5931,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
@@ -5927,106 +5947,106 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -6037,7 +6057,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -6048,7 +6068,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -6059,51 +6079,51 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>ESTASI</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -6114,18 +6134,18 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
@@ -6136,29 +6156,29 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
@@ -6169,40 +6189,40 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MELONE</v>
+        <v>LIMONE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MIRTILLO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
@@ -6213,18 +6233,18 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MORA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -6235,29 +6255,29 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6268,62 +6288,62 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PERA</v>
+        <v>MELONE</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -6334,7 +6354,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -6345,18 +6365,18 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SEADAS</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6367,51 +6387,51 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TIRAMISU'</v>
+        <v>PERA</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>UVA E NOCI</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PENSIERO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
@@ -6422,18 +6442,18 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SACRIPANTE</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -6444,29 +6464,29 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
@@ -6477,7 +6497,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>MONT BLANC</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6488,7 +6508,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>COCCO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6499,51 +6519,51 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SACHER TORTE</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
@@ -6554,18 +6574,18 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
@@ -6576,62 +6596,62 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ANGURIA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CAFFE'</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -6642,128 +6662,128 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ESTASI</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>MANDARINO</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PASSION FRUIT</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>POLLICINA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>YOGURT</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
@@ -6774,7 +6794,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>CARROT CAKE</v>
+        <v>SEADAS</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6785,40 +6805,40 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>YOGURT</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C90" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
@@ -6829,18 +6849,18 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6851,18 +6871,18 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ALBICOCCA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6873,40 +6893,40 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>LEMON CURD</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>PAPAYA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C98" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6917,7 +6937,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6928,40 +6948,40 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>CACHI</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CACHI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C103" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C104" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6972,18 +6992,18 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
@@ -6994,7 +7014,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>FICHI</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -7005,7 +7025,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>FICHI</v>
+        <v>UVA FRAGOLA E ZENZERO</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -7016,29 +7036,18 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C110" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
-      </c>
-      <c r="B111" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C111" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C110"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 19-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 26-04-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>3</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -512,8 +512,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>8</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -562,8 +562,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>3</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -586,8 +586,8 @@
       <c r="K4" t="str">
         <v/>
       </c>
-      <c r="L4">
-        <v>2</v>
+      <c r="L4" t="str">
+        <v/>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -624,8 +624,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -675,7 +675,7 @@
         <v/>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -749,7 +749,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -763,7 +763,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -774,8 +774,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>2</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -874,8 +874,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -898,8 +898,8 @@
       <c r="O10" t="str">
         <v/>
       </c>
-      <c r="P10" t="str">
-        <v/>
+      <c r="P10">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -962,8 +962,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1148,8 +1148,8 @@
       <c r="O15" t="str">
         <v/>
       </c>
-      <c r="P15">
-        <v>1</v>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>2</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1336,8 +1336,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v/>
+      <c r="L19">
+        <v>2</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>2</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1462,8 +1462,8 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" t="str">
-        <v/>
+      <c r="D22">
+        <v>2</v>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1498,8 +1498,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22" t="str">
-        <v/>
+      <c r="P22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1512,8 +1512,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>3</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1562,8 +1562,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24">
-        <v>2</v>
+      <c r="D24" t="str">
+        <v/>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1699,7 +1699,7 @@
         <v/>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1762,8 +1762,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28">
-        <v>3</v>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1798,8 +1798,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28" t="str">
-        <v/>
+      <c r="P28">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1848,8 +1848,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>2</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1998,8 +1998,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32">
-        <v>1</v>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2012,8 +2012,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>3</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2098,8 +2098,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34">
-        <v>3</v>
+      <c r="P34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2162,8 +2162,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36">
-        <v>1</v>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2198,8 +2198,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>3</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2262,8 +2262,8 @@
       <c r="C38" t="str">
         <v/>
       </c>
-      <c r="D38">
-        <v>1</v>
+      <c r="D38" t="str">
+        <v/>
       </c>
       <c r="E38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
@@ -2348,8 +2348,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39" t="str">
-        <v/>
+      <c r="P39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2412,8 +2412,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="D41">
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2498,8 +2498,8 @@
       <c r="O42" t="str">
         <v/>
       </c>
-      <c r="P42">
-        <v>1</v>
+      <c r="P42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2513,7 +2513,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>2.635</v>
+        <v>4.837</v>
       </c>
     </row>
     <row r="4">
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>2.741</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="6">
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>36.063</v>
+        <v>5.841</v>
       </c>
     </row>
     <row r="7">
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>4.344</v>
+        <v>2.219</v>
       </c>
     </row>
     <row r="8">
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>6.041</v>
+        <v>2.696</v>
       </c>
     </row>
     <row r="9">
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>8.632</v>
+        <v>5.419</v>
       </c>
     </row>
     <row r="10">
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>7.854</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="11">
@@ -3030,7 +3030,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>6.968</v>
+        <v>6.929</v>
       </c>
     </row>
     <row r="12">
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>2.692</v>
+        <v>7.424</v>
       </c>
     </row>
     <row r="13">
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>20.032</v>
+        <v>8.371</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>8.950</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>4.977</v>
+        <v>8.950</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.988</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>3.044</v>
+        <v>6.236</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3167,10 +3167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>5.840</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="str">
-        <v>3.102</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>10.308</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>8.202</v>
+        <v>2.716</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>8.213</v>
+        <v>4.828</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3270,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.569</v>
+        <v>2.682</v>
       </c>
     </row>
     <row r="24">
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>5.459</v>
+        <v>2.555</v>
       </c>
     </row>
     <row r="25">
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>4.865</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="26">
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>5.259</v>
+        <v>2.633</v>
       </c>
     </row>
     <row r="27">
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>16.645</v>
+        <v>7.984</v>
       </c>
     </row>
     <row r="29">
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" t="str">
-        <v>9.303</v>
+        <v>13.265</v>
       </c>
     </row>
     <row r="30">
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>9.346</v>
+        <v>4.668</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>6.248</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="str">
-        <v>8.827</v>
+        <v>8.377</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>5.302</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>LEMON CURD</v>
+        <v>LIMONE</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34" t="str">
-        <v>4.975</v>
+        <v>9.799</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>LIMONE</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>14.465</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>3.077</v>
+        <v>2.794</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>2.980</v>
+        <v>5.985</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>8.858</v>
+        <v>5.840</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>9.125</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.863</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MORA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>9.645</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>2.719</v>
+        <v>6.045</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F43" t="str">
-        <v>5.196</v>
+        <v>14.305</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>2.359</v>
+        <v>8.681</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>MORA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3710,7 +3710,7 @@
         <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>4.707</v>
+        <v>5.218</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>3.060</v>
+        <v>2.508</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F47" t="str">
-        <v>23.127</v>
+        <v>8.440</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="str">
-        <v>6.043</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="str">
-        <v>5.538</v>
+        <v>17.644</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" t="str">
-        <v>2.651</v>
+        <v>11.632</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="str">
-        <v>4.896</v>
+        <v>8.326</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PERA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.482</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F53" t="str">
-        <v>8.440</v>
+        <v>19.546</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>11.930</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.574</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>4.555</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>YOGURT</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>8.944</v>
+        <v>5.744</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3970,7 +3970,7 @@
         <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>6.017</v>
+        <v>4.858</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>25.068</v>
+        <v>3.022</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +4007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>2.522</v>
+        <v>5.259</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>3.164</v>
+        <v>2.467</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>9.009</v>
+        <v>5.564</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +4067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F63" t="str">
-        <v>3.103</v>
+        <v>40.350</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4087,10 +4087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E64" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>8.138</v>
+        <v>5.226</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>5.999</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CARROT CAKE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>5.564</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +4147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F67" t="str">
-        <v>60.402</v>
+        <v>7.985</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4167,10 +4167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E68" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>2.225</v>
+        <v>5.659</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>5.226</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>2.681</v>
+        <v>3.251</v>
       </c>
     </row>
     <row r="71">
@@ -4218,7 +4218,7 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
-        <v>MONT BLANC</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -4227,10 +4227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E71" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="str">
-        <v>6.178</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="72">
@@ -4238,7 +4238,7 @@
         <v>Stock</v>
       </c>
       <c r="B72" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -4247,10 +4247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E72" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="str">
-        <v>6.080</v>
+        <v>8.578</v>
       </c>
     </row>
     <row r="73">
@@ -4258,7 +4258,7 @@
         <v>Stock</v>
       </c>
       <c r="B73" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -4267,10 +4267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E73" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="str">
-        <v>3.291</v>
+        <v>8.843</v>
       </c>
     </row>
     <row r="74">
@@ -4278,7 +4278,7 @@
         <v>Stock</v>
       </c>
       <c r="B74" t="str">
-        <v>SACHER TORTE</v>
+        <v>FASHIONED SPRITZ</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -4287,155 +4287,15 @@
         <v>Mantenimento</v>
       </c>
       <c r="E74" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>10.847</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B75" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E75" t="str">
-        <v>2</v>
-      </c>
-      <c r="F75" t="str">
-        <v>5.181</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B76" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="D76" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E76" t="str">
-        <v>6</v>
-      </c>
-      <c r="F76" t="str">
-        <v>3.203</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B77" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E77" t="str">
-        <v>1</v>
-      </c>
-      <c r="F77" t="str">
-        <v>3.110</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B78" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E78" t="str">
-        <v>1</v>
-      </c>
-      <c r="F78" t="str">
-        <v>3.251</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B79" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="D79" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E79" t="str">
-        <v>6</v>
-      </c>
-      <c r="F79" t="str">
-        <v>17.072</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B80" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
-      </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E80" t="str">
-        <v>3</v>
-      </c>
-      <c r="F80" t="str">
-        <v>8.578</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B81" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="D81" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E81" t="str">
-        <v>4</v>
-      </c>
-      <c r="F81" t="str">
-        <v>12.106</v>
+        <v>1.985</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F74"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4469,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -4478,10 +4338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>4.016</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="3">
@@ -4489,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -4498,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>7.087</v>
+        <v>5.440</v>
       </c>
     </row>
     <row r="4">
@@ -4509,7 +4369,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4518,10 +4378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>8.483</v>
+        <v>3.461</v>
       </c>
     </row>
     <row r="5">
@@ -4538,10 +4398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="str">
-        <v>18.354</v>
+        <v>30.049</v>
       </c>
     </row>
     <row r="6">
@@ -4549,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4558,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="str">
-        <v>2.862</v>
+        <v>6.362</v>
       </c>
     </row>
     <row r="7">
@@ -4569,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4581,7 +4441,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>4.705</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="8">
@@ -4601,7 +4461,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>9.036</v>
+        <v>8.751</v>
       </c>
     </row>
     <row r="9">
@@ -4609,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4621,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>3.341</v>
+        <v>2.696</v>
       </c>
     </row>
     <row r="10">
@@ -4641,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.208</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="11">
@@ -4649,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4658,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
-        <v>3.120</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="12">
@@ -4669,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4678,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="str">
-        <v>6.037</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="13">
@@ -4689,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4701,7 +4561,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>8.189</v>
+        <v>8.750</v>
       </c>
     </row>
     <row r="14">
@@ -4709,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4718,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>3.311</v>
+        <v>5.700</v>
       </c>
     </row>
     <row r="15">
@@ -4729,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4741,7 +4601,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>9.654</v>
+        <v>7.782</v>
       </c>
     </row>
     <row r="16">
@@ -4749,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4761,7 +4621,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>6.212</v>
+        <v>5.448</v>
       </c>
     </row>
     <row r="17">
@@ -4769,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4778,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>2.890</v>
+        <v>5.560</v>
       </c>
     </row>
     <row r="18">
@@ -4789,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4798,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>8.217</v>
+        <v>5.340</v>
       </c>
     </row>
     <row r="19">
@@ -4809,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4818,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>10.363</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="20">
@@ -4829,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4841,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.731</v>
+        <v>2.734</v>
       </c>
     </row>
     <row r="21">
@@ -4849,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4858,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
-        <v>5.488</v>
+        <v>16.709</v>
       </c>
     </row>
     <row r="22">
@@ -4869,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4878,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
-        <v>5.208</v>
+        <v>13.466</v>
       </c>
     </row>
     <row r="23">
@@ -4889,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4898,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>2.702</v>
+        <v>7.116</v>
       </c>
     </row>
     <row r="24">
@@ -4909,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4921,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.728</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="25">
@@ -4929,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4938,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>11.432</v>
+        <v>4.457</v>
       </c>
     </row>
     <row r="26">
@@ -4949,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4958,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>15.660</v>
+        <v>7.804</v>
       </c>
     </row>
     <row r="27">
@@ -4969,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4978,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" t="str">
-        <v>2.457</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="28">
@@ -4989,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4998,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>13.964</v>
+        <v>2.686</v>
       </c>
     </row>
     <row r="29">
@@ -5009,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -5018,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>13.366</v>
+        <v>6.016</v>
       </c>
     </row>
     <row r="30">
@@ -5029,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -5041,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.735</v>
+        <v>2.987</v>
       </c>
     </row>
     <row r="31">
@@ -5049,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -5061,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.947</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="32">
@@ -5069,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -5078,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.831</v>
+        <v>5.627</v>
       </c>
     </row>
     <row r="33">
@@ -5089,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -5098,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="str">
-        <v>2.757</v>
+        <v>12.035</v>
       </c>
     </row>
     <row r="34">
@@ -5121,7 +4981,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>4.962</v>
+        <v>4.893</v>
       </c>
     </row>
     <row r="35">
@@ -5129,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MIRTILLO</v>
+        <v>MELONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -5141,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.835</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="36">
@@ -5149,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -5158,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>9.252</v>
+        <v>2.359</v>
       </c>
     </row>
     <row r="37">
@@ -5169,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -5178,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>14.936</v>
+        <v>9.332</v>
       </c>
     </row>
     <row r="38">
@@ -5189,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -5198,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F38" t="str">
-        <v>3.065</v>
+        <v>17.449</v>
       </c>
     </row>
     <row r="39">
@@ -5209,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5218,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>4.989</v>
+        <v>2.906</v>
       </c>
     </row>
     <row r="40">
@@ -5229,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5238,10 +5098,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.883</v>
+        <v>2.874</v>
       </c>
     </row>
     <row r="41">
@@ -5249,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5258,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>7.449</v>
+        <v>2.452</v>
       </c>
     </row>
     <row r="42">
@@ -5269,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PERA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5278,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>19.953</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="43">
@@ -5289,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>POLLICINA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5301,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.900</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="44">
@@ -5309,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5321,7 +5181,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>5.991</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="45">
@@ -5329,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5338,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.951</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="46">
@@ -5349,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>SEADAS</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5361,7 +5221,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.982</v>
+        <v>5.808</v>
       </c>
     </row>
     <row r="47">
@@ -5369,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5378,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>28.271</v>
+        <v>2.980</v>
       </c>
     </row>
     <row r="48">
@@ -5389,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5398,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F48" t="str">
-        <v>5.911</v>
+        <v>27.744</v>
       </c>
     </row>
     <row r="49">
@@ -5409,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>UVA E NOCI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5421,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.240</v>
+        <v>2.789</v>
       </c>
     </row>
     <row r="50">
@@ -5438,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.766</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="51">
@@ -5449,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PENSIERO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5458,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="str">
-        <v>4.435</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="52">
@@ -5469,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SACRIPANTE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5481,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>3.046</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="53">
@@ -5489,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5498,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.682</v>
+        <v>6.131</v>
       </c>
     </row>
     <row r="54">
@@ -5509,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>CARROT CAKE</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5518,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>2.765</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="55">
@@ -5529,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5538,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>2.594</v>
+        <v>5.615</v>
       </c>
     </row>
     <row r="56">
@@ -5549,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5558,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>3.114</v>
+        <v>16.969</v>
       </c>
     </row>
     <row r="57">
@@ -5569,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>MONT BLANC</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5581,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>3.102</v>
+        <v>2.225</v>
       </c>
     </row>
     <row r="58">
@@ -5589,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5601,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>2.356</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="59">
@@ -5609,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5618,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>2.708</v>
+        <v>6.070</v>
       </c>
     </row>
     <row r="60">
@@ -5629,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>COCCO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5641,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.085</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="61">
@@ -5649,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5661,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>993</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="62">
@@ -5669,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5678,10 +5538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>3.006</v>
+        <v>6.080</v>
       </c>
     </row>
     <row r="63">
@@ -5689,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5701,7 +5561,7 @@
         <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>5.733</v>
+        <v>6.454</v>
       </c>
     </row>
     <row r="64">
@@ -5709,7 +5569,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5718,10 +5578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.565</v>
+        <v>2.905</v>
       </c>
     </row>
     <row r="65">
@@ -5729,7 +5589,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5738,10 +5598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>9.827</v>
+        <v>2.698</v>
       </c>
     </row>
     <row r="66">
@@ -5749,7 +5609,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5758,10 +5618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F66" t="str">
-        <v>3.109</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="67">
@@ -5769,7 +5629,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -5778,10 +5638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" t="str">
-        <v>14.521</v>
+        <v>5.919</v>
       </c>
     </row>
     <row r="68">
@@ -5789,7 +5649,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -5798,10 +5658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F68" t="str">
-        <v>5.775</v>
+        <v>22.823</v>
       </c>
     </row>
     <row r="69">
@@ -5821,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.758</v>
+        <v>3.190</v>
       </c>
     </row>
   </sheetData>
@@ -5833,7 +5693,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5865,7 +5725,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -5887,7 +5747,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5898,7 +5758,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -5909,7 +5769,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5920,7 +5780,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5931,7 +5791,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5942,7 +5802,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5964,7 +5824,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5975,12 +5835,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5991,18 +5851,18 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
@@ -6013,7 +5873,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
@@ -6024,29 +5884,29 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -6057,35 +5917,35 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6096,7 +5956,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -6118,7 +5978,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -6140,7 +6000,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -6151,7 +6011,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -6162,56 +6022,56 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>LEMON CURD</v>
+        <v>LIMONE</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LIMONE</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
@@ -6222,29 +6082,29 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -6255,18 +6115,18 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
@@ -6277,7 +6137,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MORA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6288,7 +6148,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -6299,18 +6159,18 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -6321,7 +6181,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>MORA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
@@ -6332,18 +6192,18 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
@@ -6354,7 +6214,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -6365,7 +6225,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6376,18 +6236,18 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
@@ -6398,40 +6258,40 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PERA</v>
+        <v>SEADAS</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
@@ -6442,7 +6302,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
@@ -6453,62 +6313,62 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>YOGURT</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6519,18 +6379,18 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -6541,18 +6401,18 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>CARROT CAKE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -6563,7 +6423,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
@@ -6574,29 +6434,29 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
@@ -6607,18 +6467,18 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>MONT BLANC</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
@@ -6629,18 +6489,18 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SACHER TORTE</v>
+        <v>FASHIONED SPRITZ</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
@@ -6651,84 +6511,84 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>BAKLAVA</v>
+        <v>MELONE</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
@@ -6739,40 +6599,40 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>COCCO CREMA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MIRTILLO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6783,18 +6643,18 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6805,35 +6665,35 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>TIRAMISU'</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>YOGURT</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C90" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>PENSIERO</v>
+        <v>COCCO</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -6849,29 +6709,29 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C94" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>MANDARINO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
@@ -6882,29 +6742,29 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C96" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ALBICOCCA</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6915,18 +6775,18 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6937,18 +6797,18 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C101" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>CACHI</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
@@ -6959,18 +6819,18 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C103" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
@@ -6981,7 +6841,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>CACHI</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6992,18 +6852,18 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
@@ -7014,7 +6874,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FICHI</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -7025,29 +6885,18 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C109" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
-      </c>
-      <c r="B110" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C110" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 26-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 03-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -537,7 +537,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -548,8 +548,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>3</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -625,7 +625,7 @@
         <v/>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -636,8 +636,8 @@
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
-        <v/>
+      <c r="L5">
+        <v>1</v>
       </c>
       <c r="M5" t="str">
         <v>ANGURIA</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -662,8 +662,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -749,7 +749,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>2</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -824,8 +824,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>3</v>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -924,8 +924,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>2</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>1</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1036,8 +1036,8 @@
       <c r="K13" t="str">
         <v/>
       </c>
-      <c r="L13" t="str">
-        <v/>
+      <c r="L13">
+        <v>1</v>
       </c>
       <c r="M13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1336,8 +1336,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19">
-        <v>2</v>
+      <c r="L19" t="str">
+        <v/>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1362,8 +1362,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>2</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1386,8 +1386,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20">
-        <v>2</v>
+      <c r="L20" t="str">
+        <v/>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1486,8 +1486,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22" t="str">
-        <v/>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1562,8 +1562,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>3</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1698,8 +1698,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26">
-        <v>3</v>
+      <c r="P26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1712,8 +1712,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="D27">
+        <v>3</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1762,8 +1762,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="D28">
+        <v>9</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1798,8 +1798,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28">
-        <v>1</v>
+      <c r="P28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1812,8 +1812,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29" t="str">
-        <v/>
+      <c r="D29">
+        <v>1</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1862,8 +1862,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30">
-        <v>2</v>
+      <c r="D30" t="str">
+        <v/>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1898,8 +1898,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1912,8 +1912,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="D31">
+        <v>1</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>2</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1998,8 +1998,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32" t="str">
-        <v/>
+      <c r="P32">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2013,7 +2013,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>2</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2098,8 +2098,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34" t="str">
-        <v/>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2162,8 +2162,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36" t="str">
-        <v/>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2449,7 +2449,7 @@
         <v/>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>4.239</v>
+        <v>2.495</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>4.837</v>
+        <v>6.457</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F4" t="str">
-        <v>5.207</v>
+        <v>23.822</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>10.754</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>5.841</v>
+        <v>2.733</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +2938,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.219</v>
+        <v>5.698</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.696</v>
+        <v>5.560</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>5.419</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>2.538</v>
+        <v>4.842</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>6.929</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>7.424</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="str">
-        <v>8.371</v>
+        <v>11.998</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>2.952</v>
+        <v>3.248</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>8.950</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3130,7 +3130,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>4.977</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>6.236</v>
+        <v>8.765</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3167,10 +3167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>3.044</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>11.796</v>
+        <v>4.853</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>3.102</v>
+        <v>10.138</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.716</v>
+        <v>4.819</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>4.828</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>2.682</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>2.555</v>
+        <v>11.152</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3310,7 +3310,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>7.485</v>
+        <v>6.465</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>2.633</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>ESTASI</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3350,7 +3350,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>5.766</v>
+        <v>6.128</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FIORDILATTE</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3370,7 +3370,7 @@
         <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>7.984</v>
+        <v>8.377</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>13.265</v>
+        <v>10.422</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>4.668</v>
+        <v>3.150</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>2.115</v>
+        <v>5.746</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>8.377</v>
+        <v>6.054</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LEMON CURD</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="str">
-        <v>4.975</v>
+        <v>6.989</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>LIMONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="str">
-        <v>9.799</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MELONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.993</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3527,10 +3527,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>2.794</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>5.985</v>
+        <v>2.987</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>5.840</v>
+        <v>12.097</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.394</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MIRTILLO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3610,7 +3610,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>4.784</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>MORA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>2.319</v>
+        <v>4.780</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>6.045</v>
+        <v>5.097</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>NOCCIOLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" t="str">
-        <v>14.305</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>8.681</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.218</v>
+        <v>2.922</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PERA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.508</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>8.440</v>
+        <v>5.503</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48" t="str">
-        <v>6.897</v>
+        <v>16.810</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F49" t="str">
-        <v>17.644</v>
+        <v>13.450</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>11.632</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>YOGURT</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>8.326</v>
+        <v>5.804</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3847,10 +3847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>3.045</v>
+        <v>5.497</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>19.546</v>
+        <v>5.047</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>TIRAMISU'</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="str">
-        <v>5.612</v>
+        <v>8.762</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.522</v>
+        <v>2.670</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>3.164</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F57" t="str">
-        <v>5.744</v>
+        <v>20.200</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>PENSIERO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>4.858</v>
+        <v>2.595</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>SACRIPANTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>3.022</v>
+        <v>5.801</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4010,7 +4010,7 @@
         <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>5.259</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.467</v>
+        <v>2.610</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>CARROT CAKE</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>5.564</v>
+        <v>6.005</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +4067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>40.350</v>
+        <v>2.119</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4090,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>5.226</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
-        <v>2.808</v>
+        <v>6.296</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.958</v>
+        <v>3.151</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>SACHER TORTE</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +4147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F67" t="str">
-        <v>7.985</v>
+        <v>26.296</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4167,10 +4167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E68" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="str">
-        <v>5.659</v>
+        <v>11.802</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4187,10 +4187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E69" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>1.078</v>
+        <v>3.004</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4207,102 +4207,22 @@
         <v>Mantenimento</v>
       </c>
       <c r="E70" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="str">
-        <v>3.251</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E71" t="str">
-        <v>1</v>
-      </c>
-      <c r="F71" t="str">
-        <v>2.793</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E72" t="str">
-        <v>3</v>
-      </c>
-      <c r="F72" t="str">
-        <v>8.578</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B73" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="D73" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E73" t="str">
-        <v>3</v>
-      </c>
-      <c r="F73" t="str">
-        <v>8.843</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B74" t="str">
-        <v>FASHIONED SPRITZ</v>
-      </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="D74" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E74" t="str">
-        <v>1</v>
-      </c>
-      <c r="F74" t="str">
-        <v>1.985</v>
+        <v>5.807</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4329,7 +4249,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -4341,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.439</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="3">
@@ -4349,7 +4269,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -4358,10 +4278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>5.440</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="4">
@@ -4369,7 +4289,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4378,10 +4298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>3.461</v>
+        <v>7.948</v>
       </c>
     </row>
     <row r="5">
@@ -4389,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4398,10 +4318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>30.049</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4418,10 +4338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>6.362</v>
+        <v>26.282</v>
       </c>
     </row>
     <row r="7">
@@ -4429,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4441,7 +4361,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>6.132</v>
+        <v>4.333</v>
       </c>
     </row>
     <row r="8">
@@ -4449,7 +4369,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4461,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>8.751</v>
+        <v>8.470</v>
       </c>
     </row>
     <row r="9">
@@ -4469,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4478,10 +4398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>2.696</v>
+        <v>8.134</v>
       </c>
     </row>
     <row r="10">
@@ -4489,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4501,7 +4421,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.483</v>
+        <v>5.158</v>
       </c>
     </row>
     <row r="11">
@@ -4509,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4518,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>11.679</v>
+        <v>3.482</v>
       </c>
     </row>
     <row r="12">
@@ -4529,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4538,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>12.121</v>
+        <v>14.212</v>
       </c>
     </row>
     <row r="13">
@@ -4549,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4561,7 +4481,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>8.750</v>
+        <v>7.744</v>
       </c>
     </row>
     <row r="14">
@@ -4569,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4578,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>5.700</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="15">
@@ -4589,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4598,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>7.782</v>
+        <v>12.419</v>
       </c>
     </row>
     <row r="16">
@@ -4609,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4618,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>5.448</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="17">
@@ -4629,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4641,7 +4561,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>5.560</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="18">
@@ -4649,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4658,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>5.340</v>
+        <v>7.328</v>
       </c>
     </row>
     <row r="19">
@@ -4669,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4681,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.860</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="20">
@@ -4689,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4698,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>2.734</v>
+        <v>5.388</v>
       </c>
     </row>
     <row r="21">
@@ -4709,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4718,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>16.709</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="22">
@@ -4729,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4738,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>13.466</v>
+        <v>5.459</v>
       </c>
     </row>
     <row r="23">
@@ -4749,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4761,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>7.116</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="24">
@@ -4769,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4781,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>3.158</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="25">
@@ -4789,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4798,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="str">
-        <v>4.457</v>
+        <v>13.484</v>
       </c>
     </row>
     <row r="26">
@@ -4809,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4818,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <v>7.804</v>
+        <v>13.432</v>
       </c>
     </row>
     <row r="27">
@@ -4829,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4838,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>11.679</v>
+        <v>9.271</v>
       </c>
     </row>
     <row r="28">
@@ -4849,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4861,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>2.686</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="29">
@@ -4869,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4878,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>6.016</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="30">
@@ -4889,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4901,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.987</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="31">
@@ -4909,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4918,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" t="str">
-        <v>3.014</v>
+        <v>12.282</v>
       </c>
     </row>
     <row r="32">
@@ -4929,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4938,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>5.627</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="33">
@@ -4949,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4958,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>12.035</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="34">
@@ -4969,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4978,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>4.893</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="35">
@@ -4989,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MELONE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4998,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.572</v>
+        <v>6.111</v>
       </c>
     </row>
     <row r="36">
@@ -5009,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -5021,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.359</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="37">
@@ -5029,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -5038,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>9.332</v>
+        <v>2.509</v>
       </c>
     </row>
     <row r="38">
@@ -5049,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA</v>
+        <v>MELONE</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -5058,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>17.449</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="39">
@@ -5069,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MORA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5081,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.906</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="40">
@@ -5089,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5098,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="str">
-        <v>2.874</v>
+        <v>8.818</v>
       </c>
     </row>
     <row r="41">
@@ -5109,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5118,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F41" t="str">
-        <v>2.452</v>
+        <v>17.373</v>
       </c>
     </row>
     <row r="42">
@@ -5129,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5141,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>5.009</v>
+        <v>6.043</v>
       </c>
     </row>
     <row r="43">
@@ -5149,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5161,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.542</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="44">
@@ -5169,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>POLLICINA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5178,10 +5098,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>5.595</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="45">
@@ -5189,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5201,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.137</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="46">
@@ -5209,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5221,7 +5141,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.808</v>
+        <v>4.971</v>
       </c>
     </row>
     <row r="47">
@@ -5229,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5238,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>2.980</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="48">
@@ -5249,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5258,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" t="str">
-        <v>27.744</v>
+        <v>32.276</v>
       </c>
     </row>
     <row r="49">
@@ -5269,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>TIRAMISU'</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5281,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.789</v>
+        <v>2.418</v>
       </c>
     </row>
     <row r="50">
@@ -5289,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>YOGURT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5298,10 +5218,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.731</v>
+        <v>5.670</v>
       </c>
     </row>
     <row r="51">
@@ -5309,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5318,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>8.984</v>
+        <v>2.503</v>
       </c>
     </row>
     <row r="52">
@@ -5329,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PENSIERO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5341,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.254</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="53">
@@ -5349,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>SACRIPANTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5358,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F53" t="str">
-        <v>6.131</v>
+        <v>31.117</v>
       </c>
     </row>
     <row r="54">
@@ -5369,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5378,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>5.805</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="55">
@@ -5389,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>YOGURT</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5398,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>5.615</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="56">
@@ -5409,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5418,10 +5338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>16.969</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="57">
@@ -5429,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5438,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E57" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>2.225</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="58">
@@ -5449,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5458,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>3.158</v>
+        <v>7.920</v>
       </c>
     </row>
     <row r="59">
@@ -5469,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>MONT BLANC</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5478,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>6.070</v>
+        <v>8.344</v>
       </c>
     </row>
     <row r="60">
@@ -5489,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>COCCO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5501,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.195</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="61">
@@ -5509,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5518,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F61" t="str">
-        <v>2.142</v>
+        <v>20.371</v>
       </c>
     </row>
     <row r="62">
@@ -5529,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5538,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>6.080</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="63">
@@ -5549,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5558,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>6.454</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="64">
@@ -5569,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5581,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.905</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
@@ -5589,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5601,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>2.698</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="66">
@@ -5609,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5618,10 +5538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>4.212</v>
+        <v>2.897</v>
       </c>
     </row>
     <row r="67">
@@ -5629,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -5638,10 +5558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>5.919</v>
+        <v>992</v>
       </c>
     </row>
     <row r="68">
@@ -5649,7 +5569,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -5658,10 +5578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>22.823</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="69">
@@ -5669,31 +5589,91 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5.181</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>8</v>
+      </c>
+      <c r="F70" t="str">
+        <v>4.276</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>6.620</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E69" t="str">
-        <v>1</v>
-      </c>
-      <c r="F69" t="str">
-        <v>3.190</v>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>6.103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F72"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C112"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5708,117 +5688,117 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ANGURIA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
@@ -5829,29 +5809,29 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
@@ -5862,29 +5842,29 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5895,18 +5875,18 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -5917,73 +5897,73 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>ESTASI</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ESTASI</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -5994,40 +5974,40 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FIORDILATTE</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -6038,18 +6018,18 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LEMON CURD</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -6060,73 +6040,73 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>LIMONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MELONE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MIRTILLO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
@@ -6137,7 +6117,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MORA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6148,7 +6128,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -6159,18 +6139,18 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>NOCCIOLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C43" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -6181,51 +6161,51 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PERA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6236,7 +6216,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6247,73 +6227,73 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>YOGURT</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>TIRAMISU'</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -6324,29 +6304,29 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>PENSIERO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SACRIPANTE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
@@ -6357,7 +6337,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6368,7 +6348,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>CARROT CAKE</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6379,7 +6359,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
@@ -6390,40 +6370,40 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SACHER TORTE</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
@@ -6434,106 +6414,106 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>AMARENA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>FASHIONED SPRITZ</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
@@ -6544,29 +6524,29 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>GIANDUIA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
@@ -6577,18 +6557,18 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MELONE</v>
+        <v>MORA</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
@@ -6599,40 +6579,40 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>POLLICINA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6643,7 +6623,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>SEADAS</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
@@ -6654,7 +6634,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6665,7 +6645,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
@@ -6676,7 +6656,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MONT BLANC</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6687,7 +6667,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>COCCO</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
@@ -6698,7 +6678,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
@@ -6709,18 +6689,18 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6731,40 +6711,40 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C96" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>BAKLAVA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>COCCO</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6775,7 +6755,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>MANDARINO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6786,7 +6766,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6797,18 +6777,18 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C101" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ALBICOCCA</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
@@ -6819,7 +6799,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
@@ -6830,7 +6810,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
@@ -6841,29 +6821,29 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>CACHI</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C105" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CIOCCOLATO</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
@@ -6874,7 +6854,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -6885,18 +6865,51 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>CACHI</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C109" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>CIOCCOLATO</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C110" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C111" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C112" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C112"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 03-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 10-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>5</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -474,8 +474,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>5</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>3</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -625,7 +625,7 @@
         <v/>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>4</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -674,8 +674,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6">
-        <v>2</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -699,7 +699,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>2</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>3</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -786,8 +786,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>4</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -824,8 +824,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9">
-        <v>3</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -912,8 +912,8 @@
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11" t="str">
         <v>LEMON CURD</v>
@@ -925,7 +925,7 @@
         <v/>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1186,8 +1186,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16" t="str">
-        <v/>
+      <c r="L16">
+        <v>1</v>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1312,8 +1312,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="D19">
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1336,8 +1336,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v/>
+      <c r="L19">
+        <v>2</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1362,8 +1362,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20">
-        <v>2</v>
+      <c r="D20" t="str">
+        <v/>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>2</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1487,7 +1487,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1498,8 +1498,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>3</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1713,7 +1713,7 @@
         <v/>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1848,8 +1848,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29" t="str">
-        <v/>
+      <c r="P29">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1913,7 +1913,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1999,7 +1999,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2013,7 +2013,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>1</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2212,8 +2212,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>2</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2348,8 +2348,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39">
-        <v>2</v>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2448,8 +2448,8 @@
       <c r="O41" t="str">
         <v/>
       </c>
-      <c r="P41">
-        <v>2</v>
+      <c r="P41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2512,8 +2512,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.495</v>
+        <v>2.165</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>6.457</v>
+        <v>4.696</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>23.822</v>
+        <v>7.547</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BANANA E LIME</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="str">
-        <v>2.093</v>
+        <v>14.219</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>2.733</v>
+        <v>6.457</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +2938,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>5.698</v>
+        <v>17.384</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CAFFE'</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>5.560</v>
+        <v>6.389</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>3.486</v>
+        <v>11.476</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>4.842</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="11">
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
-        <v>3.118</v>
+        <v>18.056</v>
       </c>
     </row>
     <row r="12">
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>11.998</v>
+        <v>6.092</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>3.248</v>
+        <v>9.562</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3110,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.044</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>6.036</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="str">
-        <v>8.765</v>
+        <v>11.928</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3167,10 +3167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E18" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>8.416</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="19">
@@ -3190,7 +3190,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>4.853</v>
+        <v>5.080</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>10.138</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="21">
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>4.819</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>2.455</v>
+        <v>7.681</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.766</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="24">
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="str">
-        <v>11.152</v>
+        <v>13.900</v>
       </c>
     </row>
     <row r="25">
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>6.465</v>
+        <v>13.353</v>
       </c>
     </row>
     <row r="26">
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>7.038</v>
+        <v>4.710</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3347,10 +3347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>6.128</v>
+        <v>8.359</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" t="str">
-        <v>8.377</v>
+        <v>13.224</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>10.422</v>
+        <v>2.930</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>3.150</v>
+        <v>5.779</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.746</v>
+        <v>2.779</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3450,7 +3450,7 @@
         <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>6.054</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>6.989</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="34">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MIRTILLO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>4.784</v>
+        <v>5.866</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" t="str">
-        <v>2.987</v>
+        <v>14.583</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>12.097</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.891</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.105</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="41">
@@ -3647,10 +3647,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>5.097</v>
+        <v>2.259</v>
       </c>
     </row>
     <row r="43">
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>6.897</v>
+        <v>4.641</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F44" t="str">
-        <v>5.628</v>
+        <v>17.001</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.922</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>2.518</v>
+        <v>4.237</v>
       </c>
     </row>
     <row r="47">
@@ -3750,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>5.503</v>
+        <v>5.240</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>16.810</v>
+        <v>5.776</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="str">
-        <v>13.450</v>
+        <v>16.306</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50" t="str">
-        <v>3.164</v>
+        <v>13.450</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>YOGURT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3830,7 +3830,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>5.804</v>
+        <v>4.648</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>YOGURT</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>5.497</v>
+        <v>6.205</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PENSIERO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3870,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>5.047</v>
+        <v>5.497</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>SACRIPANTE</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>8.762</v>
+        <v>2.011</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>2.670</v>
+        <v>5.246</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>2.675</v>
+        <v>5.740</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>20.200</v>
+        <v>2.584</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3970,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>2.595</v>
+        <v>2.672</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3990,7 +3990,7 @@
         <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>5.801</v>
+        <v>5.802</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4010,7 +4010,7 @@
         <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>5.737</v>
+        <v>5.951</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.610</v>
+        <v>2.897</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>6.005</v>
+        <v>2.382</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.119</v>
+        <v>3.095</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4090,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>1.078</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>6.296</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>3.151</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +4147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>26.296</v>
+        <v>2.119</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4167,10 +4167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E68" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>11.802</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>3.004</v>
+        <v>2.418</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4207,22 +4207,42 @@
         <v>Mantenimento</v>
       </c>
       <c r="E70" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F70" t="str">
-        <v>5.807</v>
+        <v>14.193</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E71" t="str">
+        <v>4</v>
+      </c>
+      <c r="F71" t="str">
+        <v>11.802</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F71"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4261,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.125</v>
+        <v>2.114</v>
       </c>
     </row>
     <row r="3">
@@ -4278,10 +4298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>7.472</v>
+        <v>4.939</v>
       </c>
     </row>
     <row r="4">
@@ -4289,7 +4309,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4298,10 +4318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>7.948</v>
+        <v>26.587</v>
       </c>
     </row>
     <row r="5">
@@ -4309,7 +4329,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4318,10 +4338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>10.754</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="6">
@@ -4329,7 +4349,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4338,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>26.282</v>
+        <v>5.577</v>
       </c>
     </row>
     <row r="7">
@@ -4349,7 +4369,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4358,10 +4378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>4.333</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="8">
@@ -4369,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4381,7 +4401,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>8.470</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="9">
@@ -4389,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4398,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>8.134</v>
+        <v>3.443</v>
       </c>
     </row>
     <row r="10">
@@ -4409,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4418,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>5.158</v>
+        <v>7.424</v>
       </c>
     </row>
     <row r="11">
@@ -4429,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4438,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>3.482</v>
+        <v>6.053</v>
       </c>
     </row>
     <row r="12">
@@ -4449,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4458,10 +4478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>14.212</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="13">
@@ -4478,10 +4498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>7.744</v>
+        <v>2.580</v>
       </c>
     </row>
     <row r="14">
@@ -4501,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.000</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="15">
@@ -4518,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>12.419</v>
+        <v>9.110</v>
       </c>
     </row>
     <row r="16">
@@ -4538,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="str">
-        <v>11.796</v>
+        <v>8.765</v>
       </c>
     </row>
     <row r="17">
@@ -4549,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4558,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>5.319</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="18">
@@ -4569,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4581,7 +4601,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>7.328</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="19">
@@ -4589,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4598,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.754</v>
+        <v>5.094</v>
       </c>
     </row>
     <row r="20">
@@ -4609,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4618,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>5.388</v>
+        <v>10.138</v>
       </c>
     </row>
     <row r="21">
@@ -4629,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4641,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.352</v>
+        <v>2.677</v>
       </c>
     </row>
     <row r="22">
@@ -4649,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4658,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>5.459</v>
+        <v>2.633</v>
       </c>
     </row>
     <row r="23">
@@ -4669,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4681,7 +4701,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>7.485</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="24">
@@ -4689,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4698,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>2.626</v>
+        <v>11.119</v>
       </c>
     </row>
     <row r="25">
@@ -4709,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4718,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>13.484</v>
+        <v>12.893</v>
       </c>
     </row>
     <row r="26">
@@ -4729,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4738,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>13.432</v>
+        <v>7.201</v>
       </c>
     </row>
     <row r="27">
@@ -4749,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4758,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>9.271</v>
+        <v>3.199</v>
       </c>
     </row>
     <row r="28">
@@ -4769,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4781,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>3.090</v>
+        <v>2.056</v>
       </c>
     </row>
     <row r="29">
@@ -4789,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4801,7 +4821,7 @@
         <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>6.519</v>
+        <v>8.377</v>
       </c>
     </row>
     <row r="30">
@@ -4821,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.499</v>
+        <v>2.476</v>
       </c>
     </row>
     <row r="31">
@@ -4838,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" t="str">
-        <v>12.282</v>
+        <v>10.383</v>
       </c>
     </row>
     <row r="32">
@@ -4861,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>3.077</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="33">
@@ -4878,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.735</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="34">
@@ -4898,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.873</v>
+        <v>5.561</v>
       </c>
     </row>
     <row r="35">
@@ -4918,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>6.111</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="36">
@@ -4929,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4938,10 +4958,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" t="str">
-        <v>2.567</v>
+        <v>14.701</v>
       </c>
     </row>
     <row r="37">
@@ -4949,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4961,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.509</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="38">
@@ -4969,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELONE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4978,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.624</v>
+        <v>5.992</v>
       </c>
     </row>
     <row r="39">
@@ -4989,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MORA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -4998,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F39" t="str">
-        <v>2.319</v>
+        <v>14.681</v>
       </c>
     </row>
     <row r="40">
@@ -5009,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5018,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>8.818</v>
+        <v>5.196</v>
       </c>
     </row>
     <row r="41">
@@ -5029,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5038,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>17.373</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="42">
@@ -5049,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5058,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>6.043</v>
+        <v>2.771</v>
       </c>
     </row>
     <row r="43">
@@ -5069,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5081,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.664</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="44">
@@ -5089,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5098,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>2.651</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="45">
@@ -5109,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5121,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.444</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="46">
@@ -5129,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PERA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5141,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>4.971</v>
+        <v>5.823</v>
       </c>
     </row>
     <row r="47">
@@ -5149,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5158,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>5.590</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="48">
@@ -5169,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5178,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F48" t="str">
-        <v>32.276</v>
+        <v>27.870</v>
       </c>
     </row>
     <row r="49">
@@ -5189,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5201,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.418</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="50">
@@ -5209,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5218,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.670</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="51">
@@ -5229,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5238,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.503</v>
+        <v>5.220</v>
       </c>
     </row>
     <row r="52">
@@ -5249,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SEADAS</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5258,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.892</v>
+        <v>5.282</v>
       </c>
     </row>
     <row r="53">
@@ -5269,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>STRACCIATELLA</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5278,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>31.117</v>
+        <v>2.732</v>
       </c>
     </row>
     <row r="54">
@@ -5289,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>UVA E NOCI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5298,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" t="str">
-        <v>2.522</v>
+        <v>14.270</v>
       </c>
     </row>
     <row r="55">
@@ -5309,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>YOGURT</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5321,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.805</v>
+        <v>2.634</v>
       </c>
     </row>
     <row r="56">
@@ -5329,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5338,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>3.014</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="57">
@@ -5349,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PENSIERO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5358,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E57" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>4.684</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="58">
@@ -5369,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5378,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>7.920</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="59">
@@ -5389,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5398,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>8.344</v>
+        <v>2.809</v>
       </c>
     </row>
     <row r="60">
@@ -5409,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5418,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>2.832</v>
+        <v>5.426</v>
       </c>
     </row>
     <row r="61">
@@ -5429,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5438,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>20.371</v>
+        <v>2.928</v>
       </c>
     </row>
     <row r="62">
@@ -5449,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5458,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>2.592</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="63">
@@ -5469,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5481,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.681</v>
+        <v>2.954</v>
       </c>
     </row>
     <row r="64">
@@ -5489,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5498,10 +5518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F64" t="str">
-        <v>250</v>
+        <v>23.481</v>
       </c>
     </row>
     <row r="65">
@@ -5509,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5518,10 +5538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
-        <v>3.125</v>
+        <v>5.828</v>
       </c>
     </row>
     <row r="66">
@@ -5529,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5541,139 +5561,19 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.897</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B67" t="str">
-        <v>TORTA CAPRESE</v>
-      </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E67" t="str">
-        <v>1</v>
-      </c>
-      <c r="F67" t="str">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B68" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E68" t="str">
-        <v>2</v>
-      </c>
-      <c r="F68" t="str">
-        <v>5.421</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B69" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E69" t="str">
-        <v>2</v>
-      </c>
-      <c r="F69" t="str">
-        <v>5.181</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B70" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E70" t="str">
-        <v>8</v>
-      </c>
-      <c r="F70" t="str">
-        <v>4.276</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E71" t="str">
-        <v>2</v>
-      </c>
-      <c r="F71" t="str">
-        <v>6.620</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E72" t="str">
-        <v>2</v>
-      </c>
-      <c r="F72" t="str">
-        <v>6.103</v>
+        <v>2.973</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5688,73 +5588,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BANANA E LIME</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CAFFE'</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
@@ -5765,24 +5665,24 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5793,7 +5693,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5820,57 +5720,57 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -5886,7 +5786,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -5903,29 +5803,29 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5936,7 +5836,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -5947,7 +5847,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -5958,12 +5858,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -5974,29 +5874,29 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIMONE</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LIMONE</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
@@ -6007,7 +5907,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -6018,7 +5918,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
@@ -6029,7 +5929,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
@@ -6062,57 +5962,57 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MIRTILLO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6150,29 +6050,29 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
@@ -6194,29 +6094,29 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6227,18 +6127,18 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>YOGURT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>YOGURT</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
@@ -6249,18 +6149,18 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PENSIERO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SACRIPANTE</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
@@ -6271,117 +6171,117 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SACHER TORTE</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
@@ -6392,18 +6292,18 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
@@ -6414,117 +6314,117 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>AMARENA</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ANGURIA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>ESTASI</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
@@ -6535,29 +6435,29 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>LEMON CURD</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
@@ -6568,18 +6468,18 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MORA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PAPAYA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
@@ -6596,45 +6496,45 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SEADAS</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>UVA E NOCI</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6645,18 +6545,18 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CARROT CAKE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6667,62 +6567,62 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C94" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>MORA</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6733,18 +6633,18 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>MONT BLANC</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>COCCO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6755,18 +6655,18 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>BAKLAVA</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6777,7 +6677,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>COCCO</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6788,18 +6688,18 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
@@ -6810,7 +6710,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>MANDARINO</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
@@ -6821,18 +6721,18 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C105" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ALBICOCCA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
@@ -6843,18 +6743,18 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C107" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -6865,7 +6765,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>CACHI</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -6876,7 +6776,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>CIOCCOLATO</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
@@ -6887,7 +6787,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>CACHI</v>
       </c>
       <c r="B111" t="str">
         <v>Da Ordinare</v>
@@ -6898,18 +6798,29 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B112" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C112" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C113" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C113"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 10-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 17-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>3</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -536,8 +536,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -562,8 +562,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4">
-        <v>3</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>4</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -624,8 +624,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5">
-        <v>2</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -663,7 +663,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -699,7 +699,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -725,7 +725,7 @@
         <v/>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>4</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -775,7 +775,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -786,8 +786,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8" t="str">
-        <v/>
+      <c r="L8">
+        <v>3</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -925,7 +925,7 @@
         <v/>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>3</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -998,8 +998,8 @@
       <c r="O12" t="str">
         <v/>
       </c>
-      <c r="P12">
-        <v>1</v>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1136,8 +1136,8 @@
       <c r="K15" t="str">
         <v/>
       </c>
-      <c r="L15">
-        <v>4</v>
+      <c r="L15" t="str">
+        <v/>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1162,8 +1162,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>4</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1213,7 +1213,7 @@
         <v/>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>3</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1262,8 +1262,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18">
-        <v>1</v>
+      <c r="D18" t="str">
+        <v/>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>1</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1313,7 +1313,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1412,8 +1412,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1487,7 +1487,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1562,8 +1562,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24">
-        <v>1</v>
+      <c r="D24" t="str">
+        <v/>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>6</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1712,8 +1712,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>2</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1762,8 +1762,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28">
-        <v>2</v>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1899,7 +1899,7 @@
         <v/>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1913,7 +1913,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1999,7 +1999,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2198,8 +2198,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36" t="str">
-        <v/>
+      <c r="P36">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2212,8 +2212,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37" t="str">
-        <v/>
+      <c r="D37">
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2512,8 +2512,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43" t="str">
-        <v/>
+      <c r="D43">
+        <v>2</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2850,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.165</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="3">
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>4.696</v>
+        <v>2.417</v>
       </c>
     </row>
     <row r="4">
@@ -2907,10 +2907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>14.219</v>
+        <v>5.597</v>
       </c>
     </row>
     <row r="6">
@@ -2950,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>17.384</v>
+        <v>17.517</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>6.389</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>11.476</v>
+        <v>4.340</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>2.731</v>
+        <v>8.214</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>18.056</v>
+        <v>2.923</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="str">
-        <v>2.952</v>
+        <v>11.471</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>6.092</v>
+        <v>3.697</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>9.562</v>
+        <v>9.994</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>3.135</v>
+        <v>8.845</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.044</v>
+        <v>6.290</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>11.928</v>
+        <v>6.191</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.916</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>5.080</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>4.962</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3230,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.708</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>7.681</v>
+        <v>3.020</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F23" t="str">
-        <v>2.602</v>
+        <v>26.188</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>13.900</v>
+        <v>8.402</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>COCCO AL RUM</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>13.353</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>4.710</v>
+        <v>5.171</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3347,10 +3347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="str">
-        <v>8.359</v>
+        <v>7.765</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMONE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>13.224</v>
+        <v>5.409</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3390,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>2.930</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="str">
-        <v>5.779</v>
+        <v>7.681</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.779</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>ESTASI</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="str">
-        <v>5.682</v>
+        <v>9.571</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v>5.738</v>
+        <v>11.470</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" t="str">
-        <v>7.192</v>
+        <v>10.899</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MELONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="str">
-        <v>4.713</v>
+        <v>7.008</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3527,10 +3527,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" t="str">
-        <v>5.866</v>
+        <v>8.359</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" t="str">
-        <v>14.583</v>
+        <v>10.737</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>2.964</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>5.105</v>
+        <v>8.014</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PAPAYA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.253</v>
+        <v>5.991</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3630,7 +3630,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>4.780</v>
+        <v>5.826</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PERA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.259</v>
+        <v>2.865</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F43" t="str">
-        <v>4.641</v>
+        <v>15.812</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>17.001</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>POLLICINA</v>
+        <v>MELONE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3710,7 +3710,7 @@
         <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>5.628</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>4.237</v>
+        <v>2.758</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" t="str">
-        <v>5.240</v>
+        <v>11.516</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>SEADAS</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>5.776</v>
+        <v>3.243</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>STRACCIATELLA</v>
+        <v>NOCI  E UVETTA DI CORINTO</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>16.306</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>TIRAMISU'</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3807,10 +3807,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E50" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>13.450</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>UVA E NOCI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3830,7 +3830,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>4.648</v>
+        <v>4.780</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>YOGURT</v>
+        <v>PERA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>6.205</v>
+        <v>4.635</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PERA AL GORGONZOLA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>5.497</v>
+        <v>2.248</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>2.011</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PENSIERO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3907,10 +3907,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>5.246</v>
+        <v>2.245</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F56" t="str">
-        <v>5.740</v>
+        <v>22.355</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57" t="str">
-        <v>2.584</v>
+        <v>11.104</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>2.672</v>
+        <v>6.590</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CARROT CAKE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>5.802</v>
+        <v>3.012</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4010,7 +4010,7 @@
         <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>5.951</v>
+        <v>5.627</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.897</v>
+        <v>2.556</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>2.382</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +4067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63" t="str">
-        <v>3.095</v>
+        <v>13.252</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4087,10 +4087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E64" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="str">
-        <v>5.737</v>
+        <v>8.133</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="str">
-        <v>3.077</v>
+        <v>6.958</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>3.077</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>2.119</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4170,7 +4170,7 @@
         <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>1.078</v>
+        <v>5.497</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.418</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4207,10 +4207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E70" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>14.193</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="71">
@@ -4218,31 +4218,351 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
+        <v>CARROT CAKE</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>5.802</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>5.822</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>FIOR DI CIOCCOLATO</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E73" t="str">
+        <v>1</v>
+      </c>
+      <c r="F73" t="str">
+        <v>2.866</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ROSA KARKADE E ARANCIA</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E74" t="str">
+        <v>3</v>
+      </c>
+      <c r="F74" t="str">
+        <v>7.328</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E75" t="str">
+        <v>1</v>
+      </c>
+      <c r="F75" t="str">
+        <v>3.237</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B76" t="str">
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E76" t="str">
+        <v>1</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2.623</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B77" t="str">
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2</v>
+      </c>
+      <c r="F77" t="str">
+        <v>5.733</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B78" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E78" t="str">
+        <v>1</v>
+      </c>
+      <c r="F78" t="str">
+        <v>3.216</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B79" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5.737</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B80" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E80" t="str">
+        <v>1</v>
+      </c>
+      <c r="F80" t="str">
+        <v>2.532</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B81" t="str">
+        <v>FAVE FRESCHE &amp; PECORINO</v>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E81" t="str">
+        <v>1</v>
+      </c>
+      <c r="F81" t="str">
+        <v>3.077</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B82" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2</v>
+      </c>
+      <c r="F82" t="str">
+        <v>1.078</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B83" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2</v>
+      </c>
+      <c r="F83" t="str">
+        <v>6.011</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B84" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2</v>
+      </c>
+      <c r="F84" t="str">
+        <v>5.426</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B85" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E85" t="str">
+        <v>6</v>
+      </c>
+      <c r="F85" t="str">
+        <v>16.946</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B86" t="str">
         <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E71" t="str">
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E86" t="str">
         <v>4</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F86" t="str">
         <v>11.802</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v>Mantenimento</v>
+      </c>
+      <c r="E87" t="str">
+        <v>1</v>
+      </c>
+      <c r="F87" t="str">
+        <v>3.211</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F87"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4278,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.114</v>
+        <v>4.480</v>
       </c>
     </row>
     <row r="3">
@@ -4298,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>4.939</v>
+        <v>2.531</v>
       </c>
     </row>
     <row r="4">
@@ -4309,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4318,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>26.587</v>
+        <v>5.734</v>
       </c>
     </row>
     <row r="5">
@@ -4329,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4338,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5" t="str">
-        <v>2.094</v>
+        <v>23.182</v>
       </c>
     </row>
     <row r="6">
@@ -4349,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4361,7 +4681,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>5.577</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="7">
@@ -4378,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
-        <v>2.769</v>
+        <v>8.594</v>
       </c>
     </row>
     <row r="8">
@@ -4398,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>8.368</v>
+        <v>5.314</v>
       </c>
     </row>
     <row r="9">
@@ -4421,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>3.443</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="10">
@@ -4438,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>7.424</v>
+        <v>2.401</v>
       </c>
     </row>
     <row r="11">
@@ -4461,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>6.053</v>
+        <v>6.267</v>
       </c>
     </row>
     <row r="12">
@@ -4481,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.048</v>
+        <v>2.858</v>
       </c>
     </row>
     <row r="13">
@@ -4498,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>2.580</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="14">
@@ -4509,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4518,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>2.988</v>
+        <v>5.891</v>
       </c>
     </row>
     <row r="15">
@@ -4529,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4538,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>9.110</v>
+        <v>5.864</v>
       </c>
     </row>
     <row r="16">
@@ -4549,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4558,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>8.765</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="17">
@@ -4569,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4581,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>3.102</v>
+        <v>2.317</v>
       </c>
     </row>
     <row r="18">
@@ -4589,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4598,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>8.416</v>
+        <v>4.819</v>
       </c>
     </row>
     <row r="19">
@@ -4609,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4618,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="str">
-        <v>5.094</v>
+        <v>8.422</v>
       </c>
     </row>
     <row r="20">
@@ -4629,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4641,7 +4961,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>10.138</v>
+        <v>8.975</v>
       </c>
     </row>
     <row r="21">
@@ -4649,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4658,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>2.677</v>
+        <v>7.021</v>
       </c>
     </row>
     <row r="22">
@@ -4669,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4681,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.633</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="23">
@@ -4689,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4698,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>8.532</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="24">
@@ -4709,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4718,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>11.119</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="25">
@@ -4729,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4738,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>12.893</v>
+        <v>10.020</v>
       </c>
     </row>
     <row r="26">
@@ -4749,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4758,10 +5078,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>7.201</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="27">
@@ -4769,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4781,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.199</v>
+        <v>3.239</v>
       </c>
     </row>
     <row r="28">
@@ -4789,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4801,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>2.056</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="29">
@@ -4809,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MORA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4818,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>8.377</v>
+        <v>2.275</v>
       </c>
     </row>
     <row r="30">
@@ -4829,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LEMON CURD</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4838,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>2.476</v>
+        <v>5.954</v>
       </c>
     </row>
     <row r="31">
@@ -4849,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LIMONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4858,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="str">
-        <v>10.383</v>
+        <v>9.041</v>
       </c>
     </row>
     <row r="32">
@@ -4869,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -4881,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.993</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="33">
@@ -4889,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -4898,10 +5218,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.498</v>
+        <v>2.170</v>
       </c>
     </row>
     <row r="34">
@@ -4909,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>PERA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -4918,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.561</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="35">
@@ -4929,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -4941,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.805</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="36">
@@ -4949,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -4958,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>14.701</v>
+        <v>8.528</v>
       </c>
     </row>
     <row r="37">
@@ -4969,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MIRTILLO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -4981,7 +5301,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.487</v>
+        <v>2.676</v>
       </c>
     </row>
     <row r="38">
@@ -4989,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -4998,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.992</v>
+        <v>2.691</v>
       </c>
     </row>
     <row r="39">
@@ -5009,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5018,10 +5338,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="str">
-        <v>14.681</v>
+        <v>21.697</v>
       </c>
     </row>
     <row r="40">
@@ -5029,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5038,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.196</v>
+        <v>2.647</v>
       </c>
     </row>
     <row r="41">
@@ -5049,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5058,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>2.850</v>
+        <v>5.804</v>
       </c>
     </row>
     <row r="42">
@@ -5069,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5081,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.771</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="43">
@@ -5089,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5101,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.166</v>
+        <v>2.459</v>
       </c>
     </row>
     <row r="44">
@@ -5109,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5118,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>5.962</v>
+        <v>8.762</v>
       </c>
     </row>
     <row r="45">
@@ -5129,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5138,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.518</v>
+        <v>5.387</v>
       </c>
     </row>
     <row r="46">
@@ -5149,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5161,7 +5481,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.823</v>
+        <v>5.300</v>
       </c>
     </row>
     <row r="47">
@@ -5169,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5178,10 +5498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="str">
-        <v>3.045</v>
+        <v>8.792</v>
       </c>
     </row>
     <row r="48">
@@ -5189,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5198,10 +5518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>27.870</v>
+        <v>2.677</v>
       </c>
     </row>
     <row r="49">
@@ -5209,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5221,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.860</v>
+        <v>2.803</v>
       </c>
     </row>
     <row r="50">
@@ -5229,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5238,10 +5558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.702</v>
+        <v>6.087</v>
       </c>
     </row>
     <row r="51">
@@ -5249,7 +5569,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5258,10 +5578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>5.220</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="52">
@@ -5269,7 +5589,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5278,10 +5598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F52" t="str">
-        <v>5.282</v>
+        <v>2.608</v>
       </c>
     </row>
     <row r="53">
@@ -5289,7 +5609,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>CARROT CAKE</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5301,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>2.732</v>
+        <v>3.232</v>
       </c>
     </row>
     <row r="54">
@@ -5309,7 +5629,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5318,10 +5638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>14.270</v>
+        <v>5.569</v>
       </c>
     </row>
     <row r="55">
@@ -5329,7 +5649,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5338,10 +5658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F55" t="str">
-        <v>2.634</v>
+        <v>19.968</v>
       </c>
     </row>
     <row r="56">
@@ -5349,7 +5669,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5358,222 +5678,22 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.403</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B57" t="str">
-        <v>MONT BLANC</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E57" t="str">
-        <v>1</v>
-      </c>
-      <c r="F57" t="str">
-        <v>3.090</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B58" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E58" t="str">
-        <v>1</v>
-      </c>
-      <c r="F58" t="str">
-        <v>2.958</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B59" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E59" t="str">
-        <v>1</v>
-      </c>
-      <c r="F59" t="str">
-        <v>2.809</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B60" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E60" t="str">
-        <v>2</v>
-      </c>
-      <c r="F60" t="str">
-        <v>5.426</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B61" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E61" t="str">
-        <v>1</v>
-      </c>
-      <c r="F61" t="str">
-        <v>2.928</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B62" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E62" t="str">
-        <v>6</v>
-      </c>
-      <c r="F62" t="str">
-        <v>3.202</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B63" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="D63" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E63" t="str">
-        <v>1</v>
-      </c>
-      <c r="F63" t="str">
-        <v>2.954</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B64" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="D64" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E64" t="str">
-        <v>8</v>
-      </c>
-      <c r="F64" t="str">
-        <v>23.481</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C65" t="str">
-        <v/>
-      </c>
-      <c r="D65" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E65" t="str">
-        <v>2</v>
-      </c>
-      <c r="F65" t="str">
-        <v>5.828</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B66" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E66" t="str">
-        <v>1</v>
-      </c>
-      <c r="F66" t="str">
-        <v>2.973</v>
+        <v>2.834</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C116"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5594,7 +5714,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -5627,7 +5747,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5649,12 +5769,12 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
@@ -5665,40 +5785,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>BIANCANEVE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CAFFE'</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
@@ -5709,18 +5829,18 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5731,18 +5851,18 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
@@ -5753,117 +5873,117 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C20" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FIORDILATTE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FRAGOLA</v>
+        <v>COCCO AL RUM</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -5874,40 +5994,40 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LIMONE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
@@ -5918,7 +6038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>ESTASI</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
@@ -5929,62 +6049,62 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MELONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NOCCIOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -5995,29 +6115,29 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>LIMONE</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>PAPAYA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6028,18 +6148,18 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PERA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -6050,18 +6170,18 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>POLLICINA</v>
+        <v>MELONE</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
@@ -6072,51 +6192,51 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SEADAS</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>STRACCIATELLA</v>
+        <v>NOCI  E UVETTA DI CORINTO</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C49" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TIRAMISU'</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6127,7 +6247,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>UVA E NOCI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
@@ -6138,18 +6258,18 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>YOGURT</v>
+        <v>PERA</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PERA AL GORGONZOLA</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
@@ -6160,7 +6280,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
@@ -6171,7 +6291,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PENSIERO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
@@ -6182,7 +6302,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
@@ -6193,62 +6313,62 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CARROT CAKE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>SEADAS</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
@@ -6259,18 +6379,18 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -6281,7 +6401,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
@@ -6292,7 +6412,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
@@ -6303,51 +6423,51 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>YOGURT</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
@@ -6358,40 +6478,40 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -6402,106 +6522,106 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>COCCO CREMA</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CREMA AGNESE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ESTASI</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>GIANDUIA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>LEMON CURD</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>MIRTILLO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
@@ -6512,29 +6632,29 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>MONT BLANC</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6545,18 +6665,18 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SACHER TORTE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6567,139 +6687,139 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>MORA</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C94" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>MORA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C96" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C98" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C100" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>COCCO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C101" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>BAKLAVA</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
@@ -6710,18 +6830,18 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C104" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>MANDARINO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6732,29 +6852,29 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>COCCO</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C107" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALBICOCCA</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -6765,7 +6885,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -6776,7 +6896,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
@@ -6787,18 +6907,18 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>CACHI</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B111" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C111" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>CIOCCOLATO</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B112" t="str">
         <v>Da Ordinare</v>
@@ -6809,18 +6929,51 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B113" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C113" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>ZABAIONE AL SAKE'</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C114" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>CACHI</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C115" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>CIOCCOLATO</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C116" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C116"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 17-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 24-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -486,8 +486,8 @@
       <c r="K2" t="str">
         <v/>
       </c>
-      <c r="L2">
-        <v>1</v>
+      <c r="L2" t="str">
+        <v/>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -513,7 +513,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -537,7 +537,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>3</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -663,7 +663,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -699,7 +699,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -712,8 +712,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -736,8 +736,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="L7">
+        <v>2</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>1</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -774,8 +774,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -798,8 +798,8 @@
       <c r="O8" t="str">
         <v/>
       </c>
-      <c r="P8">
-        <v>1</v>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>3</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -986,8 +986,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12">
-        <v>4</v>
+      <c r="L12" t="str">
+        <v/>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1024,8 +1024,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>2</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1136,8 +1136,8 @@
       <c r="K15" t="str">
         <v/>
       </c>
-      <c r="L15" t="str">
-        <v/>
+      <c r="L15">
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1162,8 +1162,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="D16">
+        <v>4</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1213,7 +1213,7 @@
         <v/>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1286,8 +1286,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1313,7 +1313,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1337,7 +1337,7 @@
         <v/>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1362,8 +1362,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1436,8 +1436,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21">
-        <v>2</v>
+      <c r="L21" t="str">
+        <v/>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1463,7 +1463,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1762,8 +1762,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="D28">
+        <v>3</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1798,8 +1798,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28" t="str">
-        <v/>
+      <c r="P28">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1849,7 +1849,7 @@
         <v/>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1898,8 +1898,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30">
-        <v>2</v>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2013,7 +2013,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>2</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2163,7 +2163,7 @@
         <v/>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2462,8 +2462,8 @@
       <c r="C42" t="str">
         <v/>
       </c>
-      <c r="D42" t="str">
-        <v/>
+      <c r="D42">
+        <v>1</v>
       </c>
       <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.155</v>
+        <v>2.380</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2867,10 +2867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2.417</v>
+        <v>7.547</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="str">
-        <v>7.547</v>
+        <v>14.133</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2910,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>5.597</v>
+        <v>6.457</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="str">
-        <v>6.457</v>
+        <v>9.056</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +2938,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>17.517</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>5.858</v>
+        <v>6.872</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2990,7 +2990,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>4.340</v>
+        <v>5.447</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="str">
-        <v>8.214</v>
+        <v>11.318</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>2.923</v>
+        <v>5.581</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3050,7 +3050,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="str">
-        <v>11.471</v>
+        <v>9.994</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>3.697</v>
+        <v>5.857</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>9.994</v>
+        <v>6.290</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3107,10 +3107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>8.845</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="str">
-        <v>6.290</v>
+        <v>9.123</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3150,7 +3150,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>6.191</v>
+        <v>6.144</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>2.985</v>
+        <v>3.020</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="str">
-        <v>2.343</v>
+        <v>12.075</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>3.135</v>
+        <v>11.553</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO AL RUM</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3230,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>3.044</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +3247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>3.020</v>
+        <v>7.502</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>26.188</v>
+        <v>10.460</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>8.402</v>
+        <v>5.409</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>COCCO AL RUM</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3310,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>2.396</v>
+        <v>2.479</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3327,10 +3327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>5.171</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3350,7 +3350,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="str">
-        <v>7.765</v>
+        <v>7.681</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>ESTASI</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>5.409</v>
+        <v>9.571</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>2.496</v>
+        <v>8.306</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +3407,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" t="str">
-        <v>7.681</v>
+        <v>10.723</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +3427,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>2.602</v>
+        <v>4.154</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>ESTASI</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +3447,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>9.571</v>
+        <v>2.995</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3470,7 +3470,7 @@
         <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v>11.470</v>
+        <v>8.359</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>FRAGOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>10.899</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>7.008</v>
+        <v>5.489</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3527,10 +3527,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E36" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>8.359</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>10.737</v>
+        <v>5.954</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>2.436</v>
+        <v>2.900</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>8.014</v>
+        <v>2.969</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.991</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3630,7 +3630,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>5.826</v>
+        <v>4.836</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.865</v>
+        <v>2.454</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MORA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>15.812</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" t="str">
-        <v>7.192</v>
+        <v>11.481</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" t="str">
-        <v>4.713</v>
+        <v>11.789</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.758</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCI  E UVETTA DI CORINTO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>11.516</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PERA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>3.243</v>
+        <v>4.502</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>NOCI  E UVETTA DI CORINTO</v>
+        <v>PERA AL GORGONZOLA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.736</v>
+        <v>2.248</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3810,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>5.105</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F51" t="str">
-        <v>4.780</v>
+        <v>17.013</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PERA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>4.635</v>
+        <v>5.430</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PERA AL GORGONZOLA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3867,10 +3867,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" t="str">
-        <v>2.248</v>
+        <v>6.590</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3887,10 +3887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>5.115</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.245</v>
+        <v>2.866</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>22.355</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>POLLICINA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" t="str">
-        <v>11.104</v>
+        <v>16.032</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>6.590</v>
+        <v>2.665</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3987,10 +3987,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>3.012</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +4007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>5.627</v>
+        <v>2.766</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4027,10 +4027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="str">
-        <v>2.556</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>SEADAS</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="str">
-        <v>2.964</v>
+        <v>8.269</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>STRACCIATELLA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +4067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>13.252</v>
+        <v>5.530</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4087,10 +4087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E64" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>8.133</v>
+        <v>5.307</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
-        <v>6.958</v>
+        <v>5.802</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>VENERE ROSA</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="str">
-        <v>2.609</v>
+        <v>5.974</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>YOGURT</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>2.883</v>
+        <v>2.925</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4167,10 +4167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E68" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>5.497</v>
+        <v>2.382</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>PENSIERO</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4187,10 +4187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E69" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>2.658</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>2.542</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="71">
@@ -4218,7 +4218,7 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
-        <v>CARROT CAKE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -4227,10 +4227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E71" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="str">
-        <v>5.802</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="72">
@@ -4238,7 +4238,7 @@
         <v>Stock</v>
       </c>
       <c r="B72" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -4247,10 +4247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E72" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="str">
-        <v>5.822</v>
+        <v>2.532</v>
       </c>
     </row>
     <row r="73">
@@ -4258,7 +4258,7 @@
         <v>Stock</v>
       </c>
       <c r="B73" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="str">
-        <v>2.866</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="74">
@@ -4278,7 +4278,7 @@
         <v>Stock</v>
       </c>
       <c r="B74" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -4287,10 +4287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E74" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" t="str">
-        <v>7.328</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="75">
@@ -4298,7 +4298,7 @@
         <v>Stock</v>
       </c>
       <c r="B75" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -4307,10 +4307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E75" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="str">
-        <v>3.237</v>
+        <v>6.011</v>
       </c>
     </row>
     <row r="76">
@@ -4318,7 +4318,7 @@
         <v>Stock</v>
       </c>
       <c r="B76" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -4327,10 +4327,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E76" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="str">
-        <v>2.623</v>
+        <v>5.426</v>
       </c>
     </row>
     <row r="77">
@@ -4338,7 +4338,7 @@
         <v>Stock</v>
       </c>
       <c r="B77" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -4347,10 +4347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E77" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" t="str">
-        <v>5.733</v>
+        <v>8.278</v>
       </c>
     </row>
     <row r="78">
@@ -4358,7 +4358,7 @@
         <v>Stock</v>
       </c>
       <c r="B78" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -4367,202 +4367,22 @@
         <v>Mantenimento</v>
       </c>
       <c r="E78" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" t="str">
-        <v>3.216</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B79" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="D79" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E79" t="str">
-        <v>2</v>
-      </c>
-      <c r="F79" t="str">
-        <v>5.737</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B80" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E80" t="str">
-        <v>1</v>
-      </c>
-      <c r="F80" t="str">
-        <v>2.532</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B81" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
-      </c>
-      <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="D81" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E81" t="str">
-        <v>1</v>
-      </c>
-      <c r="F81" t="str">
-        <v>3.077</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B82" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C82" t="str">
-        <v/>
-      </c>
-      <c r="D82" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E82" t="str">
-        <v>2</v>
-      </c>
-      <c r="F82" t="str">
-        <v>1.078</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B83" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C83" t="str">
-        <v/>
-      </c>
-      <c r="D83" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E83" t="str">
-        <v>2</v>
-      </c>
-      <c r="F83" t="str">
-        <v>6.011</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B84" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C84" t="str">
-        <v/>
-      </c>
-      <c r="D84" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E84" t="str">
-        <v>2</v>
-      </c>
-      <c r="F84" t="str">
-        <v>5.426</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B85" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C85" t="str">
-        <v/>
-      </c>
-      <c r="D85" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E85" t="str">
-        <v>6</v>
-      </c>
-      <c r="F85" t="str">
-        <v>16.946</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B86" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
-      </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E86" t="str">
-        <v>4</v>
-      </c>
-      <c r="F86" t="str">
-        <v>11.802</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C87" t="str">
-        <v/>
-      </c>
-      <c r="D87" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E87" t="str">
-        <v>1</v>
-      </c>
-      <c r="F87" t="str">
-        <v>3.211</v>
+        <v>9.080</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F78"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4601,7 +4421,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>4.480</v>
+        <v>4.611</v>
       </c>
     </row>
     <row r="3">
@@ -4618,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>2.531</v>
+        <v>4.696</v>
       </c>
     </row>
     <row r="4">
@@ -4638,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>5.734</v>
+        <v>8.485</v>
       </c>
     </row>
     <row r="5">
@@ -4658,10 +4478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" t="str">
-        <v>23.182</v>
+        <v>35.866</v>
       </c>
     </row>
     <row r="6">
@@ -4681,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>4.142</v>
+        <v>4.344</v>
       </c>
     </row>
     <row r="7">
@@ -4698,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>8.594</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="8">
@@ -4718,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.314</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="9">
@@ -4729,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4738,10 +4558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>3.486</v>
+        <v>11.550</v>
       </c>
     </row>
     <row r="10">
@@ -4749,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4758,10 +4578,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>2.401</v>
+        <v>6.092</v>
       </c>
     </row>
     <row r="11">
@@ -4769,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4781,7 +4601,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>6.267</v>
+        <v>4.461</v>
       </c>
     </row>
     <row r="12">
@@ -4789,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4801,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>2.858</v>
+        <v>3.248</v>
       </c>
     </row>
     <row r="13">
@@ -4809,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4821,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>5.101</v>
+        <v>6.037</v>
       </c>
     </row>
     <row r="14">
@@ -4829,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4838,10 +4658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>5.891</v>
+        <v>11.541</v>
       </c>
     </row>
     <row r="15">
@@ -4849,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4858,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>5.864</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="16">
@@ -4869,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4878,10 +4698,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.769</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="17">
@@ -4889,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4901,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.317</v>
+        <v>2.466</v>
       </c>
     </row>
     <row r="18">
@@ -4921,7 +4741,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>4.819</v>
+        <v>5.426</v>
       </c>
     </row>
     <row r="19">
@@ -4929,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4938,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>8.422</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="20">
@@ -4949,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FRAGOLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4958,10 +4778,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="str">
-        <v>8.975</v>
+        <v>14.494</v>
       </c>
     </row>
     <row r="21">
@@ -4969,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4978,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
-        <v>7.021</v>
+        <v>13.380</v>
       </c>
     </row>
     <row r="22">
@@ -4989,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>GIANDUIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4998,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="str">
-        <v>2.929</v>
+        <v>9.248</v>
       </c>
     </row>
     <row r="23">
@@ -5009,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -5021,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.668</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="24">
@@ -5029,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LEMON CURD</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -5038,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>2.461</v>
+        <v>7.937</v>
       </c>
     </row>
     <row r="25">
@@ -5058,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>10.020</v>
+        <v>15.549</v>
       </c>
     </row>
     <row r="26">
@@ -5069,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -5081,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.952</v>
+        <v>3.150</v>
       </c>
     </row>
     <row r="27">
@@ -5089,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -5101,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.239</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="28">
@@ -5109,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MIRTILLO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -5118,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.297</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="29">
@@ -5129,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MORA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -5141,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>2.275</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="30">
@@ -5149,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -5158,10 +4978,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="str">
-        <v>5.954</v>
+        <v>15.812</v>
       </c>
     </row>
     <row r="31">
@@ -5169,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>NOCCIOLA</v>
+        <v>MELONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -5178,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>9.041</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="32">
@@ -5189,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -5201,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.891</v>
+        <v>2.527</v>
       </c>
     </row>
     <row r="33">
@@ -5209,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PAPAYA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -5218,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.170</v>
+        <v>5.660</v>
       </c>
     </row>
     <row r="34">
@@ -5229,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -5238,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" t="str">
-        <v>2.444</v>
+        <v>14.585</v>
       </c>
     </row>
     <row r="35">
@@ -5249,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -5261,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.256</v>
+        <v>2.598</v>
       </c>
     </row>
     <row r="36">
@@ -5269,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -5278,10 +5098,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>8.528</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="37">
@@ -5289,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -5301,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.676</v>
+        <v>2.384</v>
       </c>
     </row>
     <row r="38">
@@ -5309,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -5318,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.691</v>
+        <v>4.829</v>
       </c>
     </row>
     <row r="39">
@@ -5329,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5338,10 +5158,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>21.697</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="40">
@@ -5349,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>TIRAMISU'</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5358,10 +5178,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F40" t="str">
-        <v>2.647</v>
+        <v>25.162</v>
       </c>
     </row>
     <row r="41">
@@ -5369,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>YOGURT</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5381,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>5.804</v>
+        <v>5.674</v>
       </c>
     </row>
     <row r="42">
@@ -5389,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5398,10 +5218,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>2.964</v>
+        <v>5.633</v>
       </c>
     </row>
     <row r="43">
@@ -5409,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5421,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.459</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="44">
@@ -5429,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>SACRIPANTE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5441,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>8.762</v>
+        <v>8.010</v>
       </c>
     </row>
     <row r="45">
@@ -5449,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5458,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.387</v>
+        <v>2.812</v>
       </c>
     </row>
     <row r="46">
@@ -5469,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5478,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F46" t="str">
-        <v>5.300</v>
+        <v>29.914</v>
       </c>
     </row>
     <row r="47">
@@ -5489,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5498,10 +5318,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="str">
-        <v>8.792</v>
+        <v>10.792</v>
       </c>
     </row>
     <row r="48">
@@ -5509,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5521,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.677</v>
+        <v>2.704</v>
       </c>
     </row>
     <row r="49">
@@ -5529,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5541,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.803</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="50">
@@ -5549,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5561,7 +5381,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>6.087</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="51">
@@ -5569,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SACHER TORTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5581,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.517</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="52">
@@ -5589,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5598,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.608</v>
+        <v>2.011</v>
       </c>
     </row>
     <row r="53">
@@ -5609,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5621,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>3.232</v>
+        <v>2.588</v>
       </c>
     </row>
     <row r="54">
@@ -5629,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5638,10 +5458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>5.569</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="55">
@@ -5649,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5658,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>19.968</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="56">
@@ -5669,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5678,22 +5498,282 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" t="str">
-        <v>2.834</v>
+        <v>8.553</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B57" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E57" t="str">
+        <v>1</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2.897</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B58" t="str">
+        <v>FIOR DI CIOCCOLATO</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E58" t="str">
+        <v>1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2.866</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ROSA KARKADE E ARANCIA</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5.109</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B60" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2.664</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E61" t="str">
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2.623</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5.737</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E63" t="str">
+        <v>1</v>
+      </c>
+      <c r="F63" t="str">
+        <v>3.077</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B64" t="str">
+        <v>FAVE FRESCHE &amp; PECORINO</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E64" t="str">
+        <v>1</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2.928</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B65" t="str">
+        <v>LIMONE &amp; BASILICO</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E65" t="str">
+        <v>1</v>
+      </c>
+      <c r="F65" t="str">
+        <v>2.119</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B66" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E66" t="str">
+        <v>3</v>
+      </c>
+      <c r="F66" t="str">
+        <v>1.602</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B67" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>7</v>
+      </c>
+      <c r="F67" t="str">
+        <v>19.771</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E68" t="str">
+        <v>1</v>
+      </c>
+      <c r="F68" t="str">
+        <v>2.966</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B69" t="str">
+        <v>STRAWBERRY FIELD FOREVER</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>1</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2.726</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5708,7 +5788,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
@@ -5719,18 +5799,18 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C3" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
@@ -5741,40 +5821,40 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
@@ -5785,18 +5865,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
@@ -5807,18 +5887,18 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
@@ -5829,18 +5909,18 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5851,29 +5931,29 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
@@ -5884,7 +5964,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5895,18 +5975,18 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C19" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
@@ -5917,7 +5997,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO AL RUM</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -5928,18 +6008,18 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
@@ -5950,7 +6030,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
@@ -5961,7 +6041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>COCCO AL RUM</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
@@ -5972,18 +6052,18 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -5994,7 +6074,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>ESTASI</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
@@ -6005,95 +6085,95 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ESTASI</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FRAGOLA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
@@ -6104,7 +6184,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
@@ -6115,29 +6195,29 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6148,7 +6228,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -6159,7 +6239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MORA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -6170,7 +6250,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -6181,40 +6261,40 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCI  E UVETTA DI CORINTO</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PERA</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -6225,7 +6305,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>NOCI  E UVETTA DI CORINTO</v>
+        <v>PERA AL GORGONZOLA</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6236,7 +6316,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6247,29 +6327,29 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PERA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PERA AL GORGONZOLA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
@@ -6280,128 +6360,128 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>SEADAS</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>POLLICINA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C59" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>YOGURT</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C61" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SEADAS</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>STRACCIATELLA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
@@ -6412,84 +6492,84 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VENERE ROSA</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>YOGURT</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>PENSIERO</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CARROT CAKE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
@@ -6500,29 +6580,29 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
@@ -6533,128 +6613,128 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>AMARENA</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SACHER TORTE</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>MELONE</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C86" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C87" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
@@ -6665,18 +6745,18 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>GIANDUIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6687,29 +6767,29 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MIRTILLO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>MORA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PAPAYA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
@@ -6720,51 +6800,51 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C94" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SACRIPANTE</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C96" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6775,7 +6855,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
@@ -6786,51 +6866,51 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C100" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C101" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C103" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>MONT BLANC</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
@@ -6841,7 +6921,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6852,29 +6932,29 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>COCCO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C107" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -6885,7 +6965,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MANDARINO</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -6896,7 +6976,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
@@ -6907,29 +6987,29 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B111" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C111" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ALBICOCCA</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B112" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C112" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>COCCO</v>
       </c>
       <c r="B113" t="str">
         <v>Da Ordinare</v>
@@ -6940,7 +7020,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B114" t="str">
         <v>Da Ordinare</v>
@@ -6951,29 +7031,51 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>CACHI</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B115" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C115" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>CIOCCOLATO</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B116" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C116" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>CIOCCOLATA CALDA FONDENTE</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C117" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>ZABAIONE AL SAKE'</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Da Ordinare</v>
+      </c>
+      <c r="C118" t="str">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 24-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 31-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -462,8 +462,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -498,8 +498,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2">
-        <v>1</v>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -512,8 +512,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
-        <v>8</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -524,8 +524,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -562,8 +562,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -574,8 +574,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -598,8 +598,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4">
-        <v>2</v>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -612,8 +612,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -648,8 +648,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -724,8 +724,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>2</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -748,8 +748,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -762,8 +762,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>4</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -774,8 +774,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>3</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -786,8 +786,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>1</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -874,8 +874,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10">
-        <v>2</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -886,8 +886,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -924,8 +924,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11">
-        <v>1</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -974,8 +974,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>4</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -998,8 +998,8 @@
       <c r="O12" t="str">
         <v/>
       </c>
-      <c r="P12" t="str">
-        <v/>
+      <c r="P12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1012,8 +1012,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1162,8 +1162,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>4</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1186,8 +1186,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16">
-        <v>1</v>
+      <c r="L16" t="str">
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1212,8 +1212,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>1</v>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1236,8 +1236,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1262,8 +1262,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="D18">
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1298,8 +1298,8 @@
       <c r="O18" t="str">
         <v/>
       </c>
-      <c r="P18" t="str">
-        <v/>
+      <c r="P18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1313,7 +1313,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1386,8 +1386,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v/>
+      <c r="L20">
+        <v>1</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1648,8 +1648,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>6</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1698,8 +1698,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26" t="str">
-        <v/>
+      <c r="P26">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1748,8 +1748,8 @@
       <c r="O27" t="str">
         <v/>
       </c>
-      <c r="P27" t="str">
-        <v/>
+      <c r="P27">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1812,8 +1812,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29">
-        <v>5</v>
+      <c r="D29" t="str">
+        <v/>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1848,8 +1848,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>1</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1862,8 +1862,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="D30">
+        <v>3</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1898,8 +1898,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1912,8 +1912,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>2</v>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1948,8 +1948,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>2</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -2048,8 +2048,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>2</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2112,8 +2112,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>2</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2163,7 +2163,7 @@
         <v/>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2198,8 +2198,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>3</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2212,8 +2212,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>1</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2348,8 +2348,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39" t="str">
-        <v/>
+      <c r="P39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2363,7 +2363,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2412,8 +2412,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41">
-        <v>1</v>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2463,7 +2463,7 @@
         <v/>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -2513,7 +2513,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -2811,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +2838,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +2847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.380</v>
+        <v>3.709</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +2858,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANGURIA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2870,7 +2870,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>7.547</v>
+        <v>6.784</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2878,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -2887,10 +2887,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="str">
-        <v>14.133</v>
+        <v>32.779</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +2898,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2910,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>6.457</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +2918,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E6" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>9.056</v>
+        <v>2.089</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +2938,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BAKLAVA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +2947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.858</v>
+        <v>2.693</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +2958,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2970,7 +2970,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>6.872</v>
+        <v>9.164</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +2978,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2990,7 +2990,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>5.447</v>
+        <v>6.290</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +2998,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>BIANCANEVE</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3007,10 +3007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E10" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>11.318</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +3018,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CAFFE'</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +3027,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="str">
-        <v>5.581</v>
+        <v>14.554</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +3038,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +3047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>9.994</v>
+        <v>3.132</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>5.857</v>
+        <v>2.971</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +3078,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +3087,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="str">
-        <v>6.290</v>
+        <v>18.397</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +3098,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3110,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>2.985</v>
+        <v>2.851</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +3118,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +3127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F16" t="str">
-        <v>9.123</v>
+        <v>16.410</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +3138,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +3147,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>6.144</v>
+        <v>2.497</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +3158,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3167,10 +3167,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>3.020</v>
+        <v>5.409</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +3178,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>12.075</v>
+        <v>5.256</v>
       </c>
     </row>
     <row r="20">
@@ -3198,7 +3198,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -3207,10 +3207,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>11.553</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +3218,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>COCCO AL RUM</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +3227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>2.396</v>
+        <v>7.681</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +3238,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3250,7 +3250,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>7.502</v>
+        <v>7.867</v>
       </c>
     </row>
     <row r="23">
@@ -3258,7 +3258,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>10.460</v>
+        <v>5.416</v>
       </c>
     </row>
     <row r="24">
@@ -3278,7 +3278,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -3287,10 +3287,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="str">
-        <v>5.409</v>
+        <v>12.996</v>
       </c>
     </row>
     <row r="25">
@@ -3298,7 +3298,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>2.479</v>
+        <v>9.144</v>
       </c>
     </row>
     <row r="26">
@@ -3318,7 +3318,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -3330,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.607</v>
+        <v>2.995</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3347,10 +3347,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" t="str">
-        <v>7.681</v>
+        <v>15.620</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +3358,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="str">
-        <v>9.571</v>
+        <v>10.724</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +3378,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>FIORDILATTE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3387,10 +3387,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E29" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>8.306</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +3398,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="F30" t="str">
-        <v>10.723</v>
+        <v>12.338</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +3418,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>4.154</v>
+        <v>5.765</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +3438,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>GIANDUIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.995</v>
+        <v>2.857</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +3458,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>8.359</v>
+        <v>2.903</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +3478,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.436</v>
+        <v>2.828</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +3498,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>LIMONE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +3507,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F35" t="str">
-        <v>5.489</v>
+        <v>16.497</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +3518,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.697</v>
+        <v>2.173</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +3538,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MELONE</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>5.954</v>
+        <v>2.800</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +3558,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +3567,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.900</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +3578,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +3587,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>2.969</v>
+        <v>8.802</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +3598,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +3607,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F40" t="str">
-        <v>2.887</v>
+        <v>14.252</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +3618,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +3627,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>4.836</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +3638,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>MIRTILLO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>2.454</v>
+        <v>6.250</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3658,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>MORA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3667,10 +3667,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>2.411</v>
+        <v>4.408</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +3678,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +3687,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>11.481</v>
+        <v>4.767</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +3698,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +3707,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>11.789</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +3718,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +3727,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" t="str">
-        <v>2.964</v>
+        <v>6.155</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +3738,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>NOCI  E UVETTA DI CORINTO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +3747,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="str">
-        <v>2.736</v>
+        <v>8.370</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +3758,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PERA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +3767,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="str">
-        <v>4.502</v>
+        <v>8.641</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +3778,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PERA AL GORGONZOLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +3787,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>2.248</v>
+        <v>5.711</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +3798,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3810,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>5.115</v>
+        <v>5.398</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +3818,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E51" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>17.013</v>
+        <v>5.533</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +3838,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>POLLICINA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3847,10 +3847,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F52" t="str">
-        <v>5.430</v>
+        <v>27.518</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3858,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3870,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="F53" t="str">
-        <v>6.590</v>
+        <v>8.242</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +3878,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3890,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.744</v>
+        <v>2.310</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.866</v>
+        <v>3.100</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +3918,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +3927,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>2.895</v>
+        <v>5.680</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3947,10 +3947,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E57" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>16.032</v>
+        <v>2.243</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +3958,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +3967,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>2.665</v>
+        <v>8.291</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +3978,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3990,7 +3990,7 @@
         <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>4.514</v>
+        <v>5.802</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +3998,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +4007,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F60" t="str">
-        <v>2.766</v>
+        <v>25.500</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +4018,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="F61" t="str">
-        <v>6.972</v>
+        <v>8.449</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +4038,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>SACRIPANTE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4047,10 +4047,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E62" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>8.269</v>
+        <v>2.612</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +4058,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +4067,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>5.530</v>
+        <v>1.751</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +4078,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4090,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>5.307</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>CARROT CAKE</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>5.802</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +4118,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>5.974</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +4138,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>2.925</v>
+        <v>3.305</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +4158,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.382</v>
+        <v>2.532</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +4178,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>5.733</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="70">
@@ -4198,7 +4198,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>LATTE DI FICO (PAMPANELLA)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>2.778</v>
+        <v>3.053</v>
       </c>
     </row>
     <row r="71">
@@ -4218,7 +4218,7 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -4227,10 +4227,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E71" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="str">
-        <v>3.216</v>
+        <v>8.337</v>
       </c>
     </row>
     <row r="72">
@@ -4238,7 +4238,7 @@
         <v>Stock</v>
       </c>
       <c r="B72" t="str">
-        <v>SACHER TORTE</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -4247,10 +4247,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E72" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F72" t="str">
-        <v>2.532</v>
+        <v>14.905</v>
       </c>
     </row>
     <row r="73">
@@ -4258,7 +4258,7 @@
         <v>Stock</v>
       </c>
       <c r="B73" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+        <v>FIORDILATTE NEW</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="str">
-        <v>2.271</v>
+        <v>1.936</v>
       </c>
     </row>
     <row r="74">
@@ -4278,7 +4278,7 @@
         <v>Stock</v>
       </c>
       <c r="B74" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="F74" t="str">
-        <v>1.078</v>
+        <v>5.924</v>
       </c>
     </row>
     <row r="75">
@@ -4298,7 +4298,7 @@
         <v>Stock</v>
       </c>
       <c r="B75" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>FASHIONED SPRITZ</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -4307,82 +4307,22 @@
         <v>Mantenimento</v>
       </c>
       <c r="E75" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" t="str">
-        <v>6.011</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B76" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="D76" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E76" t="str">
-        <v>2</v>
-      </c>
-      <c r="F76" t="str">
-        <v>5.426</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B77" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E77" t="str">
-        <v>3</v>
-      </c>
-      <c r="F77" t="str">
-        <v>8.278</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B78" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E78" t="str">
-        <v>3</v>
-      </c>
-      <c r="F78" t="str">
-        <v>9.080</v>
+        <v>2.560</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F75"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4418,10 +4358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>4.611</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="3">
@@ -4441,7 +4381,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>4.696</v>
+        <v>5.034</v>
       </c>
     </row>
     <row r="4">
@@ -4449,7 +4389,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -4461,7 +4401,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>8.485</v>
+        <v>7.547</v>
       </c>
     </row>
     <row r="5">
@@ -4469,7 +4409,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -4478,10 +4418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>35.866</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="6">
@@ -4489,7 +4429,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4498,10 +4438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>4.344</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="7">
@@ -4509,7 +4449,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4518,10 +4458,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" t="str">
-        <v>2.841</v>
+        <v>21.197</v>
       </c>
     </row>
     <row r="8">
@@ -4529,7 +4469,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CAFFE'</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4538,10 +4478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="str">
-        <v>2.976</v>
+        <v>9.119</v>
       </c>
     </row>
     <row r="9">
@@ -4549,7 +4489,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4561,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>11.550</v>
+        <v>10.867</v>
       </c>
     </row>
     <row r="10">
@@ -4569,7 +4509,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4578,10 +4518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>6.092</v>
+        <v>8.564</v>
       </c>
     </row>
     <row r="11">
@@ -4589,7 +4529,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4598,10 +4538,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="str">
-        <v>4.461</v>
+        <v>8.475</v>
       </c>
     </row>
     <row r="12">
@@ -4609,7 +4549,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4621,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.248</v>
+        <v>3.697</v>
       </c>
     </row>
     <row r="13">
@@ -4629,7 +4569,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4641,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>6.037</v>
+        <v>4.903</v>
       </c>
     </row>
     <row r="14">
@@ -4649,7 +4589,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4658,10 +4598,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="str">
-        <v>11.541</v>
+        <v>14.886</v>
       </c>
     </row>
     <row r="15">
@@ -4669,7 +4609,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4678,10 +4618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>8.339</v>
+        <v>3.082</v>
       </c>
     </row>
     <row r="16">
@@ -4689,7 +4629,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4698,10 +4638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.101</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="17">
@@ -4709,7 +4649,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4721,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.466</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="18">
@@ -4729,7 +4669,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4738,10 +4678,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18" t="str">
-        <v>5.426</v>
+        <v>17.773</v>
       </c>
     </row>
     <row r="19">
@@ -4749,7 +4689,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4761,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.455</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="20">
@@ -4769,7 +4709,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4778,10 +4718,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>14.494</v>
+        <v>10.017</v>
       </c>
     </row>
     <row r="21">
@@ -4789,7 +4729,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4798,10 +4738,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>13.380</v>
+        <v>7.901</v>
       </c>
     </row>
     <row r="22">
@@ -4809,7 +4749,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4818,10 +4758,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>9.248</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="23">
@@ -4829,7 +4769,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4841,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>3.072</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="24">
@@ -4849,7 +4789,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -4858,10 +4798,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>7.937</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="25">
@@ -4869,7 +4809,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4878,10 +4818,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>15.549</v>
+        <v>9.571</v>
       </c>
     </row>
     <row r="26">
@@ -4889,7 +4829,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4898,10 +4838,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <v>3.150</v>
+        <v>16.427</v>
       </c>
     </row>
     <row r="27">
@@ -4909,7 +4849,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4918,10 +4858,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" t="str">
-        <v>2.793</v>
+        <v>15.485</v>
       </c>
     </row>
     <row r="28">
@@ -4929,7 +4869,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4938,10 +4878,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>5.682</v>
+        <v>6.545</v>
       </c>
     </row>
     <row r="29">
@@ -4949,7 +4889,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -4958,10 +4898,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>2.873</v>
+        <v>6.137</v>
       </c>
     </row>
     <row r="30">
@@ -4969,7 +4909,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4978,10 +4918,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>15.812</v>
+        <v>2.800</v>
       </c>
     </row>
     <row r="31">
@@ -4989,7 +4929,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MELONE</v>
+        <v>LIMONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -4998,10 +4938,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="str">
-        <v>2.294</v>
+        <v>8.073</v>
       </c>
     </row>
     <row r="32">
@@ -5009,7 +4949,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MIRTILLO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -5021,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.527</v>
+        <v>2.930</v>
       </c>
     </row>
     <row r="33">
@@ -5029,7 +4969,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -5041,7 +4981,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>5.660</v>
+        <v>5.991</v>
       </c>
     </row>
     <row r="34">
@@ -5049,7 +4989,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -5058,10 +4998,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>14.585</v>
+        <v>5.679</v>
       </c>
     </row>
     <row r="35">
@@ -5069,7 +5009,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -5078,10 +5018,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.598</v>
+        <v>6.013</v>
       </c>
     </row>
     <row r="36">
@@ -5089,7 +5029,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PAPAYA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -5098,10 +5038,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>2.253</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="37">
@@ -5109,7 +5049,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -5118,10 +5058,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>2.384</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="38">
@@ -5129,7 +5069,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PERA</v>
+        <v>MELONE</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -5141,7 +5081,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>4.829</v>
+        <v>5.027</v>
       </c>
     </row>
     <row r="39">
@@ -5149,7 +5089,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5158,10 +5098,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>7.004</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="40">
@@ -5169,7 +5109,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5178,10 +5118,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>25.162</v>
+        <v>5.760</v>
       </c>
     </row>
     <row r="41">
@@ -5189,7 +5129,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>POLLICINA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5198,10 +5138,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
-        <v>5.674</v>
+        <v>14.382</v>
       </c>
     </row>
     <row r="42">
@@ -5209,7 +5149,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5221,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>5.633</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="43">
@@ -5229,7 +5169,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5241,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.788</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="44">
@@ -5249,7 +5189,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5258,10 +5198,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>8.010</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="45">
@@ -5269,7 +5209,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>SEADAS</v>
+        <v>PERA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5278,10 +5218,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="str">
-        <v>2.812</v>
+        <v>6.761</v>
       </c>
     </row>
     <row r="46">
@@ -5289,7 +5229,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5298,10 +5238,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>29.914</v>
+        <v>2.303</v>
       </c>
     </row>
     <row r="47">
@@ -5309,7 +5249,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>TIRAMISU'</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5318,10 +5258,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" t="str">
-        <v>10.792</v>
+        <v>22.949</v>
       </c>
     </row>
     <row r="48">
@@ -5329,7 +5269,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>VENERE ROSA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5338,10 +5278,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>2.704</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="49">
@@ -5349,7 +5289,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5358,10 +5298,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>3.164</v>
+        <v>4.436</v>
       </c>
     </row>
     <row r="50">
@@ -5369,7 +5309,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>YOGURT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5381,7 +5321,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>6.149</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="51">
@@ -5389,7 +5329,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5401,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.846</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="52">
@@ -5409,7 +5349,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -5418,10 +5358,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.011</v>
+        <v>5.797</v>
       </c>
     </row>
     <row r="53">
@@ -5429,7 +5369,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PENSIERO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -5438,10 +5378,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.588</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="54">
@@ -5449,7 +5389,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -5458,10 +5398,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F54" t="str">
-        <v>2.607</v>
+        <v>30.139</v>
       </c>
     </row>
     <row r="55">
@@ -5469,7 +5409,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5478,10 +5418,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="str">
-        <v>5.352</v>
+        <v>8.113</v>
       </c>
     </row>
     <row r="56">
@@ -5489,7 +5429,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5498,10 +5438,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>8.553</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="57">
@@ -5509,7 +5449,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5521,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.897</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="58">
@@ -5529,7 +5469,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5538,10 +5478,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>2.866</v>
+        <v>8.210</v>
       </c>
     </row>
     <row r="59">
@@ -5549,7 +5489,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5558,10 +5498,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>5.109</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="60">
@@ -5569,7 +5509,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5578,10 +5518,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="str">
-        <v>2.664</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="61">
@@ -5589,7 +5529,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5601,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.623</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="62">
@@ -5609,7 +5549,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5618,10 +5558,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="str">
-        <v>5.737</v>
+        <v>8.269</v>
       </c>
     </row>
     <row r="63">
@@ -5629,7 +5569,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5641,7 +5581,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>3.077</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="64">
@@ -5649,7 +5589,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5661,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.928</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="65">
@@ -5669,7 +5609,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5678,10 +5618,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65" t="str">
-        <v>2.119</v>
+        <v>14.240</v>
       </c>
     </row>
     <row r="66">
@@ -5689,7 +5629,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5698,10 +5638,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>1.602</v>
+        <v>2.462</v>
       </c>
     </row>
     <row r="67">
@@ -5709,7 +5649,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -5718,10 +5658,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>19.771</v>
+        <v>3.237</v>
       </c>
     </row>
     <row r="68">
@@ -5729,7 +5669,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -5741,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.966</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="69">
@@ -5749,7 +5689,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -5761,19 +5701,139 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.726</v>
+        <v>2.290</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>4</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2.144</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>1</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2.915</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>1</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2.759</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E73" t="str">
+        <v>5</v>
+      </c>
+      <c r="F73" t="str">
+        <v>13.854</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5.611</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E75" t="str">
+        <v>1</v>
+      </c>
+      <c r="F75" t="str">
+        <v>3.211</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F75"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C114"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5788,18 +5848,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANGURIA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
@@ -5810,7 +5870,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B4" t="str">
         <v>Da Ordinare</v>
@@ -5821,7 +5881,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
@@ -5832,40 +5892,40 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BAKLAVA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BANANA E LIME</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
@@ -5876,7 +5936,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>BIANCANEVE</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
@@ -5887,40 +5947,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CAFFE'</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5931,40 +5991,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C15" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
@@ -5975,7 +6035,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
@@ -5986,18 +6046,18 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="B20" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C20" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>COCCO AL RUM</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
@@ -6008,7 +6068,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
@@ -6019,51 +6079,51 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="B23" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="B24" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="B25" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="B26" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
@@ -6074,7 +6134,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
@@ -6085,40 +6145,40 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FIORDILATTE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C30" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GIANDUIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
@@ -6129,18 +6189,18 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>LEMON CURD</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
@@ -6151,62 +6211,62 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LIMONE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C35" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MELONE</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C39" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
@@ -6217,29 +6277,29 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C41" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MIRTILLO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C42" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MORA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -6250,62 +6310,62 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C45" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>NOCI  E UVETTA DI CORINTO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PERA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PERA AL GORGONZOLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6316,106 +6376,106 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C50" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>SEADAS</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C51" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>POLLICINA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C57" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TIRAMISU'</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>UVA E NOCI</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
@@ -6426,18 +6486,18 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6448,40 +6508,40 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SACRIPANTE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C64" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CARROT CAKE</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
@@ -6492,29 +6552,29 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
@@ -6525,51 +6585,51 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>LATTE DI FICO (PAMPANELLA)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SACHER TORTE</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+        <v>FIORDILATTE NEW</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
@@ -6580,18 +6640,18 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>FASHIONED SPRITZ</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
@@ -6602,40 +6662,40 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>AMARENA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
@@ -6646,29 +6706,29 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>COCCO CREMA</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
@@ -6679,40 +6739,40 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C83" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>MELONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6723,7 +6783,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PAPAYA</v>
+        <v>MORA</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
@@ -6734,29 +6794,29 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PASSION FRUIT</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C88" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C89" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6767,40 +6827,40 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>VENERE ROSA</v>
+        <v>YOGURT</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>PENSIERO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6811,40 +6871,40 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C96" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
@@ -6855,18 +6915,18 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6877,7 +6937,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6888,13 +6948,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C102" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6910,18 +6970,18 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C104" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6932,29 +6992,29 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C107" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -6965,7 +7025,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -6976,7 +7036,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>MONT BLANC</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
@@ -6987,29 +7047,29 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B111" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C111" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>COCCO</v>
       </c>
       <c r="B112" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C112" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>COCCO</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B113" t="str">
         <v>Da Ordinare</v>
@@ -7020,62 +7080,18 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>MANDARINO</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B114" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C114" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>PASTIERA NAPOLETANA</v>
-      </c>
-      <c r="B115" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C115" t="str">
         <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>ALBICOCCA</v>
-      </c>
-      <c r="B116" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C116" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
-      </c>
-      <c r="B117" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C117" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>ZABAIONE AL SAKE'</v>
-      </c>
-      <c r="B118" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C118" t="str">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_report.xlsx
+++ b/output/shocapp_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Ordini Settimanali 31-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ordini Settimanali 03-05-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Mantenimento" sheetId="2" r:id="rId2"/>
     <sheet name="Esaurito" sheetId="3" r:id="rId3"/>
     <sheet name="Da Ordinare" sheetId="4" r:id="rId4"/>
@@ -400,2418 +400,936 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:H39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Gelato</v>
       </c>
       <c r="B1" t="str">
-        <v>ESAURITO</v>
+        <v>ORDINE</v>
       </c>
       <c r="C1" t="str">
-        <v>MANTENIMENTO</v>
+        <v>Creme</v>
       </c>
       <c r="D1" t="str">
         <v>ORDINE</v>
       </c>
       <c r="E1" t="str">
-        <v>Creme</v>
+        <v>Cioccolati</v>
       </c>
       <c r="F1" t="str">
-        <v>ESAURITO</v>
+        <v>ORDINE</v>
       </c>
       <c r="G1" t="str">
-        <v>MANTENIMENTO</v>
+        <v>Sorbetti</v>
       </c>
       <c r="H1" t="str">
         <v>ORDINE</v>
       </c>
-      <c r="I1" t="str">
-        <v>Cioccolati</v>
-      </c>
-      <c r="J1" t="str">
-        <v>ESAURITO</v>
-      </c>
-      <c r="K1" t="str">
-        <v>MANTENIMENTO</v>
-      </c>
-      <c r="L1" t="str">
-        <v>ORDINE</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Sorbetti</v>
-      </c>
-      <c r="N1" t="str">
-        <v>ESAURITO</v>
-      </c>
-      <c r="O1" t="str">
-        <v>MANTENIMENTO</v>
-      </c>
-      <c r="P1" t="str">
-        <v>ORDINE</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+        <v>ARACHIDI</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>CARROT CAKE</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="str">
-        <v>CARROT CAKE</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
+        <v>C. AL LATTE GELATO</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
       </c>
       <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>CIOCCOLATO</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
+      <c r="H2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>BACIO DEL PRINCIPE</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
+        <v>BACIO</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
       </c>
       <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+        <v>CHEESECAKE MIRTILLI</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>C. AL PIMENTO</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>AMARENA</v>
       </c>
       <c r="H3">
         <v>2</v>
-      </c>
-      <c r="I3" t="str">
-        <v>CIOCCOLATO AL LATTE GELATO</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3" t="str">
-        <v>AMARENA</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BASILICO</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4">
+        <v>C. AGNESE</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v>C. AL WHISKY</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>ANANAS</v>
+      </c>
+      <c r="H4">
         <v>3</v>
-      </c>
-      <c r="E4" t="str">
-        <v>CREMA AGNESE</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-      <c r="I4" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>ANANAS E ZENZERO</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>3</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>C. CANNELLA</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="str">
+        <v>C. BIANCO</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>ANGURIA</v>
+      </c>
+      <c r="H5">
         <v>4</v>
-      </c>
-      <c r="E5" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5" t="str">
-        <v>ANGURIA</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6">
-        <v>2</v>
+        <v>C. FRAGOLE E MANDORLE</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>C. CRUDO DEL PERU'</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>CIOCCOLATO BIANCO</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6">
-        <v>2</v>
+        <v>AVOCADO</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>C. PASTICCIERA PARISI</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
+        <v>C. E ARANCIA</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
       </c>
       <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7">
+      <c r="H7">
         <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>COCCO CREMA</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
+        <v>COCCO C.</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
+        <v>C. VANIGLIA</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
       </c>
       <c r="E8" t="str">
-        <v>CREMA PASTICCIERA PARISI</v>
+        <v>C. EQUADOR</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>CACHI</v>
       </c>
       <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>CACHI</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CREMA BANANA E CROCCANTE AL SESAMO</v>
+        <v>C.BANANA</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+        <v>C. ZENZERO</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>CREMA VANIGLIA</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
+        <v>C. KENTUCKY</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>CIOCCOLATO EQUADOR</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>CILIEGIA</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FICHI ALLA GRECA</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
+        <v>FIORDILATTE</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
+        <v>LEMON CURD</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>C. LAPSANG SOUCHOUNG</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10" t="str">
-        <v>COCCO</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10">
-        <v>1</v>
+        <v>FRAGOLA</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>LAVANDA</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>SACRIPANTE</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>LEMON CURD</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+        <v>C. MADAGASCAR</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>COCCO AL RUM</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
+        <v>FRUTTI DI BOSCO</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FIORDILATTE</v>
+        <v>LATTE DI FICO</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12">
-        <v>4</v>
+        <v>TIRAMISU'</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>SACRIPANTE</v>
+        <v>C. ROSEMARY</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H12">
         <v>4</v>
       </c>
-      <c r="I12" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
+        <v>MENTA E C.</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>TIRAMISU'</v>
+        <v>C. UGANDA</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>LIMONE</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13" t="str">
-        <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LATTE &amp; CEREALI</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
+        <v>LIQUIRIZIA</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>ZABAIONE GELATO</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
+        <v>C. VENEZUELA</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>MANGO</v>
       </c>
       <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="str">
-        <v>CIOCCOLATO UGANDA</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v>FEIJOA</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LATTE DI FICO (PAMPANELLA)</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
+        <v>MANDORLA AL CARDAMOMO</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>C. WASABI</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>MELA M.C.</v>
       </c>
       <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15">
-        <v>5</v>
-      </c>
-      <c r="M15" t="str">
-        <v>FICHI</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
+        <v>MANDORLA BIANCA</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>speciali</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
+        <v>ESTASI</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>MELOGRANO</v>
       </c>
       <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>CIOCCOLATO WASABI</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>FICHI D INDIA</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LIQUIRIZIA</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
+        <v>MANDORLA E ARANCIA</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Varie</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
+        <v>V. FIOR DI CIOCCOLATO</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>MELONE</v>
       </c>
       <c r="H17" t="str">
         <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>ESTASI</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17">
-        <v>3</v>
-      </c>
-      <c r="M17" t="str">
-        <v>FRAGOLA</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17">
-        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
+        <v>MANDORLA TOSTATA</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>CAPRESE</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="str">
-        <v>CASTAGNACCIO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="F18" t="str">
         <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>MIRTILLO</v>
       </c>
       <c r="H18" t="str">
         <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MANDORLA BIANCA</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
+        <v>MONTBLANC</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19">
-        <v>2</v>
+        <v>CHICCHIAINI</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>COTOGNATA</v>
+        <v>V. GIANDUIA VARIEGATA</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>GIANDUIA</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19" t="str">
-        <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
+        <v>MORA</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MANDORLA E ARANCIA</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
+        <v>NOCCIOLA</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>CIOCCOLATA CALDA</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="str">
-        <v>CREMA COGNAC E NOCE MOSCATA</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
+        <v>MOU LATTE SALATO</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>PANACEA</v>
       </c>
       <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>GIANDUIA VARIEGATA</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20" t="str">
-        <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>MANDORLA TOSTATA</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
+        <v>NOCCIOLA BURRO</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21">
-        <v>1</v>
+        <v>COPPETTA GRANDE</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
-        <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
       </c>
       <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>MOU LATTE SALATO</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v>HIBISCUS</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+        <v>PAPAYA</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>MONTBLANC</v>
+        <v>NOCI PECAN</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="str">
-        <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
+        <v>COPPETTA PICCOLA</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
       </c>
       <c r="F22" t="str">
         <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22" t="str">
-        <v>LAMPONI SORBETTO</v>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOCCIOLA</v>
+        <v>PEREBH</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="str">
-        <v>FIORI DI MAGNOLIA &amp; LIME</v>
+        <v>MOUSSE</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="F23" t="str">
         <v/>
       </c>
       <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v>LIMONE</v>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23">
-        <v>2</v>
+        <v>PENSIERO</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>P.BRONTE</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>SUSHI GELATO</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
-      <c r="E24" t="str">
-        <v>GELATO DI PANETTONE</v>
-      </c>
       <c r="F24" t="str">
         <v/>
       </c>
       <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>Varie</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v>MANDARINO</v>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24">
+        <v>PERA</v>
+      </c>
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>NOCI E UVETTA DI CORINTO</v>
+        <v>P. SIRIANO</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>TORTA AGNESE 6P</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
-      <c r="E25" t="str">
-        <v>GELSI BIANCHI, SAKE' E ANACARDI SALATI</v>
-      </c>
       <c r="F25" t="str">
         <v/>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>CAPRESE</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>NOCI PECAN</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>TORTA AGNESE 8P</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
-      <c r="E26" t="str">
-        <v>GORGONZOLA</v>
-      </c>
       <c r="F26" t="str">
         <v/>
       </c>
       <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v>CHICCHIAINI</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26">
+        <v>PUNCH PARADISE</v>
+      </c>
+      <c r="H26">
         <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PERE BELLE HELENE</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
+        <v>RICOTTA E AGRUMI</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>TORTA CHEESCAKE 6P</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
-      <c r="E27" t="str">
-        <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
-      </c>
       <c r="F27" t="str">
         <v/>
       </c>
       <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v>CIALDINE</v>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v>MELOGRANO WONDERFUL</v>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-      <c r="P27">
-        <v>3</v>
+        <v>ROSA E ARANCIA</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>RICOTTA E FICHI</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28" t="str">
-        <v>MATE-LATE</v>
+        <v>TORTA CHEESCAKE 8P</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="F28" t="str">
         <v/>
       </c>
       <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v>CIOCCOLATA CALDA</v>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v>MELONE</v>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v/>
-      </c>
-      <c r="P28">
+        <v>UVA E NOCI</v>
+      </c>
+      <c r="H28">
         <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>PISTACCHIO SIRIANO</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
+        <v>RICOTTA E PERA</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>TORTA LAURA 6P</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
-      <c r="E29" t="str">
-        <v>MOJITO ALLA AMARENA</v>
-      </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>COPPA IN CIALDA</v>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v>MIRTILLO</v>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v/>
-      </c>
-      <c r="P29" t="str">
-        <v/>
+        <v>UVA FRAGOLA</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>POLLICINA</v>
+        <v>RICOTTA E AMARENE</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30" t="str">
-        <v>NON TI SCORDAR DI ME</v>
+        <v>TORTA LAURA 8P</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
       </c>
       <c r="F30" t="str">
         <v/>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>V. BANACHI</v>
       </c>
       <c r="H30" t="str">
         <v/>
-      </c>
-      <c r="I30" t="str">
-        <v>COPPETTA GRANDE</v>
-      </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v>MORA</v>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-      <c r="P30">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>RICOTTA E COCCO</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>TORTA TIRAMISU 6P</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
-      <c r="E31" t="str">
-        <v>PASTIERA NAPOLETANA</v>
-      </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v>COPPETTA PICCOLA</v>
-      </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
-      <c r="P31" t="str">
-        <v/>
+        <v>V. CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>RICOTTA E FICHI ALLA GRECA</v>
-      </c>
-      <c r="B32" t="str">
-        <v/>
+        <v>RISO E VANIGLIA</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>TORTA TIRAMISU 8P</v>
       </c>
       <c r="D32" t="str">
         <v/>
       </c>
-      <c r="E32" t="str">
-        <v>PECORINO</v>
-      </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v>MOUSSE</v>
-      </c>
-      <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v>PAPAYA</v>
-      </c>
-      <c r="N32" t="str">
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <v/>
-      </c>
-      <c r="P32">
-        <v>2</v>
+        <v>V. CASTAGNA E MIRTO</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
-      </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="str">
-        <v>PERA AL GORGONZOLA</v>
+        <v>SEADAS</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>V.BRONTE GREEN</v>
       </c>
       <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v>SUSHI GELATO</v>
-      </c>
-      <c r="J33" t="str">
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <v>PASSION FRUIT</v>
-      </c>
-      <c r="N33" t="str">
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <v/>
-      </c>
-      <c r="P33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>RICOTTA, AMARENE &amp; NOCCIOLE PRALINATE</v>
-      </c>
-      <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v/>
+        <v>STRACCHINO PERA</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
-      <c r="E34" t="str">
-        <v>PERA E PECORINO DOP</v>
-      </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v>SUSHI MISTI</v>
-      </c>
-      <c r="J34" t="str">
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <v>PENSIERO</v>
-      </c>
-      <c r="N34" t="str">
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <v/>
-      </c>
-      <c r="P34">
-        <v>1</v>
+        <v>V. NOCCIOLA F.</v>
+      </c>
+      <c r="H34">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>STRACCHINO ALBICOCCHA</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
       <c r="D35" t="str">
         <v/>
       </c>
-      <c r="E35" t="str">
-        <v>PESCA BIANCA AL BASILICO</v>
-      </c>
       <c r="F35" t="str">
         <v/>
       </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
       <c r="H35" t="str">
         <v/>
-      </c>
-      <c r="I35" t="str">
-        <v>SUSHI TIRAMISU</v>
-      </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="M35" t="str">
-        <v>PERA</v>
-      </c>
-      <c r="N35" t="str">
-        <v/>
-      </c>
-      <c r="O35" t="str">
-        <v/>
-      </c>
-      <c r="P35">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>RISO E VANIGLIA</v>
-      </c>
-      <c r="B36" t="str">
-        <v/>
+        <v>STRACCIATELLA</v>
+      </c>
+      <c r="B36">
+        <v>10</v>
       </c>
       <c r="C36" t="str">
-        <v/>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="str">
-        <v>PESCA TABACCHIERA</v>
+        <v>TOTAL:</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
       <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v>TORTA AGNESE 6P</v>
-      </c>
-      <c r="J36" t="str">
-        <v/>
-      </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <v>PESCHE AL VINO</v>
-      </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <v/>
-      </c>
-      <c r="P36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SEADAS</v>
-      </c>
-      <c r="B37" t="str">
-        <v/>
-      </c>
-      <c r="C37" t="str">
-        <v/>
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
-      <c r="E37" t="str">
-        <v>POMODORO DATTERINO</v>
-      </c>
       <c r="F37" t="str">
         <v/>
       </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
       <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
-        <v>TORTA AGNESE 8P</v>
-      </c>
-      <c r="J37" t="str">
-        <v/>
-      </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v/>
-      </c>
-      <c r="M37" t="str">
-        <v>PRUGNA ROSSA, FIORI D'IBISCO</v>
-      </c>
-      <c r="N37" t="str">
-        <v/>
-      </c>
-      <c r="O37" t="str">
-        <v/>
-      </c>
-      <c r="P37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
       <c r="D38" t="str">
         <v/>
       </c>
-      <c r="E38" t="str">
-        <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
-      </c>
       <c r="F38" t="str">
         <v/>
       </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
       <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v>TORTA CHEESCAKE 6P</v>
-      </c>
-      <c r="J38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <v>PRUGNE AL SAKE'</v>
-      </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <v/>
-      </c>
-      <c r="P38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39" t="str">
-        <v>ROSA KAEKADE E ARANCIA</v>
+        <v>YOGURT</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
       <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v>TORTA CHEESCAKE 8P</v>
-      </c>
-      <c r="J39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <v>PUNCH PARADISE</v>
-      </c>
-      <c r="N39" t="str">
-        <v/>
-      </c>
-      <c r="O39" t="str">
-        <v/>
-      </c>
-      <c r="P39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>STRACCIATELLA</v>
-      </c>
-      <c r="B40" t="str">
-        <v/>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40" t="str">
-        <v>STRACCIATELLA AL FIOR DI RISO</v>
-      </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v>TORTA LAURA 6P</v>
-      </c>
-      <c r="J40" t="str">
-        <v/>
-      </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <v>RIBES NERO</v>
-      </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40" t="str">
-        <v/>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>TE VERDE MATCHA</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v>TORRONE SALATO</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v>TORTA LAURA 8P</v>
-      </c>
-      <c r="J41" t="str">
-        <v/>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v>UVA E NOCI</v>
-      </c>
-      <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v/>
-      </c>
-      <c r="P41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>VENERE ROSA</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
-      </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="str">
-        <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v>TORTA TIRAMISU 6P</v>
-      </c>
-      <c r="J42" t="str">
-        <v/>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <v>UVA FRAGOLA E ZENZERO</v>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-      <c r="P42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>YOGURT</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43" t="str">
-        <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v>TORTA TIRAMISU 8P</v>
-      </c>
-      <c r="J43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
-      <c r="M43" t="str">
-        <v>V. BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <v/>
-      </c>
-      <c r="P43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v/>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="J44" t="str">
-        <v/>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-      <c r="L44" t="str">
-        <v/>
-      </c>
-      <c r="M44" t="str">
-        <v>V. CASTAGNA AL WHISKY</v>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
-        <v/>
-      </c>
-      <c r="P44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v/>
-      </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
-      <c r="C45" t="str">
-        <v/>
-      </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="J45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v>V. CASTAGNA E MIRTO</v>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-      <c r="P45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v/>
-      </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-      <c r="J46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="M46" t="str">
-        <v>V. EVERGREEN BRONTE VEGAN</v>
-      </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46" t="str">
-        <v/>
-      </c>
-      <c r="P46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v/>
-      </c>
-      <c r="B47" t="str">
-        <v/>
-      </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="D47" t="str">
-        <v/>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
-        <v/>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-      <c r="J47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-      <c r="L47" t="str">
-        <v/>
-      </c>
-      <c r="M47" t="str">
-        <v>V. NOCCIOLA AL FRUTTOSIO</v>
-      </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="O47" t="str">
-        <v/>
-      </c>
-      <c r="P47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v/>
-      </c>
-      <c r="B48" t="str">
-        <v/>
-      </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48" t="str">
-        <v/>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48" t="str">
-        <v>ZUCCA COI SUOI SEMI CARAMELLATI</v>
-      </c>
-      <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="O48" t="str">
-        <v/>
-      </c>
-      <c r="P48" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2838,7 +1356,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -2847,10 +1365,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>3.709</v>
+        <v>2.495</v>
       </c>
     </row>
     <row r="3">
@@ -2858,7 +1376,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -2867,10 +1385,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>6.784</v>
+        <v>6.457</v>
       </c>
     </row>
     <row r="4">
@@ -2887,10 +1405,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E4" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" t="str">
-        <v>32.779</v>
+        <v>20.732</v>
       </c>
     </row>
     <row r="5">
@@ -2898,7 +1416,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -2907,10 +1425,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>5.858</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="6">
@@ -2918,7 +1436,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -2930,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>2.089</v>
+        <v>2.733</v>
       </c>
     </row>
     <row r="7">
@@ -2938,7 +1456,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -2947,10 +1465,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.693</v>
+        <v>5.698</v>
       </c>
     </row>
     <row r="8">
@@ -2958,7 +1476,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -2967,10 +1485,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E8" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>9.164</v>
+        <v>2.893</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +1496,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2987,10 +1505,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>6.290</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="10">
@@ -2998,7 +1516,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -3010,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.985</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="11">
@@ -3018,7 +1536,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -3027,10 +1545,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E11" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>14.554</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="12">
@@ -3038,7 +1556,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -3047,10 +1565,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="str">
-        <v>3.132</v>
+        <v>11.998</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +1576,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -3070,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.971</v>
+        <v>3.248</v>
       </c>
     </row>
     <row r="14">
@@ -3078,7 +1596,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3087,10 +1605,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E14" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>18.397</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="15">
@@ -3098,7 +1616,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -3110,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>2.851</v>
+        <v>2.999</v>
       </c>
     </row>
     <row r="16">
@@ -3118,7 +1636,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -3127,10 +1645,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E16" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F16" t="str">
-        <v>16.410</v>
+        <v>8.765</v>
       </c>
     </row>
     <row r="17">
@@ -3138,7 +1656,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -3147,10 +1665,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>2.497</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="18">
@@ -3158,7 +1676,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -3170,7 +1688,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.409</v>
+        <v>4.853</v>
       </c>
     </row>
     <row r="19">
@@ -3178,7 +1696,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -3187,10 +1705,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="str">
-        <v>5.256</v>
+        <v>10.138</v>
       </c>
     </row>
     <row r="20">
@@ -3210,7 +1728,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>5.337</v>
+        <v>4.819</v>
       </c>
     </row>
     <row r="21">
@@ -3218,7 +1736,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3227,10 +1745,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>7.681</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="22">
@@ -3238,7 +1756,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3247,10 +1765,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>7.867</v>
+        <v>2.927</v>
       </c>
     </row>
     <row r="23">
@@ -3267,10 +1785,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>5.416</v>
+        <v>11.152</v>
       </c>
     </row>
     <row r="24">
@@ -3287,10 +1805,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E24" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>12.996</v>
+        <v>2.293</v>
       </c>
     </row>
     <row r="25">
@@ -3307,10 +1825,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>9.144</v>
+        <v>4.533</v>
       </c>
     </row>
     <row r="26">
@@ -3327,10 +1845,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>2.995</v>
+        <v>6.128</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +1856,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -3347,10 +1865,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E27" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F27" t="str">
-        <v>15.620</v>
+        <v>8.377</v>
       </c>
     </row>
     <row r="28">
@@ -3358,7 +1876,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -3367,10 +1885,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E28" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>10.724</v>
+        <v>7.965</v>
       </c>
     </row>
     <row r="29">
@@ -3378,7 +1896,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LEMON CURD</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -3390,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>2.436</v>
+        <v>3.150</v>
       </c>
     </row>
     <row r="30">
@@ -3398,7 +1916,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -3407,10 +1925,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E30" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>12.338</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="31">
@@ -3418,7 +1936,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -3427,10 +1945,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.765</v>
+        <v>3.239</v>
       </c>
     </row>
     <row r="32">
@@ -3438,7 +1956,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -3447,10 +1965,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.857</v>
+        <v>4.903</v>
       </c>
     </row>
     <row r="33">
@@ -3458,7 +1976,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -3467,10 +1985,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="str">
-        <v>2.903</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="34">
@@ -3478,7 +1996,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MELONE</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -3487,10 +2005,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.828</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="35">
@@ -3498,7 +2016,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -3507,10 +2025,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E35" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>16.497</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="36">
@@ -3518,7 +2036,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -3530,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.173</v>
+        <v>2.987</v>
       </c>
     </row>
     <row r="37">
@@ -3538,7 +2056,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -3547,10 +2065,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>2.800</v>
+        <v>9.289</v>
       </c>
     </row>
     <row r="38">
@@ -3558,7 +2076,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MIRTILLO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -3567,10 +2085,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>4.866</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="39">
@@ -3578,7 +2096,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -3587,10 +2105,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>8.802</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="40">
@@ -3598,7 +2116,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>NOCCIOLA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -3607,10 +2125,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E40" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>14.252</v>
+        <v>4.780</v>
       </c>
     </row>
     <row r="41">
@@ -3618,7 +2136,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PERA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -3627,10 +2145,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>2.985</v>
+        <v>5.097</v>
       </c>
     </row>
     <row r="42">
@@ -3638,7 +2156,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3647,10 +2165,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="str">
-        <v>6.250</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +2176,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PASSION FRUIT</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3670,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>4.408</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="44">
@@ -3678,7 +2196,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PERA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3687,10 +2205,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>4.767</v>
+        <v>2.922</v>
       </c>
     </row>
     <row r="45">
@@ -3698,7 +2216,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -3707,10 +2225,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.115</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="46">
@@ -3718,7 +2236,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -3727,10 +2245,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E46" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>6.155</v>
+        <v>2.691</v>
       </c>
     </row>
     <row r="47">
@@ -3738,7 +2256,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -3747,10 +2265,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E47" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="str">
-        <v>8.370</v>
+        <v>11.306</v>
       </c>
     </row>
     <row r="48">
@@ -3758,7 +2276,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -3767,10 +2285,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E48" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F48" t="str">
-        <v>8.641</v>
+        <v>13.450</v>
       </c>
     </row>
     <row r="49">
@@ -3778,7 +2296,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -3787,10 +2305,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>5.711</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="50">
@@ -3798,7 +2316,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -3810,7 +2328,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>5.398</v>
+        <v>5.804</v>
       </c>
     </row>
     <row r="51">
@@ -3818,7 +2336,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3830,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>5.533</v>
+        <v>5.497</v>
       </c>
     </row>
     <row r="52">
@@ -3838,7 +2356,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3847,10 +2365,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E52" t="str">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>27.518</v>
+        <v>5.047</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +2376,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>TIRAMISU'</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -3870,7 +2388,7 @@
         <v>3</v>
       </c>
       <c r="F53" t="str">
-        <v>8.242</v>
+        <v>8.762</v>
       </c>
     </row>
     <row r="54">
@@ -3878,7 +2396,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -3890,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.310</v>
+        <v>2.670</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +2416,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3910,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>3.100</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="56">
@@ -3918,7 +2436,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -3927,10 +2445,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="str">
-        <v>5.680</v>
+        <v>20.200</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +2456,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PENSIERO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -3950,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.243</v>
+        <v>2.595</v>
       </c>
     </row>
     <row r="58">
@@ -3958,7 +2476,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -3967,10 +2485,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>8.291</v>
+        <v>5.801</v>
       </c>
     </row>
     <row r="59">
@@ -3978,7 +2496,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CARROT CAKE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -3990,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>5.802</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="60">
@@ -3998,7 +2516,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -4007,10 +2525,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E60" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>25.500</v>
+        <v>2.610</v>
       </c>
     </row>
     <row r="61">
@@ -4018,7 +2536,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4027,10 +2545,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E61" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>8.449</v>
+        <v>6.005</v>
       </c>
     </row>
     <row r="62">
@@ -4038,7 +2556,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4050,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>2.612</v>
+        <v>2.119</v>
       </c>
     </row>
     <row r="63">
@@ -4058,7 +2576,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4067,10 +2585,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E63" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>1.751</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="64">
@@ -4078,7 +2596,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4090,7 +2608,7 @@
         <v>2</v>
       </c>
       <c r="F64" t="str">
-        <v>5.733</v>
+        <v>6.296</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +2616,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>LATTE DI FICO (PAMPANELLA)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4110,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>2.778</v>
+        <v>3.151</v>
       </c>
     </row>
     <row r="66">
@@ -4118,7 +2636,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4127,10 +2645,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F66" t="str">
-        <v>3.216</v>
+        <v>20.332</v>
       </c>
     </row>
     <row r="67">
@@ -4138,7 +2656,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4147,10 +2665,10 @@
         <v>Mantenimento</v>
       </c>
       <c r="E67" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <v>3.305</v>
+        <v>11.802</v>
       </c>
     </row>
     <row r="68">
@@ -4158,7 +2676,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>SACHER TORTE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4170,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.532</v>
+        <v>3.004</v>
       </c>
     </row>
     <row r="69">
@@ -4178,7 +2696,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4190,132 +2708,12 @@
         <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>1.078</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B70" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E70" t="str">
-        <v>1</v>
-      </c>
-      <c r="F70" t="str">
-        <v>3.053</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E71" t="str">
-        <v>3</v>
-      </c>
-      <c r="F71" t="str">
-        <v>8.337</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E72" t="str">
-        <v>5</v>
-      </c>
-      <c r="F72" t="str">
-        <v>14.905</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B73" t="str">
-        <v>FIORDILATTE NEW</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="D73" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E73" t="str">
-        <v>1</v>
-      </c>
-      <c r="F73" t="str">
-        <v>1.936</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B74" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="D74" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E74" t="str">
-        <v>2</v>
-      </c>
-      <c r="F74" t="str">
-        <v>5.924</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B75" t="str">
-        <v>FASHIONED SPRITZ</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v>Mantenimento</v>
-      </c>
-      <c r="E75" t="str">
-        <v>1</v>
-      </c>
-      <c r="F75" t="str">
-        <v>2.560</v>
+        <v>5.807</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4361,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.513</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="3">
@@ -4378,10 +2776,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>5.034</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="4">
@@ -4401,7 +2799,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>7.547</v>
+        <v>7.948</v>
       </c>
     </row>
     <row r="5">
@@ -4421,7 +2819,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>11.259</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="6">
@@ -4429,7 +2827,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -4438,10 +2836,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6" t="str">
-        <v>3.213</v>
+        <v>29.554</v>
       </c>
     </row>
     <row r="7">
@@ -4449,7 +2847,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -4458,10 +2856,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>21.197</v>
+        <v>4.333</v>
       </c>
     </row>
     <row r="8">
@@ -4469,7 +2867,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -4478,10 +2876,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>9.119</v>
+        <v>8.470</v>
       </c>
     </row>
     <row r="9">
@@ -4489,7 +2887,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -4498,10 +2896,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>10.867</v>
+        <v>8.134</v>
       </c>
     </row>
     <row r="10">
@@ -4509,7 +2907,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -4521,7 +2919,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>8.564</v>
+        <v>7.966</v>
       </c>
     </row>
     <row r="11">
@@ -4529,7 +2927,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CAFFE'</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -4538,10 +2936,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>8.475</v>
+        <v>3.482</v>
       </c>
     </row>
     <row r="12">
@@ -4549,7 +2947,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -4558,10 +2956,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>3.697</v>
+        <v>14.212</v>
       </c>
     </row>
     <row r="13">
@@ -4569,7 +2967,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -4578,10 +2976,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="str">
-        <v>4.903</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="14">
@@ -4589,7 +2987,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -4598,10 +2996,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>14.886</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="15">
@@ -4609,7 +3007,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -4618,10 +3016,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" t="str">
-        <v>3.082</v>
+        <v>15.493</v>
       </c>
     </row>
     <row r="16">
@@ -4629,7 +3027,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -4638,10 +3036,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>3.135</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="17">
@@ -4649,7 +3047,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -4658,10 +3056,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>3.044</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="18">
@@ -4669,7 +3067,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -4678,10 +3076,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>17.773</v>
+        <v>7.328</v>
       </c>
     </row>
     <row r="19">
@@ -4689,7 +3087,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -4701,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.875</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="20">
@@ -4709,7 +3107,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4718,10 +3116,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>10.017</v>
+        <v>5.388</v>
       </c>
     </row>
     <row r="21">
@@ -4729,7 +3127,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4738,10 +3136,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>7.901</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="22">
@@ -4749,7 +3147,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -4761,7 +3159,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>4.975</v>
+        <v>5.459</v>
       </c>
     </row>
     <row r="23">
@@ -4769,7 +3167,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -4778,10 +3176,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>2.708</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="24">
@@ -4801,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.602</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="25">
@@ -4809,7 +3207,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>ESTASI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -4818,10 +3216,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="str">
-        <v>9.571</v>
+        <v>13.484</v>
       </c>
     </row>
     <row r="26">
@@ -4829,7 +3227,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -4838,10 +3236,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="str">
-        <v>16.427</v>
+        <v>17.670</v>
       </c>
     </row>
     <row r="27">
@@ -4849,7 +3247,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRAGOLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -4858,10 +3256,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>15.485</v>
+        <v>9.271</v>
       </c>
     </row>
     <row r="28">
@@ -4869,7 +3267,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -4878,10 +3276,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>6.545</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="29">
@@ -4898,10 +3296,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>6.137</v>
+        <v>8.575</v>
       </c>
     </row>
     <row r="30">
@@ -4909,7 +3307,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -4921,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.800</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="31">
@@ -4938,10 +3336,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" t="str">
-        <v>8.073</v>
+        <v>14.807</v>
       </c>
     </row>
     <row r="32">
@@ -4961,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.930</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="33">
@@ -4978,10 +3376,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.991</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="34">
@@ -4998,10 +3396,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.679</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="35">
@@ -5021,7 +3419,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>6.013</v>
+        <v>6.111</v>
       </c>
     </row>
     <row r="36">
@@ -5038,10 +3436,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>5.752</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="37">
@@ -5049,7 +3447,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -5058,10 +3456,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>7.192</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="38">
@@ -5069,7 +3467,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -5078,10 +3476,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.027</v>
+        <v>2.509</v>
       </c>
     </row>
     <row r="39">
@@ -5089,7 +3487,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MORA</v>
+        <v>MELONE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -5101,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.411</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="40">
@@ -5109,7 +3507,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MORA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -5118,10 +3516,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.760</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="41">
@@ -5129,7 +3527,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -5138,10 +3536,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" t="str">
-        <v>14.382</v>
+        <v>8.818</v>
       </c>
     </row>
     <row r="42">
@@ -5149,7 +3547,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -5158,10 +3556,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F42" t="str">
-        <v>6.207</v>
+        <v>17.373</v>
       </c>
     </row>
     <row r="43">
@@ -5169,7 +3567,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -5178,10 +3576,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>2.507</v>
+        <v>6.043</v>
       </c>
     </row>
     <row r="44">
@@ -5189,7 +3587,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -5201,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.396</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="45">
@@ -5209,7 +3607,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -5218,10 +3616,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>6.761</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="46">
@@ -5229,7 +3627,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -5241,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.303</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="47">
@@ -5249,7 +3647,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PERA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -5258,10 +3656,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>22.949</v>
+        <v>4.971</v>
       </c>
     </row>
     <row r="48">
@@ -5269,7 +3667,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>POLLICINA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -5281,7 +3679,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>5.607</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="49">
@@ -5289,7 +3687,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -5298,10 +3696,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F49" t="str">
-        <v>4.436</v>
+        <v>35.047</v>
       </c>
     </row>
     <row r="50">
@@ -5309,7 +3707,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -5318,10 +3716,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.590</v>
+        <v>2.418</v>
       </c>
     </row>
     <row r="51">
@@ -5329,7 +3727,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -5338,10 +3736,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.839</v>
+        <v>5.670</v>
       </c>
     </row>
     <row r="52">
@@ -5361,7 +3759,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>5.797</v>
+        <v>5.514</v>
       </c>
     </row>
     <row r="53">
@@ -5378,10 +3776,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>5.859</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="54">
@@ -5398,10 +3796,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F54" t="str">
-        <v>30.139</v>
+        <v>36.581</v>
       </c>
     </row>
     <row r="55">
@@ -5409,7 +3807,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TIRAMISU'</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -5418,10 +3816,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>8.113</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="56">
@@ -5429,7 +3827,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>UVA E NOCI</v>
+        <v>YOGURT</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -5441,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>2.444</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="57">
@@ -5449,7 +3847,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>VENERE ROSA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -5461,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.609</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="58">
@@ -5469,7 +3867,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>YOGURT</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -5478,10 +3876,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>8.210</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="59">
@@ -5489,7 +3887,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -5498,10 +3896,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>2.651</v>
+        <v>7.920</v>
       </c>
     </row>
     <row r="60">
@@ -5509,7 +3907,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -5521,7 +3919,7 @@
         <v>3</v>
       </c>
       <c r="F60" t="str">
-        <v>6.972</v>
+        <v>8.344</v>
       </c>
     </row>
     <row r="61">
@@ -5529,7 +3927,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>PENSIERO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -5541,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.658</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="62">
@@ -5549,7 +3947,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -5558,10 +3956,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F62" t="str">
-        <v>8.269</v>
+        <v>20.371</v>
       </c>
     </row>
     <row r="63">
@@ -5569,7 +3967,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -5581,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.863</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="64">
@@ -5589,7 +3987,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -5601,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.576</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="65">
@@ -5609,7 +4007,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -5618,10 +4016,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>14.240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66">
@@ -5629,7 +4027,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -5641,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.462</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="67">
@@ -5649,7 +4047,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -5661,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>3.237</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="68">
@@ -5669,7 +4067,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -5681,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.271</v>
+        <v>2.897</v>
       </c>
     </row>
     <row r="69">
@@ -5689,7 +4087,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -5701,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.290</v>
+        <v>992</v>
       </c>
     </row>
     <row r="70">
@@ -5709,7 +4107,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -5718,10 +4116,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E70" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70" t="str">
-        <v>2.144</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="71">
@@ -5729,7 +4127,7 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -5738,10 +4136,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E71" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="str">
-        <v>2.915</v>
+        <v>5.181</v>
       </c>
     </row>
     <row r="72">
@@ -5749,7 +4147,7 @@
         <v>Stock</v>
       </c>
       <c r="B72" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -5758,10 +4156,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E72" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F72" t="str">
-        <v>2.759</v>
+        <v>4.276</v>
       </c>
     </row>
     <row r="73">
@@ -5769,7 +4167,7 @@
         <v>Stock</v>
       </c>
       <c r="B73" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -5778,10 +4176,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E73" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F73" t="str">
-        <v>13.854</v>
+        <v>6.620</v>
       </c>
     </row>
     <row r="74">
@@ -5789,7 +4187,7 @@
         <v>Stock</v>
       </c>
       <c r="B74" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -5798,10 +4196,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E74" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>5.611</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="75">
@@ -5818,10 +4216,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E75" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="str">
-        <v>3.211</v>
+        <v>6.103</v>
       </c>
     </row>
   </sheetData>
@@ -5833,7 +4231,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C112"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5848,18 +4246,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="B2" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="B3" t="str">
         <v>Da Ordinare</v>
@@ -5876,78 +4274,78 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C4" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="B5" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C5" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B6" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C6" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B7" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C7" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B8" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="B9" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C9" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CIOCCOLATO BIANCO</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="B10" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C10" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="B11" t="str">
         <v>Da Ordinare</v>
@@ -5958,29 +4356,29 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="B12" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="B13" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C13" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="B14" t="str">
         <v>Da Ordinare</v>
@@ -5991,7 +4389,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="B15" t="str">
         <v>Da Ordinare</v>
@@ -6002,40 +4400,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="B16" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C16" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="B17" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="B18" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C18" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="B19" t="str">
         <v>Da Ordinare</v>
@@ -6057,24 +4455,24 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="B21" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C21" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="B22" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C22" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -6085,7 +4483,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C23" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6096,7 +4494,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C24" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -6107,7 +4505,7 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C25" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -6118,45 +4516,45 @@
         <v>Da Ordinare</v>
       </c>
       <c r="C26" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B27" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C27" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIMONE</v>
       </c>
       <c r="B28" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C28" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LEMON CURD</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B29" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C29" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B30" t="str">
         <v>Da Ordinare</v>
@@ -6167,51 +4565,51 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B31" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="B32" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="B33" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C33" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MELONE</v>
       </c>
       <c r="B34" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C34" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="B35" t="str">
         <v>Da Ordinare</v>
@@ -6222,40 +4620,40 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="B36" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C36" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MELONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B37" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C37" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MIRTILLO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="B38" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C38" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="B39" t="str">
         <v>Da Ordinare</v>
@@ -6266,18 +4664,18 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NOCCIOLA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="B40" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C40" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PERA</v>
       </c>
       <c r="B41" t="str">
         <v>Da Ordinare</v>
@@ -6288,7 +4686,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="B42" t="str">
         <v>Da Ordinare</v>
@@ -6299,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PASSION FRUIT</v>
+        <v>POLLICINA</v>
       </c>
       <c r="B43" t="str">
         <v>Da Ordinare</v>
@@ -6310,7 +4708,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PERA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B44" t="str">
         <v>Da Ordinare</v>
@@ -6321,7 +4719,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B45" t="str">
         <v>Da Ordinare</v>
@@ -6332,29 +4730,29 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="B46" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C46" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="B47" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C47" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="B48" t="str">
         <v>Da Ordinare</v>
@@ -6365,7 +4763,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="B49" t="str">
         <v>Da Ordinare</v>
@@ -6376,7 +4774,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>YOGURT</v>
       </c>
       <c r="B50" t="str">
         <v>Da Ordinare</v>
@@ -6387,7 +4785,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SEADAS</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="B51" t="str">
         <v>Da Ordinare</v>
@@ -6398,62 +4796,62 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PENSIERO</v>
       </c>
       <c r="B52" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>TIRAMISU'</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="B53" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C53" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>UVA E NOCI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B54" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C54" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="B55" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C55" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B56" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>PENSIERO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="B57" t="str">
         <v>Da Ordinare</v>
@@ -6464,18 +4862,18 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B58" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C58" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CARROT CAKE</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="B59" t="str">
         <v>Da Ordinare</v>
@@ -6486,18 +4884,18 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="B60" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C60" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>FAVE FRESCHE &amp; PECORINO</v>
       </c>
       <c r="B61" t="str">
         <v>Da Ordinare</v>
@@ -6508,29 +4906,29 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="B62" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C62" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="B63" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C63" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="B64" t="str">
         <v>Da Ordinare</v>
@@ -6541,205 +4939,205 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LATTE DI FICO (PAMPANELLA)</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="B65" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C65" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="B66" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C66" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="B67" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C67" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SACHER TORTE</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="B68" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C68" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="B69" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C69" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>AMARENA</v>
       </c>
       <c r="B70" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C70" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="B71" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B72" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C72" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FIORDILATTE NEW</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="B73" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C73" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="B74" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C74" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>FASHIONED SPRITZ</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="B75" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C75" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ANGURIA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="B76" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C76" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="B77" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C77" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="B78" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C78" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="B79" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C79" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>BIANCANEVE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B80" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C80" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>CAFFE'</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B81" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C81" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>MORA</v>
       </c>
       <c r="B82" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C82" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>PAPAYA</v>
       </c>
       <c r="B83" t="str">
         <v>Da Ordinare</v>
@@ -6750,29 +5148,29 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CREMA AGNESE</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B84" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C84" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ESTASI</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B85" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C85" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="B86" t="str">
         <v>Da Ordinare</v>
@@ -6783,7 +5181,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MORA</v>
+        <v>SEADAS</v>
       </c>
       <c r="B87" t="str">
         <v>Da Ordinare</v>
@@ -6794,18 +5192,18 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="B88" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C88" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="B89" t="str">
         <v>Da Ordinare</v>
@@ -6816,7 +5214,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>VENERE ROSA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="B90" t="str">
         <v>Da Ordinare</v>
@@ -6827,40 +5225,40 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>YOGURT</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="B91" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C91" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="B92" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C92" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SACRIPANTE</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="B93" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C93" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="B94" t="str">
         <v>Da Ordinare</v>
@@ -6871,18 +5269,18 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B95" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C95" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="B96" t="str">
         <v>Da Ordinare</v>
@@ -6893,40 +5291,40 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="B97" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C97" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>COCCO</v>
       </c>
       <c r="B98" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C98" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PAPAYA</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="B99" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C99" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="B100" t="str">
         <v>Da Ordinare</v>
@@ -6937,7 +5335,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="B101" t="str">
         <v>Da Ordinare</v>
@@ -6948,7 +5346,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="B102" t="str">
         <v>Da Ordinare</v>
@@ -6959,18 +5357,18 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B103" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C103" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>MANDARINO</v>
       </c>
       <c r="B104" t="str">
         <v>Da Ordinare</v>
@@ -6981,7 +5379,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="B105" t="str">
         <v>Da Ordinare</v>
@@ -6992,18 +5390,18 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="B106" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C106" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="B107" t="str">
         <v>Da Ordinare</v>
@@ -7014,7 +5412,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="B108" t="str">
         <v>Da Ordinare</v>
@@ -7025,7 +5423,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MONT BLANC</v>
+        <v>CACHI</v>
       </c>
       <c r="B109" t="str">
         <v>Da Ordinare</v>
@@ -7036,7 +5434,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="B110" t="str">
         <v>Da Ordinare</v>
@@ -7047,51 +5445,29 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="B111" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C111" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>COCCO</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="B112" t="str">
         <v>Da Ordinare</v>
       </c>
       <c r="C112" t="str">
         <v>1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>MANDARINO</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C113" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>PASTIERA NAPOLETANA</v>
-      </c>
-      <c r="B114" t="str">
-        <v>Da Ordinare</v>
-      </c>
-      <c r="C114" t="str">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C112"/>
   </ignoredErrors>
 </worksheet>
 </file>